--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02E6903-5556-438A-ACEC-D6865094572A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0529E9-B895-4AE4-91B6-51997D41A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="3000" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="228">
   <si>
     <t>tag_name</t>
   </si>
@@ -492,13 +492,240 @@
   </si>
   <si>
     <t xml:space="preserve">In cases where no MUAC or mortality data is being collected, the sample size can be estimated based on other household level indicators such as FSL and WASH. The below table summarizes the sampling assumptions for each strata. </t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>handling</t>
+  </si>
+  <si>
+    <t>@tor_title</t>
+  </si>
+  <si>
+    <t>Research Terms of Reference</t>
+  </si>
+  <si>
+    <t>@research_cycle_title</t>
+  </si>
+  <si>
+    <t>@research_cycle_id</t>
+  </si>
+  <si>
+    <t>Integrated Public Health Rapid Assessment (IPHRA)</t>
+  </si>
+  <si>
+    <t>Research Cycle ID</t>
+  </si>
+  <si>
+    <t>replace</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>checkbox_replace</t>
+  </si>
+  <si>
+    <t>@header_exec_summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Summary </t>
+  </si>
+  <si>
+    <t>@header_country</t>
+  </si>
+  <si>
+    <t>Country of intervention</t>
+  </si>
+  <si>
+    <t>@header_type_emergency</t>
+  </si>
+  <si>
+    <t>Type of Emergency</t>
+  </si>
+  <si>
+    <t>Type of Crisis</t>
+  </si>
+  <si>
+    <t>@header_type_crisis</t>
+  </si>
+  <si>
+    <t>@header_crisis_natural_disaster</t>
+  </si>
+  <si>
+    <t>@header_crisis_conflict</t>
+  </si>
+  <si>
+    <t>@header_crisis_other</t>
+  </si>
+  <si>
+    <t>@header_crisis_sudden_onset</t>
+  </si>
+  <si>
+    <t>@header_crisis_slow_onset</t>
+  </si>
+  <si>
+    <t>@header_crisis_protracted</t>
+  </si>
+  <si>
+    <t>Natural disaster</t>
+  </si>
+  <si>
+    <t>Conflict</t>
+  </si>
+  <si>
+    <t>Protracted</t>
+  </si>
+  <si>
+    <t>Other (Specify)</t>
+  </si>
+  <si>
+    <t>Sudden Onset</t>
+  </si>
+  <si>
+    <t>Slow Onset</t>
+  </si>
+  <si>
+    <t>@header_mandating_agency</t>
+  </si>
+  <si>
+    <t>Mandating Body/ Agency</t>
+  </si>
+  <si>
+    <t>IMPACT Project Code</t>
+  </si>
+  <si>
+    <t>@header_impact_project_code</t>
+  </si>
+  <si>
+    <t>@header_overall_timeframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Research Timeframe </t>
+  </si>
+  <si>
+    <t>@header_research_timeframe</t>
+  </si>
+  <si>
+    <t>Research Timeframe</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>@header_pilot_date</t>
+  </si>
+  <si>
+    <t>Pilot/ training:</t>
+  </si>
+  <si>
+    <t>@header_data_start_date</t>
+  </si>
+  <si>
+    <t>@header_data_end_date</t>
+  </si>
+  <si>
+    <t>@header_analysis_date</t>
+  </si>
+  <si>
+    <t>@header_data_validation_date</t>
+  </si>
+  <si>
+    <t>@header_prelim_presentation_date</t>
+  </si>
+  <si>
+    <t>@header_output_validation_date</t>
+  </si>
+  <si>
+    <t>@header_output_published_date</t>
+  </si>
+  <si>
+    <t>@header_final_presentation_date</t>
+  </si>
+  <si>
+    <t>@crisis_other</t>
+  </si>
+  <si>
+    <t>@crisis_conflict</t>
+  </si>
+  <si>
+    <t>@crisis_natural_disaster</t>
+  </si>
+  <si>
+    <t>@crisis_sudden_onset</t>
+  </si>
+  <si>
+    <t>@crisis_slow_onset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data collected: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start collect data: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysed: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data sent for validation: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preliminary presentation: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outputs sent for validation: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outputs published: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final presentation: </t>
+  </si>
+  <si>
+    <t>@header_humanitarian_milestone</t>
+  </si>
+  <si>
+    <t>@header_milestone</t>
+  </si>
+  <si>
+    <t>@header_deadline</t>
+  </si>
+  <si>
+    <t>Deadline (can be tentative)</t>
+  </si>
+  <si>
+    <t>Milestone</t>
+  </si>
+  <si>
+    <t>Humanitarian milestones
+Specify what will the assessment inform and when 
+e.g. The shelter cluster will use this data to draft its Revised Flash Appeal;</t>
+  </si>
+  <si>
+    <t>@header_milestone_donor</t>
+  </si>
+  <si>
+    <t>@header_milestone_intercluster</t>
+  </si>
+  <si>
+    <t>@header_milestone_cluster</t>
+  </si>
+  <si>
+    <t>@header_milestone_ngo_platform</t>
+  </si>
+  <si>
+    <t>@header_milestone_other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +737,47 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFEE5859"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -532,10 +800,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,938 +1125,1565 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:D188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.5703125" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="8" spans="1:4" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B27" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B29" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B61" t="s">
+        <v>162</v>
+      </c>
+      <c r="D61" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B70" t="s">
+        <v>164</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>25</v>
       </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>26</v>
       </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B72" t="s">
+        <v>164</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>28</v>
       </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B76" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B77" t="s">
+        <v>164</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>32</v>
       </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>34</v>
       </c>
-      <c r="B31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B80" t="s">
+        <v>164</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>35</v>
       </c>
-      <c r="B32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B81" t="s">
+        <v>164</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>36</v>
       </c>
-      <c r="B33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B82" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>37</v>
       </c>
-      <c r="B34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>38</v>
       </c>
-      <c r="B35" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B84" t="s">
+        <v>164</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>39</v>
       </c>
-      <c r="B36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B85" t="s">
+        <v>164</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>40</v>
       </c>
-      <c r="B37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B86" t="s">
+        <v>164</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>41</v>
       </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B87" t="s">
+        <v>164</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>42</v>
       </c>
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B88" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>43</v>
       </c>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B89" t="s">
+        <v>164</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>44</v>
       </c>
-      <c r="B41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B90" t="s">
+        <v>164</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>45</v>
       </c>
-      <c r="B42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B91" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>46</v>
       </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B92" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>47</v>
       </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B93" t="s">
+        <v>164</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>48</v>
       </c>
-      <c r="B45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B94" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>49</v>
       </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B95" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>50</v>
       </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B96" t="s">
+        <v>164</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>51</v>
       </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B97" t="s">
+        <v>164</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>52</v>
       </c>
-      <c r="B49" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B98" t="s">
+        <v>164</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>53</v>
       </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B99" t="s">
+        <v>164</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>54</v>
       </c>
-      <c r="B51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B100" t="s">
+        <v>164</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>55</v>
       </c>
-      <c r="B52" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B101" t="s">
+        <v>164</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>57</v>
       </c>
-      <c r="B54" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>58</v>
       </c>
-      <c r="B55" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>59</v>
       </c>
-      <c r="B56" t="s">
+      <c r="D105" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>61</v>
       </c>
-      <c r="B57" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>62</v>
       </c>
-      <c r="B58" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>74</v>
       </c>
-      <c r="B70" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>75</v>
       </c>
-      <c r="B71" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>76</v>
       </c>
-      <c r="B72" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>77</v>
       </c>
-      <c r="B73" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>78</v>
       </c>
-      <c r="B74" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>79</v>
       </c>
-      <c r="B75" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>80</v>
       </c>
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>81</v>
       </c>
-      <c r="B77" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>82</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D127" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>84</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D128" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>98</v>
       </c>
-      <c r="B93" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="D142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>99</v>
       </c>
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="D143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>100</v>
       </c>
-      <c r="B95" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="D144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>101</v>
       </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="D145" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>102</v>
       </c>
-      <c r="B97" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="D146" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>103</v>
       </c>
-      <c r="B98" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="D147" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>104</v>
       </c>
-      <c r="B99" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="D148" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>105</v>
       </c>
-      <c r="B100" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="D149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>106</v>
       </c>
-      <c r="B101" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="D150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>107</v>
       </c>
-      <c r="B102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="D151" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>108</v>
       </c>
-      <c r="B103" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="D152" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>109</v>
       </c>
-      <c r="B104" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="D153" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>110</v>
       </c>
-      <c r="B105" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="D154" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>111</v>
       </c>
-      <c r="B106" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>112</v>
       </c>
-      <c r="B107" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="D156" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>113</v>
       </c>
-      <c r="B108" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="D157" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>114</v>
       </c>
-      <c r="B109" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="D158" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>125</v>
       </c>
-      <c r="B120" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="D169" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>126</v>
       </c>
-      <c r="B121" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="D170" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0529E9-B895-4AE4-91B6-51997D41A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF81DB17-EAB8-4C26-A021-819798752877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="530">
   <si>
     <t>tag_name</t>
   </si>
@@ -65,9 +65,6 @@
     <t>@geographic_coverage</t>
   </si>
   <si>
-    <t>@recall_period</t>
-  </si>
-  <si>
     <t>@general_objective</t>
   </si>
   <si>
@@ -104,24 +101,6 @@
     <t>@final_presentation_date</t>
   </si>
   <si>
-    <t>@em_natural_d</t>
-  </si>
-  <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>@em_conflict</t>
-  </si>
-  <si>
-    <t>@em_other</t>
-  </si>
-  <si>
-    <t>@crisis_sudden</t>
-  </si>
-  <si>
-    <t>@crisis_slow</t>
-  </si>
-  <si>
     <t>@crisis_protracted</t>
   </si>
   <si>
@@ -215,9 +194,6 @@
     <t>@num_strata_units</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>@popsize_known_strata_unit_yes</t>
   </si>
   <si>
@@ -242,9 +218,6 @@
     <t>@kii_wash_inc</t>
   </si>
   <si>
-    <t>@kii_nut_inc</t>
-  </si>
-  <si>
     <t>@obs_community_inc</t>
   </si>
   <si>
@@ -278,18 +251,6 @@
     <t>@sampling_hh_rlc</t>
   </si>
   <si>
-    <t>@sampling_modified_epi</t>
-  </si>
-  <si>
-    <t>@sample_site_target</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>@sample_hh_target</t>
-  </si>
-  <si>
     <t>@precision_gen_indicator</t>
   </si>
   <si>
@@ -326,21 +287,12 @@
     <t>@num_obs_latrine_target</t>
   </si>
   <si>
-    <t>@num_obs_waterpoint_target</t>
-  </si>
-  <si>
     <t>@gender_disagg_yes</t>
   </si>
   <si>
     <t>@gender_disagg_no</t>
   </si>
   <si>
-    <t>@sex_disagg_yes</t>
-  </si>
-  <si>
-    <t>@sex_disagg_no</t>
-  </si>
-  <si>
     <t>@platform_impact</t>
   </si>
   <si>
@@ -492,12 +444,6 @@
   </si>
   <si>
     <t xml:space="preserve">In cases where no MUAC or mortality data is being collected, the sample size can be estimated based on other household level indicators such as FSL and WASH. The below table summarizes the sampling assumptions for each strata. </t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>character</t>
   </si>
   <si>
     <t>handling</t>
@@ -719,13 +665,1096 @@
   </si>
   <si>
     <t>@header_milestone_other</t>
+  </si>
+  <si>
+    <t>@date_milestone_donor</t>
+  </si>
+  <si>
+    <t>@date_milestone_intercluster</t>
+  </si>
+  <si>
+    <t>@date_milestone_cluster</t>
+  </si>
+  <si>
+    <t>@date_milestone_ngo_platform</t>
+  </si>
+  <si>
+    <t>@date_milestone_other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donor plan/strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inter-cluster plan/strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster plan/strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGO platform plan/strategy </t>
+  </si>
+  <si>
+    <t>Other (Specify):</t>
+  </si>
+  <si>
+    <t>@header_audience_type_dissemination</t>
+  </si>
+  <si>
+    <t>@header_audience_type</t>
+  </si>
+  <si>
+    <t>@header_dissemination</t>
+  </si>
+  <si>
+    <t>Audience type</t>
+  </si>
+  <si>
+    <t>Audience type &amp; Dissemination</t>
+  </si>
+  <si>
+    <t>Dissemination</t>
+  </si>
+  <si>
+    <t>@header_audience_strategic</t>
+  </si>
+  <si>
+    <t>@header_audience_programmatic</t>
+  </si>
+  <si>
+    <t>@header_audience_operational</t>
+  </si>
+  <si>
+    <t>@header_audience_other</t>
+  </si>
+  <si>
+    <t>Programmatic</t>
+  </si>
+  <si>
+    <t>Operational</t>
+  </si>
+  <si>
+    <t>Strategic</t>
+  </si>
+  <si>
+    <t>[Other, Specify]</t>
+  </si>
+  <si>
+    <t>@header_dissem_general_mailing</t>
+  </si>
+  <si>
+    <t>@header_dissem_cluster_mailing</t>
+  </si>
+  <si>
+    <t>@header_dissem_presentation</t>
+  </si>
+  <si>
+    <t>@header_dissem_website</t>
+  </si>
+  <si>
+    <t>@header_dissem_other</t>
+  </si>
+  <si>
+    <t>General Product Mailing (e.g. mail to NGO consortium; HCT participants; Donors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster Mailing (Education, Shelter and WASH) and presentation of findings at next cluster meeting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentation of findings (e.g. at HCT meeting; Cluster meeting) </t>
+  </si>
+  <si>
+    <t>Website Dissemination (Relief Web &amp; REACH Resource Centre)</t>
+  </si>
+  <si>
+    <t>@header_yes</t>
+  </si>
+  <si>
+    <t>@header_no</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>@header_stakeholder_mapping</t>
+  </si>
+  <si>
+    <t>Stakeholder mapping Has a detailed stakeholder mapping been conducted during research design to identify all actors that could contribute to and/or benefit from the research?</t>
+  </si>
+  <si>
+    <t>@header_general_objective</t>
+  </si>
+  <si>
+    <t>General Objective</t>
+  </si>
+  <si>
+    <t>@header_specific_objective</t>
+  </si>
+  <si>
+    <t>Specific Objective(s)</t>
+  </si>
+  <si>
+    <t>@header_research_questions</t>
+  </si>
+  <si>
+    <t>Research Questions</t>
+  </si>
+  <si>
+    <t>@header_geographic_coverage</t>
+  </si>
+  <si>
+    <t>Geographic Coverage</t>
+  </si>
+  <si>
+    <t>Secondary data sources</t>
+  </si>
+  <si>
+    <t>@header_secondary_data_sources</t>
+  </si>
+  <si>
+    <t>@header_pop</t>
+  </si>
+  <si>
+    <t>Population(s)
+Select all that apply</t>
+  </si>
+  <si>
+    <t>@header_pop_idpcamp</t>
+  </si>
+  <si>
+    <t>@header_pop_idpinformal</t>
+  </si>
+  <si>
+    <t>@header_pop_idphost</t>
+  </si>
+  <si>
+    <t>@header_pop_idpother</t>
+  </si>
+  <si>
+    <t>@header_pop_refugee</t>
+  </si>
+  <si>
+    <t>@header_pop_refugeeinformal</t>
+  </si>
+  <si>
+    <t>@header_pop_refugeehost</t>
+  </si>
+  <si>
+    <t>@header_pop_refugeeother</t>
+  </si>
+  <si>
+    <t>@header_pop_host</t>
+  </si>
+  <si>
+    <t>@header_pop_other</t>
+  </si>
+  <si>
+    <t>IDPs in camp</t>
+  </si>
+  <si>
+    <t>IDPs in host communities</t>
+  </si>
+  <si>
+    <t>IDPs in informal sites</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IDPs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF58585A"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>[Other, Specify]</t>
+    </r>
+  </si>
+  <si>
+    <t>Refugees in camp</t>
+  </si>
+  <si>
+    <t>Refugees in informal sites</t>
+  </si>
+  <si>
+    <t>Refugees in host communities</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refugees </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF58585A"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>[Other, Specify]</t>
+    </r>
+  </si>
+  <si>
+    <t>Host communities</t>
+  </si>
+  <si>
+    <t>@header_stratification</t>
+  </si>
+  <si>
+    <t>@stratification_geographical</t>
+  </si>
+  <si>
+    <t>@stratification_group</t>
+  </si>
+  <si>
+    <t>@stratification_other</t>
+  </si>
+  <si>
+    <t>Stratification
+Select type(s) and enter number of strata</t>
+  </si>
+  <si>
+    <t>@header_stratification_geographical</t>
+  </si>
+  <si>
+    <t>@header_stratification_group</t>
+  </si>
+  <si>
+    <t>@header_stratification_other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geographical #: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group #: </t>
+  </si>
+  <si>
+    <r>
+      <t>[Other Specify]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> #: _ _ </t>
+    </r>
+  </si>
+  <si>
+    <t>@num_other_units</t>
+  </si>
+  <si>
+    <t>@popsize_known_other_unit_yes</t>
+  </si>
+  <si>
+    <t>@popsize_known_other_unit_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population size per strata is known? </t>
+  </si>
+  <si>
+    <t>@header_popsize_known</t>
+  </si>
+  <si>
+    <t>@header_data_collection_tools</t>
+  </si>
+  <si>
+    <t>Data collection tool(s)</t>
+  </si>
+  <si>
+    <t>@header_sampling_sites</t>
+  </si>
+  <si>
+    <t>@header_sampling_households</t>
+  </si>
+  <si>
+    <t>@header_data_collection_target</t>
+  </si>
+  <si>
+    <t>Sampling Sites</t>
+  </si>
+  <si>
+    <t>Sampling Households</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data collection target </t>
+  </si>
+  <si>
+    <t>@header_tool_household_survey</t>
+  </si>
+  <si>
+    <t>Tool 1: Household Survey Module
+Select sampling and specify target # interviews</t>
+  </si>
+  <si>
+    <t>row_delete</t>
+  </si>
+  <si>
+    <t>@header_sampling_srs</t>
+  </si>
+  <si>
+    <t>@header_sampling_stratified</t>
+  </si>
+  <si>
+    <t>@header_sampling_cluster</t>
+  </si>
+  <si>
+    <t>@header_sampling_exhaustive</t>
+  </si>
+  <si>
+    <t>@header_sampling_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_hh_srs</t>
+  </si>
+  <si>
+    <t>@header_sampling_hh_rlc</t>
+  </si>
+  <si>
+    <t>Probability / Stratified simple random</t>
+  </si>
+  <si>
+    <t>Probability / Simple random</t>
+  </si>
+  <si>
+    <t>Probability / Cluster Sampling</t>
+  </si>
+  <si>
+    <t>All eligible sites (Proportional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purposive </t>
+  </si>
+  <si>
+    <t>Random Location Cluster (RLC)</t>
+  </si>
+  <si>
+    <t>@sampling_sites_target</t>
+  </si>
+  <si>
+    <t>@sampling_household_target</t>
+  </si>
+  <si>
+    <t>@header_sampling_sites_target</t>
+  </si>
+  <si>
+    <t>@header_sampling_household_target</t>
+  </si>
+  <si>
+    <t>Sites or PSUs (Target #):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household interview (Target #): </t>
+  </si>
+  <si>
+    <t>@header_precision</t>
+  </si>
+  <si>
+    <t>Target level of precision if probability sampling for household survey</t>
+  </si>
+  <si>
+    <t>95% level of confidence</t>
+  </si>
+  <si>
+    <t>@header_95_confidence</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_community</t>
+  </si>
+  <si>
+    <t>Tool 2: Community Leader or Member Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>Purposive</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Snowballing</t>
+  </si>
+  <si>
+    <t>@sampling_kii_community_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_community_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_community_random</t>
+  </si>
+  <si>
+    <t>@sampling_kii_community_random</t>
+  </si>
+  <si>
+    <t>@header_sampling_community_kii_snowball</t>
+  </si>
+  <si>
+    <t>@sampling_kii_community_snowball</t>
+  </si>
+  <si>
+    <t>@sampling_kii_community_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_community_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_community_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_community_target</t>
+  </si>
+  <si>
+    <t>Key informant interviews (Target #):</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_health</t>
+  </si>
+  <si>
+    <t>Health Facility Key Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_health_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_health_other</t>
+  </si>
+  <si>
+    <t>@sampling_kii_health_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_kii_health_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_health_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_health_target</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_market</t>
+  </si>
+  <si>
+    <t>Market Vendor Key Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_market_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_kii_market_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_market_other</t>
+  </si>
+  <si>
+    <t>@sampling_kii_market_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_market_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_market_target</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_fsl</t>
+  </si>
+  <si>
+    <t>FSL Assistance Provider Key Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_fsl_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_kii_fsl_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_fsl_other</t>
+  </si>
+  <si>
+    <t>@sampling_kii_fsl_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_fsl_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_fsl_target</t>
+  </si>
+  <si>
+    <t>Key Informant Interviews (Target #):</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_wash</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_wash_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_kii_wash_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_wash_other</t>
+  </si>
+  <si>
+    <t>@sampling_kii_wash_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_wash_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_wash_target</t>
+  </si>
+  <si>
+    <t>WASH Service Provider Key Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>@header_tool_kii_nutrition</t>
+  </si>
+  <si>
+    <t>@kii_nutrition_inc</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_nutrition_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_kii_nutrition_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_nutrition_other</t>
+  </si>
+  <si>
+    <t>@sampling_kii_nutrition_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_kii_nutrition_target</t>
+  </si>
+  <si>
+    <t>@sampling_kii_nutrition_target</t>
+  </si>
+  <si>
+    <t>Nutrition Service Provider Key Informant Interview Tool
+Select sampling method and specify target # interviews</t>
+  </si>
+  <si>
+    <t>@header_tool_obs_community</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_community_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_obs_community_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_community_other</t>
+  </si>
+  <si>
+    <t>@sampling_obs_community_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_community_target</t>
+  </si>
+  <si>
+    <t>@sampling_obs_community_target</t>
+  </si>
+  <si>
+    <t>Community Observation Tool</t>
+  </si>
+  <si>
+    <t>@header_tool_obs_health</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_health_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_obs_health_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_health_other</t>
+  </si>
+  <si>
+    <t>@sampling_obs_health_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_health_target</t>
+  </si>
+  <si>
+    <t>@sampling_obs_health_target</t>
+  </si>
+  <si>
+    <t>Community Observations (Target #):</t>
+  </si>
+  <si>
+    <t>Health Facility Observation Tool</t>
+  </si>
+  <si>
+    <t>Health facility observations (Target #):</t>
+  </si>
+  <si>
+    <t>@header_tool_obs_latrine</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_latrine_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_obs_latrine_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_latrine_other</t>
+  </si>
+  <si>
+    <t>@sampling_obs_latrine_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_latrine_target</t>
+  </si>
+  <si>
+    <t>@sampling_obs_latrine_target</t>
+  </si>
+  <si>
+    <t>Latrine Observation Tool</t>
+  </si>
+  <si>
+    <t>Latrine stands observations (Target #):</t>
+  </si>
+  <si>
+    <t>Water point observations (Target #):</t>
+  </si>
+  <si>
+    <t>Water Point Observation Tool</t>
+  </si>
+  <si>
+    <t>@header_tool_obs_water</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_water_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_obs_water_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_water_other</t>
+  </si>
+  <si>
+    <t>@sampling_obs_water_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_water_target</t>
+  </si>
+  <si>
+    <t>@sampling_obs_water_target</t>
+  </si>
+  <si>
+    <t>@num_obs_water_target</t>
+  </si>
+  <si>
+    <t>@header_gender_disagg</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>@header_age_disagg</t>
+  </si>
+  <si>
+    <t>@header_gender_age_disagg</t>
+  </si>
+  <si>
+    <t>Disaggregation by gender and age 
+Are you planning to conduct sex/age disaggregated analysis?</t>
+  </si>
+  <si>
+    <t>@age_disagg_yes</t>
+  </si>
+  <si>
+    <t>@age_disagg_no</t>
+  </si>
+  <si>
+    <t>@header_impact</t>
+  </si>
+  <si>
+    <t>@header_unhcr</t>
+  </si>
+  <si>
+    <t>@header_other</t>
+  </si>
+  <si>
+    <t>@header_data_management_platform</t>
+  </si>
+  <si>
+    <t>Data management platform(s)</t>
+  </si>
+  <si>
+    <t>@header_expected_type</t>
+  </si>
+  <si>
+    <t>Expected ouput type(s)</t>
+  </si>
+  <si>
+    <t>@header_output_situation_overview</t>
+  </si>
+  <si>
+    <t>@header_output_report</t>
+  </si>
+  <si>
+    <t>@header_output_profile</t>
+  </si>
+  <si>
+    <t>@header_output_prelim_presentation</t>
+  </si>
+  <si>
+    <t>@header_output_final_presentation</t>
+  </si>
+  <si>
+    <t>@header_output_factsheet</t>
+  </si>
+  <si>
+    <t>@header_output_dashboard</t>
+  </si>
+  <si>
+    <t>@header_output_webmap</t>
+  </si>
+  <si>
+    <t>@header_output_map</t>
+  </si>
+  <si>
+    <t>@header_output_other</t>
+  </si>
+  <si>
+    <t>Situation overview #:</t>
+  </si>
+  <si>
+    <t>Report #:</t>
+  </si>
+  <si>
+    <t>Profile #:</t>
+  </si>
+  <si>
+    <t>Presentation (Preliminary findings) #:</t>
+  </si>
+  <si>
+    <t>Presentation (Final)  #:</t>
+  </si>
+  <si>
+    <t>Factsheet #:</t>
+  </si>
+  <si>
+    <t>Interactive dashboard #:</t>
+  </si>
+  <si>
+    <t>Webmap #:</t>
+  </si>
+  <si>
+    <t>Map #:</t>
+  </si>
+  <si>
+    <r>
+      <t>[Other, Specify]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> #:</t>
+    </r>
+  </si>
+  <si>
+    <t>IMPACT</t>
+  </si>
+  <si>
+    <t>UNHCR</t>
+  </si>
+  <si>
+    <t>@header_access</t>
+  </si>
+  <si>
+    <t>@header_access_public</t>
+  </si>
+  <si>
+    <t>@header_access_restricted</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Public (available on REACH resource center and other humanitarian platforms)</t>
+  </si>
+  <si>
+    <t>Restricted (bilateral dissemination only upon agreed dissemination list, no publication on REACH or other platforms)</t>
+  </si>
+  <si>
+    <t>@header_visibility</t>
+  </si>
+  <si>
+    <t>@header_visibility_reach</t>
+  </si>
+  <si>
+    <t>@header_visibility_donor</t>
+  </si>
+  <si>
+    <t>@header_visibility_coordination</t>
+  </si>
+  <si>
+    <t>@header_visibility_partners</t>
+  </si>
+  <si>
+    <t>Visibility Specify which logos should be on outputs</t>
+  </si>
+  <si>
+    <r>
+      <t>REACH</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [By default unless specified otherwise]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Donor:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [List logos here as per contract]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Coordination Framework:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [List logos here as relevant]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Partners:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [List logos here if outside coordination framework]</t>
+    </r>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>@header_rationale</t>
+  </si>
+  <si>
+    <t>@header_rationale_background</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Briefly describe the context, i.e. the crisis within which the IPHRA is planned.</t>
+  </si>
+  <si>
+    <t>@text_rationale_background1</t>
+  </si>
+  <si>
+    <t>@text_rationale_background2</t>
+  </si>
+  <si>
+    <t>@text_rationale_background3</t>
+  </si>
+  <si>
+    <t>Information gap and needs i.e. what is known so far about the topic of concern/ what remains to be known and why.</t>
+  </si>
+  <si>
+    <t>Links with in-country strategy i.e. how does this specific research complement/ advance our other ongoing activities in this specific context.</t>
+  </si>
+  <si>
+    <t>@header_rationale_intended_impact</t>
+  </si>
+  <si>
+    <t>Intended impact</t>
+  </si>
+  <si>
+    <t>Who are the key actors/ what are the key decision-making processes and milestones this research aims to inform?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What would be the impact of this research on </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF58585A"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>at least</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF58585A"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> one of the following: (1) Bringing about positive change in the day-to-day lives of the population of interest (2) Improving understanding of the current situation to inform ongoing or planned humanitarian interventions (3) Improving understanding of the current situation to inform strategic decision-making processes, including funding allocations (4) Contributing towards system-wide change</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">@text_rationale_intended_impact1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@text_rationale_intended_impact2 </t>
+  </si>
+  <si>
+    <t>@header_methodology</t>
+  </si>
+  <si>
+    <t>@header_methodology_overview</t>
+  </si>
+  <si>
+    <t>Methodology overview</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview1</t>
+  </si>
+  <si>
+    <t>The general research design for the Integrated Public Health Rapid Assessment (IPHRA) will consist of a mixed-methods approach constituting three main methods: household surveys; Key Informant Interviews (KIIs); and observation checklists, each of these methods having core and supplemental specialized tools and information that can be collected.</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_rlc</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_rlc</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_rlc</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_rlc</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive</t>
+  </si>
+  <si>
+    <t>conditional_replace</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_srs</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_systematic</t>
+  </si>
+  <si>
+    <t>@header_sampling_hh_systematic</t>
+  </si>
+  <si>
+    <t>@sampling_hh_systematic</t>
+  </si>
+  <si>
+    <t>Probability / Systematic random sampling</t>
+  </si>
+  <si>
+    <t>Probability / Simple random from list or map</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using simple random sampling from a list of accessible sites and households selected in the second stage using appropriate sampling techniques such as simple random sampling from community listing or maps of households. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using simple random sampling from a list of accessible sites and households selected in the second stage using systematic random sampling of households. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using simple random sampling from a list of accessible sites and households selected in the second stage using random location cluster (RLC) method. In RLC sampling, GPS points will be randomly generated over a bounded area of selected sites and an equal number of GPS points will be generated per site. Data collection teams will collect household interviews at the closest three households at each GPS point. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>placeholder systematic</t>
+  </si>
+  <si>
+    <t>placeholder systematic rlc</t>
+  </si>
+  <si>
+    <t>placeholder systematic proportional</t>
+  </si>
+  <si>
+    <t>placeholder cluster rlc</t>
+  </si>
+  <si>
+    <t>placehodler cluster</t>
+  </si>
+  <si>
+    <t>placeholder proportional</t>
+  </si>
+  <si>
+    <t>placeholder purposive</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>placeholder ind sampling</t>
+  </si>
+  <si>
+    <t>placeholder mort sampling</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -779,6 +1808,103 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF58585A"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF58585A"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF58585A"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF58585A"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -800,7 +1926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -823,6 +1949,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,24 +2275,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D357"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="47.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="19" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="80" customWidth="1"/>
+    <col min="4" max="4" width="66.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>153</v>
+      <c r="B1" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>509</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -1150,74 +2300,59 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" t="s">
-        <v>154</v>
+        <v>138</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" t="s">
-        <v>154</v>
+        <v>140</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" t="s">
-        <v>154</v>
+        <v>141</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>193</v>
+      <c r="B5" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" t="s">
-        <v>154</v>
+      <c r="B6" s="18" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" t="s">
-        <v>154</v>
+      <c r="B7" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -1225,68 +2360,65 @@
     </row>
     <row r="8" spans="1:4" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C8" t="s">
-        <v>154</v>
+        <v>147</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>162</v>
+        <v>149</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>164</v>
+        <v>188</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D13" s="12" t="b">
         <v>0</v>
@@ -1294,21 +2426,21 @@
     </row>
     <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>164</v>
+        <v>187</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D15" s="12" t="b">
         <v>0</v>
@@ -1316,21 +2448,21 @@
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>164</v>
+        <v>186</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D17" s="12" t="b">
         <v>0</v>
@@ -1338,21 +2470,21 @@
     </row>
     <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>164</v>
+        <v>189</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D19" s="12" t="b">
         <v>0</v>
@@ -1360,21 +2492,21 @@
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>164</v>
+        <v>190</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D21" s="12" t="b">
         <v>0</v>
@@ -1382,21 +2514,21 @@
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>164</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="D23" s="12" t="b">
         <v>0</v>
@@ -1404,1286 +2536,3201 @@
     </row>
     <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>193</v>
+      <c r="B25" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>193</v>
+      <c r="B27" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>162</v>
+        <v>171</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>193</v>
+      <c r="B29" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>162</v>
+        <v>173</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>162</v>
+        <v>176</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>193</v>
+        <v>13</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>162</v>
+        <v>178</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>193</v>
+        <v>14</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>162</v>
+        <v>179</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>193</v>
+        <v>15</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>162</v>
+        <v>180</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>193</v>
+        <v>16</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>162</v>
+        <v>181</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>193</v>
+        <v>17</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>162</v>
+        <v>182</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>193</v>
+        <v>18</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>162</v>
+        <v>183</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>193</v>
+        <v>19</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>162</v>
+        <v>184</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>193</v>
+        <v>20</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>162</v>
+        <v>185</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>193</v>
+        <v>21</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>162</v>
+        <v>199</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>162</v>
+        <v>200</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
+      <c r="A57" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" t="s">
-        <v>162</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>13</v>
+      <c r="A62" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" t="s">
-        <v>164</v>
-      </c>
-      <c r="D70" t="s">
-        <v>24</v>
+      <c r="A70" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>25</v>
-      </c>
-      <c r="B71" t="s">
-        <v>164</v>
-      </c>
-      <c r="D71" t="s">
-        <v>24</v>
+      <c r="A71" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>26</v>
-      </c>
-      <c r="B72" t="s">
-        <v>164</v>
-      </c>
-      <c r="D72" t="s">
-        <v>24</v>
+      <c r="A72" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>27</v>
-      </c>
-      <c r="B73" t="s">
-        <v>164</v>
-      </c>
-      <c r="D73" t="s">
-        <v>24</v>
+      <c r="A73" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>28</v>
       </c>
-      <c r="B74" t="s">
-        <v>164</v>
-      </c>
-      <c r="D74" t="s">
-        <v>24</v>
+      <c r="B74" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>29</v>
       </c>
-      <c r="B75" t="s">
-        <v>164</v>
-      </c>
-      <c r="D75" t="s">
-        <v>24</v>
+      <c r="B75" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>30</v>
       </c>
-      <c r="B76" t="s">
-        <v>164</v>
-      </c>
-      <c r="D76" t="s">
-        <v>24</v>
+      <c r="B76" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>31</v>
       </c>
-      <c r="B77" t="s">
-        <v>164</v>
-      </c>
-      <c r="D77" t="s">
-        <v>24</v>
+      <c r="B77" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>32</v>
-      </c>
-      <c r="B78" t="s">
-        <v>164</v>
-      </c>
-      <c r="D78" t="s">
-        <v>24</v>
+      <c r="A78" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>33</v>
-      </c>
-      <c r="B79" t="s">
-        <v>164</v>
-      </c>
-      <c r="D79" t="s">
-        <v>24</v>
+      <c r="A79" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>34</v>
-      </c>
-      <c r="B80" t="s">
-        <v>164</v>
-      </c>
-      <c r="D80" t="s">
-        <v>24</v>
+      <c r="A80" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>35</v>
-      </c>
-      <c r="B81" t="s">
-        <v>164</v>
-      </c>
-      <c r="D81" t="s">
-        <v>24</v>
+      <c r="A81" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>36</v>
-      </c>
-      <c r="B82" t="s">
-        <v>164</v>
-      </c>
-      <c r="D82" t="s">
-        <v>24</v>
+      <c r="A82" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>37</v>
-      </c>
-      <c r="B83" t="s">
-        <v>164</v>
-      </c>
-      <c r="D83" t="s">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>38</v>
-      </c>
-      <c r="B84" t="s">
-        <v>164</v>
-      </c>
-      <c r="D84" t="s">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" t="s">
-        <v>164</v>
-      </c>
-      <c r="D85" t="s">
-        <v>24</v>
+        <v>34</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" t="s">
-        <v>164</v>
-      </c>
-      <c r="D86" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>41</v>
-      </c>
-      <c r="B87" t="s">
-        <v>164</v>
-      </c>
-      <c r="D87" t="s">
-        <v>24</v>
+        <v>36</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>42</v>
-      </c>
-      <c r="B88" t="s">
-        <v>164</v>
-      </c>
-      <c r="D88" t="s">
-        <v>24</v>
+      <c r="A88" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>43</v>
-      </c>
-      <c r="B89" t="s">
-        <v>164</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>44</v>
-      </c>
-      <c r="B90" t="s">
-        <v>164</v>
-      </c>
-      <c r="D90" t="s">
-        <v>24</v>
+      <c r="A90" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>45</v>
-      </c>
-      <c r="B91" t="s">
-        <v>164</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>46</v>
-      </c>
-      <c r="B92" t="s">
-        <v>164</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>47</v>
-      </c>
-      <c r="B93" t="s">
-        <v>164</v>
-      </c>
-      <c r="D93" t="s">
-        <v>24</v>
+      <c r="A92" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>48</v>
-      </c>
-      <c r="B94" t="s">
-        <v>164</v>
+        <v>10</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>49</v>
-      </c>
-      <c r="B95" t="s">
-        <v>164</v>
-      </c>
-      <c r="D95" t="s">
-        <v>24</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>50</v>
-      </c>
-      <c r="B96" t="s">
-        <v>164</v>
-      </c>
-      <c r="D96" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>51</v>
-      </c>
-      <c r="B97" t="s">
-        <v>164</v>
-      </c>
-      <c r="D97" t="s">
-        <v>24</v>
+        <v>111</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>52</v>
-      </c>
-      <c r="B98" t="s">
-        <v>164</v>
-      </c>
-      <c r="D98" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>53</v>
-      </c>
-      <c r="B99" t="s">
-        <v>164</v>
-      </c>
-      <c r="D99" t="s">
-        <v>24</v>
+        <v>112</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B99" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>54</v>
-      </c>
-      <c r="B100" t="s">
-        <v>164</v>
-      </c>
-      <c r="D100" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>55</v>
-      </c>
-      <c r="B101" t="s">
-        <v>164</v>
-      </c>
-      <c r="D101" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B100" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>57</v>
-      </c>
-      <c r="D103" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>58</v>
-      </c>
-      <c r="D104" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>59</v>
-      </c>
-      <c r="D105" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>61</v>
-      </c>
-      <c r="D106" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>62</v>
-      </c>
-      <c r="D107" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>67</v>
+        <v>12</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>68</v>
+      <c r="A113" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D113" s="17" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>69</v>
+        <v>39</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>70</v>
+        <v>40</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>72</v>
+        <v>42</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>73</v>
+        <v>43</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>74</v>
-      </c>
-      <c r="D119" t="s">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>75</v>
-      </c>
-      <c r="D120" t="s">
-        <v>24</v>
+        <v>45</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>76</v>
-      </c>
-      <c r="D121" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>77</v>
-      </c>
-      <c r="D122" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>78</v>
-      </c>
-      <c r="D123" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>79</v>
-      </c>
-      <c r="D124" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>80</v>
-      </c>
-      <c r="D125" t="s">
-        <v>24</v>
+        <v>48</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="33" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>81</v>
-      </c>
-      <c r="D126" t="s">
-        <v>24</v>
-      </c>
+      <c r="A126" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D126" s="21"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>82</v>
-      </c>
-      <c r="D127" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>84</v>
-      </c>
-      <c r="D128" t="s">
-        <v>83</v>
+      <c r="A127" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D127" s="21"/>
+    </row>
+    <row r="128" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>85</v>
+        <v>50</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>87</v>
+        <v>51</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>88</v>
+      <c r="A132" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>89</v>
+      <c r="A133" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>90</v>
+        <v>53</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>92</v>
+        <v>54</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D136" s="23" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>93</v>
+      <c r="A137" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>94</v>
+      <c r="A138" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>95</v>
+      <c r="A139" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>98</v>
-      </c>
-      <c r="D142" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>99</v>
-      </c>
-      <c r="D143" t="s">
-        <v>24</v>
+      <c r="A140" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>100</v>
-      </c>
-      <c r="D144" t="s">
-        <v>24</v>
+        <v>55</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>101</v>
-      </c>
-      <c r="D145" t="s">
-        <v>24</v>
+      <c r="A145" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D145" s="24" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>102</v>
-      </c>
-      <c r="D146" t="s">
-        <v>24</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="24"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>103</v>
-      </c>
-      <c r="D147" t="s">
-        <v>24</v>
+      <c r="A147" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="24" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>104</v>
-      </c>
-      <c r="D148" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>105</v>
-      </c>
-      <c r="D149" t="s">
-        <v>24</v>
+      <c r="A149" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D149" s="24" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>106</v>
-      </c>
-      <c r="D150" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>107</v>
-      </c>
-      <c r="D151" t="s">
-        <v>24</v>
+      <c r="A151" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D151" s="24" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>108</v>
-      </c>
-      <c r="D152" t="s">
-        <v>24</v>
+        <v>68</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>109</v>
-      </c>
-      <c r="D153" t="s">
-        <v>24</v>
+      <c r="A153" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D153" s="24" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>110</v>
-      </c>
-      <c r="D154" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>111</v>
-      </c>
-      <c r="D155" t="s">
-        <v>24</v>
+        <v>69</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>112</v>
-      </c>
-      <c r="D156" t="s">
-        <v>24</v>
+      <c r="A156" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D156" s="24" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>113</v>
-      </c>
-      <c r="D157" t="s">
-        <v>24</v>
+        <v>70</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>114</v>
-      </c>
-      <c r="D158" t="s">
-        <v>24</v>
+      <c r="A158" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D158" s="24" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>115</v>
+      <c r="A159" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>116</v>
+      <c r="A160" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D160" s="24" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>118</v>
+        <v>71</v>
+      </c>
+      <c r="B161" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>119</v>
+      <c r="A163" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B163" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D163" s="14" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>120</v>
+      <c r="A164" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>121</v>
+      <c r="A165" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D165" s="14" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>122</v>
+      <c r="A166" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>123</v>
+      <c r="A167" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B167" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D167" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>124</v>
+      <c r="A168" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B168" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D168" s="24" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>125</v>
-      </c>
-      <c r="D169" t="s">
-        <v>24</v>
+        <v>72</v>
+      </c>
+      <c r="B169" s="19" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>126</v>
-      </c>
-      <c r="D170" t="s">
-        <v>24</v>
+        <v>73</v>
+      </c>
+      <c r="B170" s="19" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>128</v>
+        <v>74</v>
+      </c>
+      <c r="B171" s="19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B172" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>129</v>
+        <v>56</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>130</v>
+      <c r="A174" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B174" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D174" s="24" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>131</v>
+      <c r="A175" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B175" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s">
-        <v>145</v>
+        <v>337</v>
+      </c>
+      <c r="B176" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D176" s="24" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B177" s="2"/>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s">
-        <v>138</v>
+        <v>338</v>
+      </c>
+      <c r="B177" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s">
-        <v>143</v>
+        <v>339</v>
+      </c>
+      <c r="B178" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D178" s="24" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s">
-        <v>137</v>
+        <v>340</v>
+      </c>
+      <c r="B179" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B180" s="2"/>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s">
-        <v>139</v>
+        <v>342</v>
+      </c>
+      <c r="B180" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D180" s="25" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s">
-        <v>141</v>
+        <v>341</v>
+      </c>
+      <c r="B181" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s">
-        <v>140</v>
+        <v>343</v>
+      </c>
+      <c r="B182" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s">
-        <v>152</v>
+        <v>344</v>
+      </c>
+      <c r="B183" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>75</v>
+      </c>
+      <c r="B184" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="B185" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
+      <c r="A186" t="s">
+        <v>57</v>
+      </c>
+      <c r="B186" s="19" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="B187" s="19" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="B188" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B189" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B190" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B191" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B192" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>76</v>
+      </c>
+      <c r="B193" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B194" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>58</v>
+      </c>
+      <c r="B195" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B196" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D196" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B197" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B198" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D198" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B199" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B200" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B201" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>77</v>
+      </c>
+      <c r="B202" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B203" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D203" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>59</v>
+      </c>
+      <c r="B204" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B205" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D205" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B206" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B207" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D207" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B208" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B209" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D209" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B210" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>78</v>
+      </c>
+      <c r="B211" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B212" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D212" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>60</v>
+      </c>
+      <c r="B213" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B214" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D214" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B215" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B216" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D216" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B217" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B218" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D218" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B219" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>79</v>
+      </c>
+      <c r="B220" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B221" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D221" s="13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>380</v>
+      </c>
+      <c r="B222" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B223" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D223" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B224" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B225" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D225" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B226" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B227" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D227" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B228" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>80</v>
+      </c>
+      <c r="B229" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B230" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D230" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>61</v>
+      </c>
+      <c r="B231" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B232" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D232" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B233" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B234" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D234" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B235" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B236" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D236" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B237" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>81</v>
+      </c>
+      <c r="B238" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B239" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D239" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B240" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B241" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D241" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B242" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B243" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D243" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B244" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B245" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D245" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B246" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>82</v>
+      </c>
+      <c r="B247" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B248" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D248" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B249" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B250" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D250" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B251" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B252" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D252" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B253" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B254" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D254" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B255" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>83</v>
+      </c>
+      <c r="B256" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B257" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D257" s="26" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B258" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B259" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D259" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B260" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B261" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D261" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B262" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B263" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D263" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B264" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>424</v>
+      </c>
+      <c r="B265" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B266" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D266" s="13" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B267" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D267" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>84</v>
+      </c>
+      <c r="B268" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>85</v>
+      </c>
+      <c r="B269" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B270" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D270" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B271" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B272" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B273" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D273" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B274" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D274" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B275" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D275" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B276" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D276" s="17" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>86</v>
+      </c>
+      <c r="B277" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>87</v>
+      </c>
+      <c r="B278" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>88</v>
+      </c>
+      <c r="B279" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B280" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B281" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B282" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D282" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A283" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B283" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D283" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A284" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B284" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B285" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D285" s="10" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>445</v>
+      </c>
+      <c r="B286" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D286" s="10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B287" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A288" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B288" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D288" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A289" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B289" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D289" s="10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B290" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D290" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>89</v>
+      </c>
+      <c r="B291" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>90</v>
+      </c>
+      <c r="B292" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>91</v>
+      </c>
+      <c r="B293" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>92</v>
+      </c>
+      <c r="B294" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>93</v>
+      </c>
+      <c r="B295" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>94</v>
+      </c>
+      <c r="B296" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>95</v>
+      </c>
+      <c r="B297" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>96</v>
+      </c>
+      <c r="B298" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>97</v>
+      </c>
+      <c r="B299" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>98</v>
+      </c>
+      <c r="B300" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>99</v>
+      </c>
+      <c r="B301" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>100</v>
+      </c>
+      <c r="B302" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>101</v>
+      </c>
+      <c r="B303" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>102</v>
+      </c>
+      <c r="B304" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>103</v>
+      </c>
+      <c r="B305" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>104</v>
+      </c>
+      <c r="B306" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>105</v>
+      </c>
+      <c r="B307" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>106</v>
+      </c>
+      <c r="B308" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>107</v>
+      </c>
+      <c r="B309" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>108</v>
+      </c>
+      <c r="B310" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B311" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A312" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B312" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A313" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B313" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>109</v>
+      </c>
+      <c r="B314" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>110</v>
+      </c>
+      <c r="B315" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B316" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D316" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A317" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B317" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D317" s="27" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A318" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B318" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D318" s="27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A319" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B319" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D319" s="27" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A320" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B320" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D320" s="27" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A321" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B321" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D321" s="10" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B322" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D322" s="28" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B323" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D323" s="29" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B324" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D324" s="29" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B325" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D325" s="29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B326" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D326" s="28" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A327" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B327" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D327" s="29" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A328" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B328" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D328" s="29" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B329" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D329" s="29" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B330" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D330" s="28" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A331" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B331" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D331" s="29" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A332" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B332" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D332" s="29" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A333" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B333" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D333" s="29" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A334" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B334" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D334" s="29" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A335" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B335" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D335" s="29" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A336" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B336" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D336" s="29" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A337" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B337" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D337" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B338" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D338" s="29" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B339" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D339" s="29" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B340" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D340" s="29" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B341" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D341" s="29" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>113</v>
+      </c>
+      <c r="B342" s="19" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>114</v>
+      </c>
+      <c r="B343" s="19" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>115</v>
+      </c>
+      <c r="B344" s="19" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B345" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C345" s="2"/>
+      <c r="D345" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B346" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C346" s="2"/>
+      <c r="D346" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B347" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C347" s="2"/>
+      <c r="D347" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B348" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C348" s="2"/>
+      <c r="D348" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B349" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C349" s="2"/>
+      <c r="D349" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B350" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C350" s="2"/>
+      <c r="D350" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B351" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C351" s="2"/>
+      <c r="D351" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B352" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C352" s="2"/>
+      <c r="D352" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B353" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="C353" s="2"/>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B354" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C354" s="2"/>
+      <c r="D354" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B355" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="C355" s="2"/>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B356" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C356" s="2"/>
+      <c r="D356" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B357" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="C357" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF81DB17-EAB8-4C26-A021-819798752877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A846EC-9121-46FE-A0A2-7DA4E4F5ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7080" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -1218,9 +1218,6 @@
     <t>@header_tool_kii_nutrition</t>
   </si>
   <si>
-    <t>@kii_nutrition_inc</t>
-  </si>
-  <si>
     <t>@header_sampling_kii_nutrition_purposive</t>
   </si>
   <si>
@@ -1748,6 +1745,9 @@
   </si>
   <si>
     <t>placeholder mort sampling</t>
+  </si>
+  <si>
+    <t>@kii_nut_inc</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1956,8 +1956,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2279,7 +2277,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="66.5703125" customWidth="1"/>
   </cols>
@@ -2292,7 +2290,7 @@
         <v>137</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -2865,7 +2863,7 @@
       <c r="A57" t="s">
         <v>23</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2873,7 +2871,7 @@
       <c r="A58" t="s">
         <v>24</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2881,7 +2879,7 @@
       <c r="A59" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2889,7 +2887,7 @@
       <c r="A60" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2897,7 +2895,7 @@
       <c r="A61" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3022,7 +3020,7 @@
       <c r="A74" t="s">
         <v>28</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3030,7 +3028,7 @@
       <c r="A75" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="B75" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3038,7 +3036,7 @@
       <c r="A76" t="s">
         <v>30</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3046,7 +3044,7 @@
       <c r="A77" t="s">
         <v>31</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B77" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3109,7 +3107,7 @@
       <c r="A83" t="s">
         <v>32</v>
       </c>
-      <c r="B83" s="19" t="s">
+      <c r="B83" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3117,7 +3115,7 @@
       <c r="A84" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3125,7 +3123,7 @@
       <c r="A85" t="s">
         <v>34</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3133,7 +3131,7 @@
       <c r="A86" t="s">
         <v>35</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3141,7 +3139,7 @@
       <c r="A87" t="s">
         <v>36</v>
       </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3160,7 +3158,7 @@
       <c r="A89" t="s">
         <v>37</v>
       </c>
-      <c r="B89" s="19" t="s">
+      <c r="B89" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3179,7 +3177,7 @@
       <c r="A91" t="s">
         <v>38</v>
       </c>
-      <c r="B91" s="19" t="s">
+      <c r="B91" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3417,7 +3415,7 @@
       <c r="A114" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="19" t="s">
+      <c r="B114" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3425,7 +3423,7 @@
       <c r="A115" t="s">
         <v>40</v>
       </c>
-      <c r="B115" s="19" t="s">
+      <c r="B115" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3433,7 +3431,7 @@
       <c r="A116" t="s">
         <v>41</v>
       </c>
-      <c r="B116" s="19" t="s">
+      <c r="B116" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3441,7 +3439,7 @@
       <c r="A117" t="s">
         <v>42</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3449,7 +3447,7 @@
       <c r="A118" t="s">
         <v>43</v>
       </c>
-      <c r="B118" s="19" t="s">
+      <c r="B118" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3457,7 +3455,7 @@
       <c r="A119" t="s">
         <v>44</v>
       </c>
-      <c r="B119" s="19" t="s">
+      <c r="B119" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3465,7 +3463,7 @@
       <c r="A120" t="s">
         <v>45</v>
       </c>
-      <c r="B120" s="19" t="s">
+      <c r="B120" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3473,7 +3471,7 @@
       <c r="A121" t="s">
         <v>46</v>
       </c>
-      <c r="B121" s="19" t="s">
+      <c r="B121" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3481,7 +3479,7 @@
       <c r="A122" t="s">
         <v>47</v>
       </c>
-      <c r="B122" s="19" t="s">
+      <c r="B122" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3489,7 +3487,7 @@
       <c r="A123" t="s">
         <v>48</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3497,10 +3495,10 @@
       <c r="A124" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B124" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D124" s="22" t="s">
+      <c r="B124" t="s">
+        <v>144</v>
+      </c>
+      <c r="D124" s="20" t="s">
         <v>284</v>
       </c>
     </row>
@@ -3508,7 +3506,7 @@
       <c r="A125" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B125" s="19" t="s">
+      <c r="B125" t="s">
         <v>144</v>
       </c>
       <c r="D125" s="10" t="s">
@@ -3519,25 +3517,25 @@
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D126" s="21"/>
+      <c r="B126" t="s">
+        <v>146</v>
+      </c>
+      <c r="D126" s="19"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B127" s="19" t="s">
+      <c r="B127" t="s">
         <v>145</v>
       </c>
-      <c r="D127" s="21"/>
+      <c r="D127" s="19"/>
     </row>
     <row r="128" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B128" s="19" t="s">
+      <c r="B128" t="s">
         <v>144</v>
       </c>
       <c r="D128" s="10" t="s">
@@ -3548,7 +3546,7 @@
       <c r="A129" t="s">
         <v>50</v>
       </c>
-      <c r="B129" s="19" t="s">
+      <c r="B129" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3556,7 +3554,7 @@
       <c r="A130" t="s">
         <v>51</v>
       </c>
-      <c r="B130" s="19" t="s">
+      <c r="B130" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3564,7 +3562,7 @@
       <c r="A131" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" t="s">
         <v>144</v>
       </c>
       <c r="D131" s="10" t="s">
@@ -3575,7 +3573,7 @@
       <c r="A132" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B132" s="19" t="s">
+      <c r="B132" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3583,7 +3581,7 @@
       <c r="A133" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B133" s="19" t="s">
+      <c r="B133" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3591,7 +3589,7 @@
       <c r="A134" t="s">
         <v>53</v>
       </c>
-      <c r="B134" s="19" t="s">
+      <c r="B134" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3599,7 +3597,7 @@
       <c r="A135" t="s">
         <v>54</v>
       </c>
-      <c r="B135" s="19" t="s">
+      <c r="B135" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3607,10 +3605,10 @@
       <c r="A136" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B136" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D136" s="23" t="s">
+      <c r="B136" t="s">
+        <v>144</v>
+      </c>
+      <c r="D136" s="21" t="s">
         <v>290</v>
       </c>
     </row>
@@ -3618,7 +3616,7 @@
       <c r="A137" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B137" s="19" t="s">
+      <c r="B137" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3626,7 +3624,7 @@
       <c r="A138" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B138" s="19" t="s">
+      <c r="B138" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3634,7 +3632,7 @@
       <c r="A139" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B139" s="19" t="s">
+      <c r="B139" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3642,7 +3640,7 @@
       <c r="A140" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B140" s="19" t="s">
+      <c r="B140" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3650,7 +3648,7 @@
       <c r="A141" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B141" s="19" t="s">
+      <c r="B141" t="s">
         <v>144</v>
       </c>
       <c r="D141" s="7" t="s">
@@ -3661,7 +3659,7 @@
       <c r="A142" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B142" s="19" t="s">
+      <c r="B142" t="s">
         <v>144</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -3672,7 +3670,7 @@
       <c r="A143" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" t="s">
         <v>144</v>
       </c>
       <c r="D143" s="13" t="s">
@@ -3683,7 +3681,7 @@
       <c r="A144" t="s">
         <v>55</v>
       </c>
-      <c r="B144" s="19" t="s">
+      <c r="B144" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3691,10 +3689,10 @@
       <c r="A145" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B145" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D145" s="24" t="s">
+      <c r="B145" t="s">
+        <v>144</v>
+      </c>
+      <c r="D145" s="22" t="s">
         <v>315</v>
       </c>
     </row>
@@ -3702,19 +3700,19 @@
       <c r="A146" t="s">
         <v>65</v>
       </c>
-      <c r="B146" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D146" s="24"/>
+      <c r="B146" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="22"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B147" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D147" s="24" t="s">
+      <c r="B147" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="22" t="s">
         <v>314</v>
       </c>
     </row>
@@ -3722,7 +3720,7 @@
       <c r="A148" t="s">
         <v>66</v>
       </c>
-      <c r="B148" s="19" t="s">
+      <c r="B148" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3730,10 +3728,10 @@
       <c r="A149" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B149" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D149" s="24" t="s">
+      <c r="B149" t="s">
+        <v>144</v>
+      </c>
+      <c r="D149" s="22" t="s">
         <v>316</v>
       </c>
     </row>
@@ -3741,7 +3739,7 @@
       <c r="A150" t="s">
         <v>67</v>
       </c>
-      <c r="B150" s="19" t="s">
+      <c r="B150" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3749,10 +3747,10 @@
       <c r="A151" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B151" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D151" s="24" t="s">
+      <c r="B151" t="s">
+        <v>144</v>
+      </c>
+      <c r="D151" s="22" t="s">
         <v>317</v>
       </c>
     </row>
@@ -3760,7 +3758,7 @@
       <c r="A152" t="s">
         <v>68</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3768,10 +3766,10 @@
       <c r="A153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B153" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D153" s="24" t="s">
+      <c r="B153" t="s">
+        <v>144</v>
+      </c>
+      <c r="D153" s="22" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3779,7 +3777,7 @@
       <c r="A154" t="s">
         <v>69</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B154" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3787,7 +3785,7 @@
       <c r="A155" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B155" s="19" t="s">
+      <c r="B155" t="s">
         <v>144</v>
       </c>
       <c r="D155" s="7" t="s">
@@ -3798,37 +3796,37 @@
       <c r="A156" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B156" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D156" s="24" t="s">
-        <v>515</v>
+      <c r="B156" t="s">
+        <v>144</v>
+      </c>
+      <c r="D156" s="22" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>70</v>
       </c>
-      <c r="B157" s="19" t="s">
+      <c r="B157" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="B158" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D158" s="24" t="s">
-        <v>514</v>
+        <v>511</v>
+      </c>
+      <c r="B158" t="s">
+        <v>144</v>
+      </c>
+      <c r="D158" s="22" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="B159" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="B159" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3836,10 +3834,10 @@
       <c r="A160" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B160" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D160" s="24" t="s">
+      <c r="B160" t="s">
+        <v>144</v>
+      </c>
+      <c r="D160" s="22" t="s">
         <v>319</v>
       </c>
     </row>
@@ -3847,7 +3845,7 @@
       <c r="A161" t="s">
         <v>71</v>
       </c>
-      <c r="B161" s="19" t="s">
+      <c r="B161" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3855,7 +3853,7 @@
       <c r="A162" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B162" s="19" t="s">
+      <c r="B162" t="s">
         <v>144</v>
       </c>
       <c r="D162" s="10" t="s">
@@ -3866,7 +3864,7 @@
       <c r="A163" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B163" s="19" t="s">
+      <c r="B163" t="s">
         <v>144</v>
       </c>
       <c r="D163" s="14" t="s">
@@ -3877,7 +3875,7 @@
       <c r="A164" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B164" s="19" t="s">
+      <c r="B164" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3885,7 +3883,7 @@
       <c r="A165" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B165" s="19" t="s">
+      <c r="B165" t="s">
         <v>144</v>
       </c>
       <c r="D165" s="14" t="s">
@@ -3896,7 +3894,7 @@
       <c r="A166" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B166" s="19" t="s">
+      <c r="B166" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3904,7 +3902,7 @@
       <c r="A167" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="19" t="s">
+      <c r="B167" t="s">
         <v>144</v>
       </c>
       <c r="D167" t="s">
@@ -3915,10 +3913,10 @@
       <c r="A168" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B168" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D168" s="24" t="s">
+      <c r="B168" t="s">
+        <v>144</v>
+      </c>
+      <c r="D168" s="22" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3926,7 +3924,7 @@
       <c r="A169" t="s">
         <v>72</v>
       </c>
-      <c r="B169" s="19" t="s">
+      <c r="B169" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3934,7 +3932,7 @@
       <c r="A170" t="s">
         <v>73</v>
       </c>
-      <c r="B170" s="19" t="s">
+      <c r="B170" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3942,7 +3940,7 @@
       <c r="A171" t="s">
         <v>74</v>
       </c>
-      <c r="B171" s="19" t="s">
+      <c r="B171" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3950,7 +3948,7 @@
       <c r="A172" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B172" s="19" t="s">
+      <c r="B172" t="s">
         <v>144</v>
       </c>
       <c r="D172" s="13" t="s">
@@ -3961,7 +3959,7 @@
       <c r="A173" t="s">
         <v>56</v>
       </c>
-      <c r="B173" s="19" t="s">
+      <c r="B173" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3969,10 +3967,10 @@
       <c r="A174" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B174" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D174" s="24" t="s">
+      <c r="B174" t="s">
+        <v>144</v>
+      </c>
+      <c r="D174" s="22" t="s">
         <v>332</v>
       </c>
     </row>
@@ -3980,7 +3978,7 @@
       <c r="A175" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B175" s="19" t="s">
+      <c r="B175" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3988,10 +3986,10 @@
       <c r="A176" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B176" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D176" s="24" t="s">
+      <c r="B176" t="s">
+        <v>144</v>
+      </c>
+      <c r="D176" s="22" t="s">
         <v>333</v>
       </c>
     </row>
@@ -3999,7 +3997,7 @@
       <c r="A177" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B177" s="19" t="s">
+      <c r="B177" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4007,10 +4005,10 @@
       <c r="A178" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B178" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D178" s="24" t="s">
+      <c r="B178" t="s">
+        <v>144</v>
+      </c>
+      <c r="D178" s="22" t="s">
         <v>334</v>
       </c>
     </row>
@@ -4018,7 +4016,7 @@
       <c r="A179" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B179" s="19" t="s">
+      <c r="B179" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4026,10 +4024,10 @@
       <c r="A180" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B180" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D180" s="25" t="s">
+      <c r="B180" t="s">
+        <v>144</v>
+      </c>
+      <c r="D180" s="23" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4037,7 +4035,7 @@
       <c r="A181" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B181" s="19" t="s">
+      <c r="B181" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4045,7 +4043,7 @@
       <c r="A182" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B182" s="19" t="s">
+      <c r="B182" t="s">
         <v>144</v>
       </c>
       <c r="D182" s="14" t="s">
@@ -4056,7 +4054,7 @@
       <c r="A183" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B183" s="19" t="s">
+      <c r="B183" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4064,7 +4062,7 @@
       <c r="A184" t="s">
         <v>75</v>
       </c>
-      <c r="B184" s="19" t="s">
+      <c r="B184" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4072,7 +4070,7 @@
       <c r="A185" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B185" s="19" t="s">
+      <c r="B185" t="s">
         <v>144</v>
       </c>
       <c r="D185" s="13" t="s">
@@ -4083,7 +4081,7 @@
       <c r="A186" t="s">
         <v>57</v>
       </c>
-      <c r="B186" s="19" t="s">
+      <c r="B186" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4091,7 +4089,7 @@
       <c r="A187" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B187" s="19" t="s">
+      <c r="B187" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4099,7 +4097,7 @@
       <c r="A188" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B188" s="19" t="s">
+      <c r="B188" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4107,7 +4105,7 @@
       <c r="A189" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B189" s="19" t="s">
+      <c r="B189" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4115,7 +4113,7 @@
       <c r="A190" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B190" s="19" t="s">
+      <c r="B190" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4123,7 +4121,7 @@
       <c r="A191" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B191" s="19" t="s">
+      <c r="B191" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4131,7 +4129,7 @@
       <c r="A192" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B192" s="19" t="s">
+      <c r="B192" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4139,7 +4137,7 @@
       <c r="A193" t="s">
         <v>76</v>
       </c>
-      <c r="B193" s="19" t="s">
+      <c r="B193" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4147,7 +4145,7 @@
       <c r="A194" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B194" s="19" t="s">
+      <c r="B194" t="s">
         <v>144</v>
       </c>
       <c r="D194" s="13" t="s">
@@ -4158,7 +4156,7 @@
       <c r="A195" t="s">
         <v>58</v>
       </c>
-      <c r="B195" s="19" t="s">
+      <c r="B195" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4166,10 +4164,10 @@
       <c r="A196" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B196" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D196" s="24" t="s">
+      <c r="B196" t="s">
+        <v>144</v>
+      </c>
+      <c r="D196" s="22" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4177,7 +4175,7 @@
       <c r="A197" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B197" s="19" t="s">
+      <c r="B197" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4185,10 +4183,10 @@
       <c r="A198" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B198" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D198" s="25" t="s">
+      <c r="B198" t="s">
+        <v>144</v>
+      </c>
+      <c r="D198" s="23" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4196,7 +4194,7 @@
       <c r="A199" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B199" s="19" t="s">
+      <c r="B199" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4204,7 +4202,7 @@
       <c r="A200" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B200" s="19" t="s">
+      <c r="B200" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4212,7 +4210,7 @@
       <c r="A201" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B201" s="19" t="s">
+      <c r="B201" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4220,7 +4218,7 @@
       <c r="A202" t="s">
         <v>77</v>
       </c>
-      <c r="B202" s="19" t="s">
+      <c r="B202" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4228,7 +4226,7 @@
       <c r="A203" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B203" s="19" t="s">
+      <c r="B203" t="s">
         <v>144</v>
       </c>
       <c r="D203" s="13" t="s">
@@ -4239,7 +4237,7 @@
       <c r="A204" t="s">
         <v>59</v>
       </c>
-      <c r="B204" s="19" t="s">
+      <c r="B204" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4247,10 +4245,10 @@
       <c r="A205" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B205" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D205" s="24" t="s">
+      <c r="B205" t="s">
+        <v>144</v>
+      </c>
+      <c r="D205" s="22" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4258,7 +4256,7 @@
       <c r="A206" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B206" s="19" t="s">
+      <c r="B206" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4266,10 +4264,10 @@
       <c r="A207" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B207" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D207" s="25" t="s">
+      <c r="B207" t="s">
+        <v>144</v>
+      </c>
+      <c r="D207" s="23" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4277,7 +4275,7 @@
       <c r="A208" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B208" s="19" t="s">
+      <c r="B208" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4285,7 +4283,7 @@
       <c r="A209" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B209" s="19" t="s">
+      <c r="B209" t="s">
         <v>144</v>
       </c>
       <c r="D209" s="14" t="s">
@@ -4296,7 +4294,7 @@
       <c r="A210" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B210" s="19" t="s">
+      <c r="B210" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4304,7 +4302,7 @@
       <c r="A211" t="s">
         <v>78</v>
       </c>
-      <c r="B211" s="19" t="s">
+      <c r="B211" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4312,7 +4310,7 @@
       <c r="A212" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B212" s="19" t="s">
+      <c r="B212" t="s">
         <v>144</v>
       </c>
       <c r="D212" s="13" t="s">
@@ -4323,7 +4321,7 @@
       <c r="A213" t="s">
         <v>60</v>
       </c>
-      <c r="B213" s="19" t="s">
+      <c r="B213" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4331,10 +4329,10 @@
       <c r="A214" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B214" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D214" s="24" t="s">
+      <c r="B214" t="s">
+        <v>144</v>
+      </c>
+      <c r="D214" s="22" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4342,7 +4340,7 @@
       <c r="A215" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B215" s="19" t="s">
+      <c r="B215" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4350,10 +4348,10 @@
       <c r="A216" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B216" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D216" s="25" t="s">
+      <c r="B216" t="s">
+        <v>144</v>
+      </c>
+      <c r="D216" s="23" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4361,7 +4359,7 @@
       <c r="A217" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B217" s="19" t="s">
+      <c r="B217" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4369,7 +4367,7 @@
       <c r="A218" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B218" s="19" t="s">
+      <c r="B218" t="s">
         <v>144</v>
       </c>
       <c r="D218" s="14" t="s">
@@ -4380,7 +4378,7 @@
       <c r="A219" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B219" s="19" t="s">
+      <c r="B219" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4388,7 +4386,7 @@
       <c r="A220" t="s">
         <v>79</v>
       </c>
-      <c r="B220" s="19" t="s">
+      <c r="B220" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4396,64 +4394,64 @@
       <c r="A221" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B221" s="19" t="s">
+      <c r="B221" t="s">
         <v>144</v>
       </c>
       <c r="D221" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>380</v>
-      </c>
-      <c r="B222" s="19" t="s">
+      <c r="A222" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B222" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B223" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D223" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="B223" t="s">
+        <v>144</v>
+      </c>
+      <c r="D223" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B224" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B224" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B225" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D225" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="B225" t="s">
+        <v>144</v>
+      </c>
+      <c r="D225" s="23" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B226" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B226" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B227" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B227" t="s">
         <v>144</v>
       </c>
       <c r="D227" s="14" t="s">
@@ -4462,9 +4460,9 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B228" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="B228" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4472,83 +4470,83 @@
       <c r="A229" t="s">
         <v>80</v>
       </c>
-      <c r="B229" s="19" t="s">
+      <c r="B229" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B230" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B230" t="s">
         <v>144</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>61</v>
       </c>
-      <c r="B231" s="19" t="s">
+      <c r="B231" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B232" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D232" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="B232" t="s">
+        <v>144</v>
+      </c>
+      <c r="D232" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B233" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B233" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B234" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D234" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="B234" t="s">
+        <v>144</v>
+      </c>
+      <c r="D234" s="23" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B235" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="B235" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B236" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B236" t="s">
         <v>144</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B237" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B237" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4556,83 +4554,83 @@
       <c r="A238" t="s">
         <v>81</v>
       </c>
-      <c r="B238" s="19" t="s">
+      <c r="B238" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B239" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="B239" t="s">
         <v>144</v>
       </c>
       <c r="D239" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B240" s="19" t="s">
+      <c r="B240" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B241" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D241" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="B241" t="s">
+        <v>144</v>
+      </c>
+      <c r="D241" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B242" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="B242" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B243" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D243" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="B243" t="s">
+        <v>144</v>
+      </c>
+      <c r="D243" s="23" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B244" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="B244" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B245" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="B245" t="s">
         <v>144</v>
       </c>
       <c r="D245" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="B246" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="B246" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4640,83 +4638,83 @@
       <c r="A247" t="s">
         <v>82</v>
       </c>
-      <c r="B247" s="19" t="s">
+      <c r="B247" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B248" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="B248" t="s">
         <v>144</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B249" s="19" t="s">
+      <c r="B249" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B250" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D250" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="B250" t="s">
+        <v>144</v>
+      </c>
+      <c r="D250" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B251" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="B251" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B252" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D252" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="B252" t="s">
+        <v>144</v>
+      </c>
+      <c r="D252" s="23" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B253" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="B253" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B254" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="B254" t="s">
         <v>144</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B255" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="B255" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4724,121 +4722,121 @@
       <c r="A256" t="s">
         <v>83</v>
       </c>
-      <c r="B256" s="19" t="s">
+      <c r="B256" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B257" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D257" s="26" t="s">
         <v>416</v>
+      </c>
+      <c r="B257" t="s">
+        <v>144</v>
+      </c>
+      <c r="D257" s="24" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B258" s="19" t="s">
+      <c r="B258" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B259" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D259" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="B259" t="s">
+        <v>144</v>
+      </c>
+      <c r="D259" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B260" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="B260" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B261" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D261" s="25" t="s">
+        <v>419</v>
+      </c>
+      <c r="B261" t="s">
+        <v>144</v>
+      </c>
+      <c r="D261" s="23" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="B262" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="B262" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B263" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="B263" t="s">
         <v>144</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B264" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B264" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>424</v>
-      </c>
-      <c r="B265" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="B265" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B266" t="s">
+        <v>144</v>
+      </c>
+      <c r="D266" s="13" t="s">
         <v>429</v>
-      </c>
-      <c r="B266" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D266" s="13" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B267" t="s">
+        <v>144</v>
+      </c>
+      <c r="D267" t="s">
         <v>425</v>
-      </c>
-      <c r="B267" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D267" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>84</v>
       </c>
-      <c r="B268" s="19" t="s">
+      <c r="B268" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4846,75 +4844,75 @@
       <c r="A269" t="s">
         <v>85</v>
       </c>
-      <c r="B269" s="19" t="s">
+      <c r="B269" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B270" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B270" t="s">
         <v>144</v>
       </c>
       <c r="D270" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B271" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="B271" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B272" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="B272" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B273" t="s">
+        <v>144</v>
+      </c>
+      <c r="D273" t="s">
         <v>436</v>
-      </c>
-      <c r="B273" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D273" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="B274" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="B274" t="s">
         <v>144</v>
       </c>
       <c r="D274" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B275" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="B275" t="s">
         <v>144</v>
       </c>
       <c r="D275" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B276" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B276" t="s">
         <v>144</v>
       </c>
       <c r="D276" s="17" t="s">
@@ -4925,7 +4923,7 @@
       <c r="A277" t="s">
         <v>86</v>
       </c>
-      <c r="B277" s="19" t="s">
+      <c r="B277" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4933,7 +4931,7 @@
       <c r="A278" t="s">
         <v>87</v>
       </c>
-      <c r="B278" s="19" t="s">
+      <c r="B278" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4941,136 +4939,136 @@
       <c r="A279" t="s">
         <v>88</v>
       </c>
-      <c r="B279" s="19" t="s">
+      <c r="B279" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B280" t="s">
+        <v>144</v>
+      </c>
+      <c r="D280" s="7" t="s">
         <v>438</v>
-      </c>
-      <c r="B280" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D280" s="7" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B281" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="B281" t="s">
         <v>144</v>
       </c>
       <c r="D281" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B282" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="B282" t="s">
         <v>144</v>
       </c>
       <c r="D282" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="B283" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="B283" t="s">
         <v>144</v>
       </c>
       <c r="D283" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B284" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B284" t="s">
         <v>144</v>
       </c>
       <c r="D284" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B285" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="B285" t="s">
         <v>144</v>
       </c>
       <c r="D285" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>445</v>
-      </c>
-      <c r="B286" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="B286" t="s">
         <v>144</v>
       </c>
       <c r="D286" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B287" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="B287" t="s">
         <v>144</v>
       </c>
       <c r="D287" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B288" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="B288" t="s">
         <v>144</v>
       </c>
       <c r="D288" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B289" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B289" t="s">
         <v>144</v>
       </c>
       <c r="D289" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="B290" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="B290" t="s">
         <v>144</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>89</v>
       </c>
-      <c r="B291" s="19" t="s">
+      <c r="B291" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5078,7 +5076,7 @@
       <c r="A292" t="s">
         <v>90</v>
       </c>
-      <c r="B292" s="19" t="s">
+      <c r="B292" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5086,7 +5084,7 @@
       <c r="A293" t="s">
         <v>91</v>
       </c>
-      <c r="B293" s="19" t="s">
+      <c r="B293" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5094,7 +5092,7 @@
       <c r="A294" t="s">
         <v>92</v>
       </c>
-      <c r="B294" s="19" t="s">
+      <c r="B294" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5102,7 +5100,7 @@
       <c r="A295" t="s">
         <v>93</v>
       </c>
-      <c r="B295" s="19" t="s">
+      <c r="B295" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5110,7 +5108,7 @@
       <c r="A296" t="s">
         <v>94</v>
       </c>
-      <c r="B296" s="19" t="s">
+      <c r="B296" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5118,7 +5116,7 @@
       <c r="A297" t="s">
         <v>95</v>
       </c>
-      <c r="B297" s="19" t="s">
+      <c r="B297" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5126,7 +5124,7 @@
       <c r="A298" t="s">
         <v>96</v>
       </c>
-      <c r="B298" s="19" t="s">
+      <c r="B298" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5134,7 +5132,7 @@
       <c r="A299" t="s">
         <v>97</v>
       </c>
-      <c r="B299" s="19" t="s">
+      <c r="B299" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5142,7 +5140,7 @@
       <c r="A300" t="s">
         <v>98</v>
       </c>
-      <c r="B300" s="19" t="s">
+      <c r="B300" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5150,7 +5148,7 @@
       <c r="A301" t="s">
         <v>99</v>
       </c>
-      <c r="B301" s="19" t="s">
+      <c r="B301" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5158,7 +5156,7 @@
       <c r="A302" t="s">
         <v>100</v>
       </c>
-      <c r="B302" s="19" t="s">
+      <c r="B302" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5166,7 +5164,7 @@
       <c r="A303" t="s">
         <v>101</v>
       </c>
-      <c r="B303" s="19" t="s">
+      <c r="B303" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5174,7 +5172,7 @@
       <c r="A304" t="s">
         <v>102</v>
       </c>
-      <c r="B304" s="19" t="s">
+      <c r="B304" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5182,7 +5180,7 @@
       <c r="A305" t="s">
         <v>103</v>
       </c>
-      <c r="B305" s="19" t="s">
+      <c r="B305" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5190,7 +5188,7 @@
       <c r="A306" t="s">
         <v>104</v>
       </c>
-      <c r="B306" s="19" t="s">
+      <c r="B306" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5198,7 +5196,7 @@
       <c r="A307" t="s">
         <v>105</v>
       </c>
-      <c r="B307" s="19" t="s">
+      <c r="B307" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5206,7 +5204,7 @@
       <c r="A308" t="s">
         <v>106</v>
       </c>
-      <c r="B308" s="19" t="s">
+      <c r="B308" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5214,7 +5212,7 @@
       <c r="A309" t="s">
         <v>107</v>
       </c>
-      <c r="B309" s="19" t="s">
+      <c r="B309" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5222,48 +5220,48 @@
       <c r="A310" t="s">
         <v>108</v>
       </c>
-      <c r="B310" s="19" t="s">
+      <c r="B310" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B311" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="B311" t="s">
         <v>144</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="B312" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="B312" t="s">
         <v>144</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B313" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="B313" t="s">
         <v>144</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>109</v>
       </c>
-      <c r="B314" s="19" t="s">
+      <c r="B314" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5271,325 +5269,325 @@
       <c r="A315" t="s">
         <v>110</v>
       </c>
-      <c r="B315" s="19" t="s">
+      <c r="B315" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B316" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="B316" t="s">
         <v>144</v>
       </c>
       <c r="D316" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B317" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D317" s="27" t="s">
-        <v>474</v>
+        <v>468</v>
+      </c>
+      <c r="B317" t="s">
+        <v>144</v>
+      </c>
+      <c r="D317" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B318" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D318" s="27" t="s">
-        <v>475</v>
+        <v>469</v>
+      </c>
+      <c r="B318" t="s">
+        <v>144</v>
+      </c>
+      <c r="D318" s="25" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B319" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D319" s="27" t="s">
-        <v>476</v>
+        <v>470</v>
+      </c>
+      <c r="B319" t="s">
+        <v>144</v>
+      </c>
+      <c r="D319" s="25" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B320" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D320" s="27" t="s">
-        <v>477</v>
+        <v>471</v>
+      </c>
+      <c r="B320" t="s">
+        <v>144</v>
+      </c>
+      <c r="D320" s="25" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B321" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="B321" t="s">
         <v>144</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B322" t="s">
+        <v>144</v>
+      </c>
+      <c r="D322" s="26" t="s">
         <v>480</v>
-      </c>
-      <c r="B322" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D322" s="28" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B323" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D323" s="29" t="s">
         <v>482</v>
+      </c>
+      <c r="B323" t="s">
+        <v>144</v>
+      </c>
+      <c r="D323" s="27" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B324" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D324" s="29" t="s">
-        <v>486</v>
+        <v>483</v>
+      </c>
+      <c r="B324" t="s">
+        <v>144</v>
+      </c>
+      <c r="D324" s="27" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B325" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D325" s="29" t="s">
-        <v>487</v>
+        <v>484</v>
+      </c>
+      <c r="B325" t="s">
+        <v>144</v>
+      </c>
+      <c r="D325" s="27" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B326" t="s">
+        <v>144</v>
+      </c>
+      <c r="D326" s="26" t="s">
         <v>488</v>
-      </c>
-      <c r="B326" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D326" s="28" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B327" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D327" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
+      </c>
+      <c r="B327" t="s">
+        <v>144</v>
+      </c>
+      <c r="D327" s="27" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B328" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D328" s="29" t="s">
-        <v>491</v>
+        <v>492</v>
+      </c>
+      <c r="B328" t="s">
+        <v>144</v>
+      </c>
+      <c r="D328" s="27" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B329" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D329" s="29" t="s">
-        <v>497</v>
+        <v>493</v>
+      </c>
+      <c r="B329" t="s">
+        <v>144</v>
+      </c>
+      <c r="D329" s="27" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B330" t="s">
+        <v>144</v>
+      </c>
+      <c r="D330" s="26" t="s">
         <v>495</v>
-      </c>
-      <c r="B330" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D330" s="28" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B331" t="s">
+        <v>144</v>
+      </c>
+      <c r="D331" s="27" t="s">
         <v>498</v>
-      </c>
-      <c r="B331" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D331" s="29" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B332" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D332" s="29" t="s">
-        <v>516</v>
+        <v>509</v>
+      </c>
+      <c r="B332" t="s">
+        <v>507</v>
+      </c>
+      <c r="D332" s="27" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B333" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D333" s="29" t="s">
-        <v>517</v>
+        <v>510</v>
+      </c>
+      <c r="B333" t="s">
+        <v>507</v>
+      </c>
+      <c r="D333" s="27" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B334" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D334" s="29" t="s">
-        <v>518</v>
+        <v>503</v>
+      </c>
+      <c r="B334" t="s">
+        <v>507</v>
+      </c>
+      <c r="D334" s="27" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B335" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D335" s="29" t="s">
-        <v>519</v>
+        <v>499</v>
+      </c>
+      <c r="B335" t="s">
+        <v>507</v>
+      </c>
+      <c r="D335" s="27" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B336" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D336" s="29" t="s">
-        <v>520</v>
+        <v>504</v>
+      </c>
+      <c r="B336" t="s">
+        <v>507</v>
+      </c>
+      <c r="D336" s="27" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B337" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D337" s="29" t="s">
-        <v>521</v>
+        <v>505</v>
+      </c>
+      <c r="B337" t="s">
+        <v>507</v>
+      </c>
+      <c r="D337" s="27" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B338" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D338" s="29" t="s">
-        <v>522</v>
+        <v>500</v>
+      </c>
+      <c r="B338" t="s">
+        <v>507</v>
+      </c>
+      <c r="D338" s="27" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B339" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D339" s="29" t="s">
-        <v>523</v>
+        <v>501</v>
+      </c>
+      <c r="B339" t="s">
+        <v>507</v>
+      </c>
+      <c r="D339" s="27" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B340" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D340" s="29" t="s">
-        <v>524</v>
+        <v>502</v>
+      </c>
+      <c r="B340" t="s">
+        <v>507</v>
+      </c>
+      <c r="D340" s="27" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B341" t="s">
         <v>507</v>
       </c>
-      <c r="B341" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="D341" s="29" t="s">
-        <v>525</v>
+      <c r="D341" s="27" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>113</v>
       </c>
-      <c r="B342" s="19" t="s">
-        <v>526</v>
+      <c r="B342" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>114</v>
       </c>
-      <c r="B343" s="19" t="s">
-        <v>527</v>
+      <c r="B343" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>115</v>
       </c>
-      <c r="B344" s="19" t="s">
-        <v>526</v>
+      <c r="B344" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B345" s="20" t="s">
+      <c r="B345" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C345" s="2"/>
@@ -5601,7 +5599,7 @@
       <c r="A346" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B346" s="20" t="s">
+      <c r="B346" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C346" s="2"/>
@@ -5613,7 +5611,7 @@
       <c r="A347" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B347" s="20" t="s">
+      <c r="B347" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C347" s="2"/>
@@ -5625,7 +5623,7 @@
       <c r="A348" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B348" s="20" t="s">
+      <c r="B348" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C348" s="2"/>
@@ -5637,7 +5635,7 @@
       <c r="A349" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B349" s="20" t="s">
+      <c r="B349" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C349" s="2"/>
@@ -5649,7 +5647,7 @@
       <c r="A350" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B350" s="20" t="s">
+      <c r="B350" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C350" s="2"/>
@@ -5661,7 +5659,7 @@
       <c r="A351" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B351" s="20" t="s">
+      <c r="B351" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C351" s="2"/>
@@ -5673,7 +5671,7 @@
       <c r="A352" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B352" s="20" t="s">
+      <c r="B352" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C352" s="2"/>
@@ -5685,8 +5683,8 @@
       <c r="A353" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B353" s="20" t="s">
-        <v>526</v>
+      <c r="B353" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="C353" s="2"/>
     </row>
@@ -5694,20 +5692,20 @@
       <c r="A354" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B354" s="20" t="s">
+      <c r="B354" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B355" s="20" t="s">
-        <v>526</v>
+      <c r="B355" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="C355" s="2"/>
     </row>
@@ -5715,20 +5713,20 @@
       <c r="A356" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B356" s="20" t="s">
+      <c r="B356" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B357" s="20" t="s">
-        <v>526</v>
+      <c r="B357" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="C357" s="2"/>
     </row>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A846EC-9121-46FE-A0A2-7DA4E4F5ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D04F3B7-D703-4DC5-9CF6-D5018C16B257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7080" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="547">
   <si>
     <t>tag_name</t>
   </si>
@@ -1748,6 +1748,57 @@
   </si>
   <si>
     <t>@kii_nut_inc</t>
+  </si>
+  <si>
+    <t>srs_srs</t>
+  </si>
+  <si>
+    <t>srs_systematic</t>
+  </si>
+  <si>
+    <t>srs_rlc</t>
+  </si>
+  <si>
+    <t>systematic</t>
+  </si>
+  <si>
+    <t>systematic_rlc</t>
+  </si>
+  <si>
+    <t>proportional_rlc</t>
+  </si>
+  <si>
+    <t>cluster_rlc</t>
+  </si>
+  <si>
+    <t>cluster</t>
+  </si>
+  <si>
+    <t>proportional</t>
+  </si>
+  <si>
+    <t>purposive</t>
+  </si>
+  <si>
+    <t>definition_household</t>
+  </si>
+  <si>
+    <t>definition_gam_women</t>
+  </si>
+  <si>
+    <t>definition_muac</t>
+  </si>
+  <si>
+    <t>definition_cdr</t>
+  </si>
+  <si>
+    <t>definition_u5dr</t>
+  </si>
+  <si>
+    <t>definition_complementary_feeding</t>
+  </si>
+  <si>
+    <t>definition_gam</t>
   </si>
 </sst>
 </file>
@@ -2277,8 +2328,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" customWidth="1"/>
     <col min="4" max="4" width="66.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5456,6 +5507,9 @@
       <c r="B332" t="s">
         <v>507</v>
       </c>
+      <c r="C332" s="2" t="s">
+        <v>530</v>
+      </c>
       <c r="D332" s="27" t="s">
         <v>515</v>
       </c>
@@ -5467,6 +5521,9 @@
       <c r="B333" t="s">
         <v>507</v>
       </c>
+      <c r="C333" s="2" t="s">
+        <v>531</v>
+      </c>
       <c r="D333" s="27" t="s">
         <v>516</v>
       </c>
@@ -5478,6 +5535,9 @@
       <c r="B334" t="s">
         <v>507</v>
       </c>
+      <c r="C334" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="D334" s="27" t="s">
         <v>517</v>
       </c>
@@ -5489,6 +5549,9 @@
       <c r="B335" t="s">
         <v>507</v>
       </c>
+      <c r="C335" s="2" t="s">
+        <v>533</v>
+      </c>
       <c r="D335" s="27" t="s">
         <v>518</v>
       </c>
@@ -5500,6 +5563,9 @@
       <c r="B336" t="s">
         <v>507</v>
       </c>
+      <c r="C336" s="2" t="s">
+        <v>534</v>
+      </c>
       <c r="D336" s="27" t="s">
         <v>519</v>
       </c>
@@ -5511,6 +5577,9 @@
       <c r="B337" t="s">
         <v>507</v>
       </c>
+      <c r="C337" s="2" t="s">
+        <v>535</v>
+      </c>
       <c r="D337" s="27" t="s">
         <v>520</v>
       </c>
@@ -5522,6 +5591,9 @@
       <c r="B338" t="s">
         <v>507</v>
       </c>
+      <c r="C338" s="2" t="s">
+        <v>536</v>
+      </c>
       <c r="D338" s="27" t="s">
         <v>521</v>
       </c>
@@ -5533,6 +5605,9 @@
       <c r="B339" t="s">
         <v>507</v>
       </c>
+      <c r="C339" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="D339" s="27" t="s">
         <v>522</v>
       </c>
@@ -5544,6 +5619,9 @@
       <c r="B340" t="s">
         <v>507</v>
       </c>
+      <c r="C340" s="2" t="s">
+        <v>538</v>
+      </c>
       <c r="D340" s="27" t="s">
         <v>523</v>
       </c>
@@ -5555,6 +5633,9 @@
       <c r="B341" t="s">
         <v>507</v>
       </c>
+      <c r="C341" s="2" t="s">
+        <v>539</v>
+      </c>
       <c r="D341" s="27" t="s">
         <v>524</v>
       </c>
@@ -5587,10 +5668,12 @@
       <c r="A345" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C345" s="2"/>
+      <c r="B345" t="s">
+        <v>507</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>540</v>
+      </c>
       <c r="D345" t="s">
         <v>129</v>
       </c>
@@ -5599,10 +5682,12 @@
       <c r="A346" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B346" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C346" s="2"/>
+      <c r="B346" t="s">
+        <v>507</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>546</v>
+      </c>
       <c r="D346" t="s">
         <v>122</v>
       </c>
@@ -5611,10 +5696,12 @@
       <c r="A347" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C347" s="2"/>
+      <c r="B347" t="s">
+        <v>507</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>541</v>
+      </c>
       <c r="D347" t="s">
         <v>127</v>
       </c>
@@ -5623,10 +5710,12 @@
       <c r="A348" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B348" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C348" s="2"/>
+      <c r="B348" t="s">
+        <v>507</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>542</v>
+      </c>
       <c r="D348" t="s">
         <v>121</v>
       </c>
@@ -5635,10 +5724,12 @@
       <c r="A349" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B349" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C349" s="2"/>
+      <c r="B349" t="s">
+        <v>507</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>543</v>
+      </c>
       <c r="D349" t="s">
         <v>123</v>
       </c>
@@ -5647,10 +5738,12 @@
       <c r="A350" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B350" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C350" s="2"/>
+      <c r="B350" t="s">
+        <v>507</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="D350" t="s">
         <v>125</v>
       </c>
@@ -5659,10 +5752,12 @@
       <c r="A351" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B351" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C351" s="2"/>
+      <c r="B351" t="s">
+        <v>507</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>545</v>
+      </c>
       <c r="D351" t="s">
         <v>124</v>
       </c>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D04F3B7-D703-4DC5-9CF6-D5018C16B257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AFBCCB-0010-4767-8C7C-316D7B9CF0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14595" yWindow="0" windowWidth="14685" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="673">
   <si>
     <t>tag_name</t>
   </si>
@@ -425,15 +425,6 @@
     <t>“A group of people who ate from the same cooking and slept under the same roof the previous night”</t>
   </si>
   <si>
-    <t>@sample_size_hh_gen</t>
-  </si>
-  <si>
-    <t>@sample_size_hh_ind</t>
-  </si>
-  <si>
-    <t>@sample_size_hh_mort</t>
-  </si>
-  <si>
     <t>@sample_size_hh_gen_table</t>
   </si>
   <si>
@@ -441,9 +432,6 @@
   </si>
   <si>
     <t>@sample_size_hh_mort_table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In cases where no MUAC or mortality data is being collected, the sample size can be estimated based on other household level indicators such as FSL and WASH. The below table summarizes the sampling assumptions for each strata. </t>
   </si>
   <si>
     <t>handling</t>
@@ -1657,18 +1645,9 @@
     <t>The general research design for the Integrated Public Health Rapid Assessment (IPHRA) will consist of a mixed-methods approach constituting three main methods: household surveys; Key Informant Interviews (KIIs); and observation checklists, each of these methods having core and supplemental specialized tools and information that can be collected.</t>
   </si>
   <si>
-    <t>@text_methodology_overview_systematic</t>
-  </si>
-  <si>
     <t>@text_methodology_overview_cluster_rlc</t>
   </si>
   <si>
-    <t>@text_methodology_overview_cluster</t>
-  </si>
-  <si>
-    <t>@text_methodology_overview_proportional</t>
-  </si>
-  <si>
     <t>@text_methodology_overview_srs_rlc</t>
   </si>
   <si>
@@ -1678,9 +1657,6 @@
     <t>@text_methodology_overview_proportional_rlc</t>
   </si>
   <si>
-    <t>@text_methodology_overview_purposive</t>
-  </si>
-  <si>
     <t>conditional_replace</t>
   </si>
   <si>
@@ -1714,72 +1690,15 @@
     <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using simple random sampling from a list of accessible sites and households selected in the second stage using random location cluster (RLC) method. In RLC sampling, GPS points will be randomly generated over a bounded area of selected sites and an equal number of GPS points will be generated per site. Data collection teams will collect household interviews at the closest three households at each GPS point. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
   </si>
   <si>
-    <t>placeholder systematic</t>
-  </si>
-  <si>
-    <t>placeholder systematic rlc</t>
-  </si>
-  <si>
-    <t>placeholder systematic proportional</t>
-  </si>
-  <si>
-    <t>placeholder cluster rlc</t>
-  </si>
-  <si>
-    <t>placehodler cluster</t>
-  </si>
-  <si>
-    <t>placeholder proportional</t>
-  </si>
-  <si>
-    <t>placeholder purposive</t>
-  </si>
-  <si>
     <t>table</t>
   </si>
   <si>
     <t>image</t>
   </si>
   <si>
-    <t>placeholder ind sampling</t>
-  </si>
-  <si>
-    <t>placeholder mort sampling</t>
-  </si>
-  <si>
     <t>@kii_nut_inc</t>
   </si>
   <si>
-    <t>srs_srs</t>
-  </si>
-  <si>
-    <t>srs_systematic</t>
-  </si>
-  <si>
-    <t>srs_rlc</t>
-  </si>
-  <si>
-    <t>systematic</t>
-  </si>
-  <si>
-    <t>systematic_rlc</t>
-  </si>
-  <si>
-    <t>proportional_rlc</t>
-  </si>
-  <si>
-    <t>cluster_rlc</t>
-  </si>
-  <si>
-    <t>cluster</t>
-  </si>
-  <si>
-    <t>proportional</t>
-  </si>
-  <si>
-    <t>purposive</t>
-  </si>
-  <si>
     <t>definition_household</t>
   </si>
   <si>
@@ -1799,13 +1718,472 @@
   </si>
   <si>
     <t>definition_gam</t>
+  </si>
+  <si>
+    <t>@sample_size_gen</t>
+  </si>
+  <si>
+    <t>@r_version</t>
+  </si>
+  <si>
+    <t>@sample_size_hh_gen_text</t>
+  </si>
+  <si>
+    <t>general_survey</t>
+  </si>
+  <si>
+    <t>individual_survey</t>
+  </si>
+  <si>
+    <t>rate_survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household sample size calculations were done in @r_version and made using a 95% confidence level and the following sampling parameters summarized in the table below, resulting in a final target sample size of @sample_size_gen households: </t>
+  </si>
+  <si>
+    <t>@sample_size_ind_persons</t>
+  </si>
+  <si>
+    <t>@ind_indicator</t>
+  </si>
+  <si>
+    <t>@sample_size_ind_hh</t>
+  </si>
+  <si>
+    <t>@sample_size_hh_ind_text</t>
+  </si>
+  <si>
+    <t>rate_individual_survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual and household sample size calculations were done in @r_version and made using a 95% confidence level and the following sampling parameters summarized in the table below for the indicator @ind_indicator, resulting in a final sample size of @sample_size_ind_persons individuals and @sample_size_ind_hh households. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@sample_size_rate_persons </t>
+  </si>
+  <si>
+    <t>@sample_size_rate_persontime</t>
+  </si>
+  <si>
+    <t>@sample_size_rate_hh</t>
+  </si>
+  <si>
+    <t>@rate_indicator</t>
+  </si>
+  <si>
+    <t>@sample_size_hh_mort_text</t>
+  </si>
+  <si>
+    <t>@sample_size_ind_mort_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual, person-time, and household sample size calculations were done in @r_version and made using a 95% confidence level and the following sampling parameters summarized in the table below for the indicator @rate_indicator, resulting in a final sample size of @sample_size_rate_persons individuals, @sample_size_rate_persontime and @sample_size_rate_hh households. </t>
+  </si>
+  <si>
+    <t>@sample_size_hh_final</t>
+  </si>
+  <si>
+    <t>Sample sizes were calculated at a 95% confidence level in @r_version for both @ind_indicator and @rate_indicator with the highest sample size between the two indicators being selected per strata. The sampling parameters for each parameter are summarized in the tables below. The resulting final household sample size across strata is @sample_size_hh_final.</t>
+  </si>
+  <si>
+    <t>conditional_table</t>
+  </si>
+  <si>
+    <t>@header_primary_data_collection</t>
+  </si>
+  <si>
+    <t>Primary Data Collection</t>
+  </si>
+  <si>
+    <t>@text_intro_primary_data_collection</t>
+  </si>
+  <si>
+    <t>The following section will provide details on the sampling and data collection methods for the household survey, key informant, and observation tools within the assessment.</t>
+  </si>
+  <si>
+    <t>@header_definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Definitions </t>
+  </si>
+  <si>
+    <t>@header_secondary_data_review</t>
+  </si>
+  <si>
+    <t>@text_intro_secondary_data_review</t>
+  </si>
+  <si>
+    <t>Secondary data review</t>
+  </si>
+  <si>
+    <t>The main assessment design is based off guidance documents and tools for Integrated Public Health Rapid Assessment (IPHRA), available on the IMPACT Intranet. Secondly, in addition to the general objectives of this assessment the IPHRA toolkit is designed to align with the Acute Needs Framework (ANF) utilized by IMPACT Initiatives in their Acute Needs Analysis workstreams. Specific objectives and research questions within the IPHRA are intended to match and inform different pillars and sub-pillars of this framework. Please see below for how the ANF framework maps against the planned primary data collection, as well as secondary data sources planned to be utilized for this assessment.</t>
+  </si>
+  <si>
+    <t>@text_intro_secondary_data_sources_table</t>
+  </si>
+  <si>
+    <t>The below table summarizes key secondary data sources that describe the population at risk, inform planning for the assessment, or that provide information on key pillars or sub-pillars to justify that those concepts do not need to be included for primary data collection:</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_srs</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_systematic</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_srs</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_systematic</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_srs</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_systematic</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_srs</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_systematic</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_rlc</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using systematic random sampling from a list of accessible sites, and households selected in the second stage using appropriate sampling techniques such as simple random sampling from community listing or maps of households. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using systematic random sampling from a list of accessible sites, and households selected in the second stage using systematic random sampling of households. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a one-stage approach sampling strategy with all eligible sites being included and the target sample being allocated across sites proportional to their population size. Household will be done using appropriate sampling techniques such as simple random sampling from community listing or maps of households. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a one-stage approach sampling strategy with all eligible sites being included and the target sample being allocated across sites proportional to their population size. Household will be done using systematic random sampling of households. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using systematic random sampling from a list of accessible sites, and households selected in the second stage using random location cluster (RLC) method. In RLC sampling, GPS points will be randomly generated over a bounded area of selected sites and an equal number of GPS points will be generated per site. Data collection teams will collect household interviews at the closest three households at each GPS point. Sites will have equal probability of selection due to a lack of reliable population data. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of six sites will be either randomly or purposefully selected for assessment. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a one-stage approach sampling strategy with all eligible sites being included and the target sample being allocated across sites proportional to their population size. Household will be done using random location cluster (RLC) method. In RLC sampling, GPS points will be randomly generated over a bounded area of selected sites and an equal number of GPS points will be generated per site. Data collection teams will collect household interviews at the closest three households at each GPS point. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected purposively in the first stage based on criteria such as need, accessibility, logistics, or other defined criteria. Households selected in the second stage using appropriate sampling techniques such as simple random sampling from community listing or maps of households. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population and may not be comparable to other sites in the population depending on the purposive selection criteria.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected purposively in the first stage based on criteria such as need, accessibility, logistics, or other defined criteria. Households selected in the second stage using systematic random sampling of households. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population and may not be comparable to other sites in the population depending on the purposive selection criteria.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected purposively in the first stage based on criteria such as need, accessibility, logistics, or other defined criteria. Households selected in the second stage using random location cluster (RLC) method. In RLC sampling, GPS points will be randomly generated over a bounded area of selected sites and an equal number of GPS points will be generated per site. Data collection teams will collect household interviews at the closest three households at each GPS point. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Results are intended to provide localized results which are not generalizable beyond the assessed population and may not be comparable to other sites in the population depending on the purposive selection criteria.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using probability proportional to size (PPS) sampling from a list of accessible sites, and households selected in the second stage using appropriate sampling techniques such as simple random sampling from community listing or maps of households. Primary sampling units (PSU) will be defined as the village, neighbourhood, or camp and the probability of their selection is proportional to their population size. Sampling with replacement will be implemented so more than one cluster may fall within the same site by random chance. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of 25 clusters with similar cluster sizes will be conducted. Results are intended to be generalizable to the population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using probability proportional to size (PPS) sampling from a list of accessible sites, and households selected in the second stage us using systematic random sampling of households. Primary sampling units (PSU) will be defined as the village, neighbourhood, or camp and the probability of their selection is proportional to their population size. Sampling with replacement will be implemented so more than one cluster may fall within the same site by random chance. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of 25 clusters with similar cluster sizes will be conducted. Results are intended to be generalizable to the population.</t>
+  </si>
+  <si>
+    <t>The household survey component will consist of a two-stage approach sampling strategy with sites selected in the first stage using probability proportional to size (PPS) sampling from a list of accessible sites, and households selected in the second stage us using random location cluster (RLC) method. Primary sampling units (PSU) will be defined as the village, neighbourhood, or camp and the probability of their selection is proportional to their population size. In RLC sampling, GPS points will be randomly generated over a bounded area of the selected PSUs and an equal number of GPS points will be generated per PSU. Data collection teams will collect household interviews at the closest three households at each GPS point. Sampling with replacement will be implemented so more than one cluster may fall within the same site by random chance. Either a single stratum will be identified representing the target population, or if comparison between multiple groups is necessary than multiple strata will be selected. Within each stratum, a minimum of 25 clusters with similar cluster sizes will be conducted. Results are intended to be generalizable to the population.</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_multiple_methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The household survey component will have different sampling approaches for different strata due to either operational or resource considerations, or due to the size or distribution of the population. </t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_srs_srs</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_srs_systematic</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_srs_rlc</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_systematic_srs</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_systematic_systematic</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_systematic_rlc</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_proportional_srs</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_proportional_systematic</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_proportional_rlc</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_cluster_srs</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_cluster_systematic</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_cluster_rlc</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_purposive_srs</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_purposive_systematic</t>
+  </si>
+  <si>
+    <t>@stratified_strata_names_purposive_rlc</t>
+  </si>
+  <si>
+    <t>multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>srs_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>srs_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>srs_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>srs_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>srs_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>srs_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>systematic_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>proportional_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>cluster_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>purposive_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_systematic . This methodology applies for the following strata: @stratified_strata_names_systematic_systematic .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_srs . This methodology applies for the following strata: @stratified_strata_names_systematic_srs .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_systematic_rlc . This methodology applies for the following strata: @stratified_strata_names_systematic_rlc .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_srs . This methodology applies for the following strata: @stratified_strata_names_proportional_srs .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_systematic . This methodology applies for the following strata: @stratified_strata_names_proportional_systematic .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_proportional_rlc . This methodology applies for the following strata: @stratified_strata_names_proportional_rlc .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_srs . This methodology applies for the following strata: @stratified_strata_names_cluster_srs .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_systematic . This methodology applies for the following strata: @stratified_strata_names_cluster_systematic .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_cluster_rlc . This methodology applies for the following strata: @stratified_strata_names_cluster_rlc .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_srs . This methodology applies for the following strata: @stratified_strata_names_purposive_srs .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_systematic . This methodology applies for the following strata: @stratified_strata_names_purposive_systematic .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_purposive_rlc . This methodology applies for the following strata: @stratified_strata_names_purposive_rlc .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_srs . This methodology applies for the following strata: @stratified_strata_names_srs_srs .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_systematic . This methodology applies for the following strata: @stratified_strata_names_srs_systematic .</t>
+  </si>
+  <si>
+    <t>@text_methodology_overview_srs_rlc . This methodology applies for the following strata: @stratified_strata_names_srs_rlc .</t>
+  </si>
+  <si>
+    <t>@text_stratified_srs_srs_strata</t>
+  </si>
+  <si>
+    <t>@text_stratified_srs_systematic</t>
+  </si>
+  <si>
+    <t>@text_stratified_srs_rlc</t>
+  </si>
+  <si>
+    <t>@text_stratified_systematic_srs</t>
+  </si>
+  <si>
+    <t>@text_stratified_systematic_systematic</t>
+  </si>
+  <si>
+    <t>@text_stratified_systematic_rlc</t>
+  </si>
+  <si>
+    <t>@text_stratified_proportional_srs</t>
+  </si>
+  <si>
+    <t>@text_stratified_proportional_systematic</t>
+  </si>
+  <si>
+    <t>@text_stratified_proportional_rlc</t>
+  </si>
+  <si>
+    <t>@text_stratified_cluster_srs</t>
+  </si>
+  <si>
+    <t>@text_stratified_cluster_systematic</t>
+  </si>
+  <si>
+    <t>@text_stratified_cluster_rlc</t>
+  </si>
+  <si>
+    <t>@text_stratified_purposive_srs</t>
+  </si>
+  <si>
+    <t>@text_stratified_purposive_systematic</t>
+  </si>
+  <si>
+    <t>@text_stratified_purposive_rlc</t>
+  </si>
+  <si>
+    <t>@text_methodology_kii_community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community informants will include one community leader per site and two community members either purposefully or randomly selected from the site. These community informants will be asked a semi-structured tool based upon the HESPER questionnaire but with qualitative follow up questions intended to triangulate needs and service gaps against other IPHRA tools.    </t>
+  </si>
+  <si>
+    <t>kii_community</t>
+  </si>
+  <si>
+    <t>@text_methodology_kii_service_providers</t>
+  </si>
+  <si>
+    <t>@text_kii_health_facility</t>
+  </si>
+  <si>
+    <t>@text_kii_nutrition_facility</t>
+  </si>
+  <si>
+    <t>@text_kii_fsl_provider</t>
+  </si>
+  <si>
+    <t>@text_kii_wash_provider</t>
+  </si>
+  <si>
+    <t>kii_service_providers</t>
+  </si>
+  <si>
+    <t>kii_health_provider</t>
+  </si>
+  <si>
+    <t>kii_nutrition_provider</t>
+  </si>
+  <si>
+    <t>kii_fsl_provider</t>
+  </si>
+  <si>
+    <t>kii_wash_provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service provider key informant interviews will be purposefully selected based on staff available for interview. These staff should be individuals with direct knowledge or involvement in service provision for the affected population. @text_kii_health_facility . @text_kii_nutrition_facility . @text_kii_fsl_provider . @text_kii_wash_provider . One interview will be conducted with staff from each health facility or service provider NGO in the assessment area. Eligible staff are preferably program or facility managers with an understanding of the service delivery challenges but may also be senior officers, health or nutrition practitioners if needed. </t>
+  </si>
+  <si>
+    <t>nutrition facilities,</t>
+  </si>
+  <si>
+    <t>health facilities,</t>
+  </si>
+  <si>
+    <t>FSL NGO providers,</t>
+  </si>
+  <si>
+    <t>WASH NGO providers.</t>
+  </si>
+  <si>
+    <t>@text_methodology_obs_community</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1956,13 +2334,26 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF58585A"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1977,7 +2368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2022,6 +2413,24 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2324,12 +2733,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D357"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" customWidth="1"/>
+    <col min="1" max="1" width="53.140625" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="68" customWidth="1"/>
     <col min="4" max="4" width="66.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2338,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -2349,35 +2758,35 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2385,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2393,7 +2802,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2401,7 +2810,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -2409,65 +2818,65 @@
     </row>
     <row r="8" spans="1:4" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D13" s="12" t="b">
         <v>0</v>
@@ -2475,21 +2884,21 @@
     </row>
     <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D15" s="12" t="b">
         <v>0</v>
@@ -2497,21 +2906,21 @@
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D17" s="12" t="b">
         <v>0</v>
@@ -2519,21 +2928,21 @@
     </row>
     <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D19" s="12" t="b">
         <v>0</v>
@@ -2541,21 +2950,21 @@
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D21" s="12" t="b">
         <v>0</v>
@@ -2563,13 +2972,13 @@
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2577,7 +2986,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D23" s="12" t="b">
         <v>0</v>
@@ -2585,13 +2994,13 @@
     </row>
     <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2599,18 +3008,18 @@
         <v>6</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2618,18 +3027,18 @@
         <v>7</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2637,29 +3046,29 @@
         <v>8</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2667,18 +3076,18 @@
         <v>13</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,18 +3095,18 @@
         <v>14</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2705,18 +3114,18 @@
         <v>15</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2724,18 +3133,18 @@
         <v>16</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2743,18 +3152,18 @@
         <v>17</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2762,18 +3171,18 @@
         <v>18</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2781,18 +3190,18 @@
         <v>19</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2800,18 +3209,18 @@
         <v>20</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2819,95 +3228,95 @@
         <v>21</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D50" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,7 +3324,7 @@
         <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2923,7 +3332,7 @@
         <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2931,7 +3340,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2939,7 +3348,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2947,124 +3356,124 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" t="s">
         <v>220</v>
-      </c>
-      <c r="B67" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D67" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D68" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" s="14" t="s">
         <v>229</v>
-      </c>
-      <c r="B73" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3072,7 +3481,7 @@
         <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3080,7 +3489,7 @@
         <v>29</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3088,7 +3497,7 @@
         <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3096,62 +3505,62 @@
         <v>31</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3159,7 +3568,7 @@
         <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3167,7 +3576,7 @@
         <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3175,7 +3584,7 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3183,7 +3592,7 @@
         <v>35</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3191,18 +3600,18 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3210,18 +3619,18 @@
         <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3229,29 +3638,29 @@
         <v>38</v>
       </c>
       <c r="B91" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3259,7 +3668,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -3267,13 +3676,13 @@
     </row>
     <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3281,18 +3690,18 @@
         <v>111</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3300,18 +3709,18 @@
         <v>112</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3319,18 +3728,18 @@
         <v>9</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3338,128 +3747,128 @@
         <v>12</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B108" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B112" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -3467,7 +3876,7 @@
         <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -3475,7 +3884,7 @@
         <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -3483,7 +3892,7 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -3491,7 +3900,7 @@
         <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -3499,7 +3908,7 @@
         <v>43</v>
       </c>
       <c r="B118" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -3507,7 +3916,7 @@
         <v>44</v>
       </c>
       <c r="B119" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -3515,7 +3924,7 @@
         <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -3523,7 +3932,7 @@
         <v>46</v>
       </c>
       <c r="B121" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -3531,7 +3940,7 @@
         <v>47</v>
       </c>
       <c r="B122" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -3539,37 +3948,37 @@
         <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="33" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B124" t="s">
+        <v>140</v>
+      </c>
+      <c r="D124" s="20" t="s">
         <v>280</v>
-      </c>
-      <c r="B124" t="s">
-        <v>144</v>
-      </c>
-      <c r="D124" s="20" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B125" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B126" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D126" s="19"/>
     </row>
@@ -3578,19 +3987,19 @@
         <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D127" s="19"/>
     </row>
     <row r="128" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B128" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -3598,7 +4007,7 @@
         <v>50</v>
       </c>
       <c r="B129" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -3606,26 +4015,26 @@
         <v>51</v>
       </c>
       <c r="B130" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -3633,7 +4042,7 @@
         <v>52</v>
       </c>
       <c r="B133" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -3641,7 +4050,7 @@
         <v>53</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3649,83 +4058,83 @@
         <v>54</v>
       </c>
       <c r="B135" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D136" s="21" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3733,18 +4142,18 @@
         <v>55</v>
       </c>
       <c r="B144" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D145" s="22" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -3752,19 +4161,19 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D146" s="22"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D147" s="22" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -3772,18 +4181,18 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B149" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D149" s="22" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -3791,18 +4200,18 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B151" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -3810,18 +4219,18 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B153" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D153" s="22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -3829,29 +4238,29 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B155" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -3859,37 +4268,37 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B158" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D158" s="22" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B159" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B160" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D160" s="22" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -3897,78 +4306,78 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B162" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B163" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B164" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B165" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B167" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D167" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B168" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -3976,7 +4385,7 @@
         <v>72</v>
       </c>
       <c r="B169" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -3984,7 +4393,7 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -3992,18 +4401,18 @@
         <v>74</v>
       </c>
       <c r="B171" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B172" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4011,102 +4420,102 @@
         <v>56</v>
       </c>
       <c r="B173" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B174" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D174" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B175" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B176" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B177" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B178" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B179" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B180" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D180" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B181" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B182" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B183" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -4114,18 +4523,18 @@
         <v>75</v>
       </c>
       <c r="B184" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B185" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D185" s="13" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -4133,55 +4542,55 @@
         <v>57</v>
       </c>
       <c r="B186" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B187" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B188" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B189" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B190" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B191" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B192" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -4189,18 +4598,18 @@
         <v>76</v>
       </c>
       <c r="B193" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B194" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D194" s="13" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -4208,61 +4617,61 @@
         <v>58</v>
       </c>
       <c r="B195" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B196" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D196" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B197" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B198" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D198" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B199" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B200" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B201" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -4270,18 +4679,18 @@
         <v>77</v>
       </c>
       <c r="B202" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B203" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D203" s="13" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -4289,64 +4698,64 @@
         <v>59</v>
       </c>
       <c r="B204" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B205" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B206" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B207" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D207" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B208" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B209" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B210" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -4354,18 +4763,18 @@
         <v>78</v>
       </c>
       <c r="B211" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B212" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D212" s="13" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -4373,64 +4782,64 @@
         <v>60</v>
       </c>
       <c r="B213" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B214" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B215" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B216" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D216" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B217" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B218" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B219" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -4438,83 +4847,83 @@
         <v>79</v>
       </c>
       <c r="B220" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B221" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D221" s="13" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="B222" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B223" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B224" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B225" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D225" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B226" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B227" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B228" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -4522,18 +4931,18 @@
         <v>80</v>
       </c>
       <c r="B229" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B230" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -4541,64 +4950,64 @@
         <v>61</v>
       </c>
       <c r="B231" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B232" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B233" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B234" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B235" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B236" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B237" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -4606,18 +5015,18 @@
         <v>81</v>
       </c>
       <c r="B238" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B239" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D239" s="13" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -4625,64 +5034,64 @@
         <v>62</v>
       </c>
       <c r="B240" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B241" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B242" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B243" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D243" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B244" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B245" t="s">
+        <v>140</v>
+      </c>
+      <c r="D245" s="14" t="s">
         <v>400</v>
-      </c>
-      <c r="B245" t="s">
-        <v>144</v>
-      </c>
-      <c r="D245" s="14" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B246" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -4690,18 +5099,18 @@
         <v>82</v>
       </c>
       <c r="B247" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B248" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -4709,64 +5118,64 @@
         <v>63</v>
       </c>
       <c r="B249" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B250" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B251" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B252" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D252" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B253" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B254" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B255" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -4774,18 +5183,18 @@
         <v>83</v>
       </c>
       <c r="B256" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B257" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D257" s="24" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -4793,94 +5202,94 @@
         <v>64</v>
       </c>
       <c r="B258" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B259" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B260" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B261" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D261" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B262" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B263" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B264" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B265" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B266" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D266" s="13" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B267" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D267" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -4888,7 +5297,7 @@
         <v>84</v>
       </c>
       <c r="B268" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -4896,78 +5305,78 @@
         <v>85</v>
       </c>
       <c r="B269" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B270" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D270" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B271" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B272" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B273" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D273" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B274" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D274" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B275" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D275" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B276" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D276" s="17" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -4975,7 +5384,7 @@
         <v>86</v>
       </c>
       <c r="B277" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -4983,7 +5392,7 @@
         <v>87</v>
       </c>
       <c r="B278" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -4991,128 +5400,128 @@
         <v>88</v>
       </c>
       <c r="B279" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B280" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B281" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D281" s="10" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B282" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D282" s="10" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B283" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D283" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B284" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D284" s="10" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B285" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D285" s="10" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B286" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D286" s="10" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B287" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D287" s="10" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B288" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D288" s="10" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B289" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D289" s="10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B290" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -5120,7 +5529,7 @@
         <v>89</v>
       </c>
       <c r="B291" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -5128,7 +5537,7 @@
         <v>90</v>
       </c>
       <c r="B292" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -5136,7 +5545,7 @@
         <v>91</v>
       </c>
       <c r="B293" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -5144,7 +5553,7 @@
         <v>92</v>
       </c>
       <c r="B294" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -5152,7 +5561,7 @@
         <v>93</v>
       </c>
       <c r="B295" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -5160,7 +5569,7 @@
         <v>94</v>
       </c>
       <c r="B296" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -5168,7 +5577,7 @@
         <v>95</v>
       </c>
       <c r="B297" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -5176,7 +5585,7 @@
         <v>96</v>
       </c>
       <c r="B298" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -5184,7 +5593,7 @@
         <v>97</v>
       </c>
       <c r="B299" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -5192,7 +5601,7 @@
         <v>98</v>
       </c>
       <c r="B300" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -5200,7 +5609,7 @@
         <v>99</v>
       </c>
       <c r="B301" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -5208,7 +5617,7 @@
         <v>100</v>
       </c>
       <c r="B302" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -5216,7 +5625,7 @@
         <v>101</v>
       </c>
       <c r="B303" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -5224,7 +5633,7 @@
         <v>102</v>
       </c>
       <c r="B304" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -5232,7 +5641,7 @@
         <v>103</v>
       </c>
       <c r="B305" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -5240,7 +5649,7 @@
         <v>104</v>
       </c>
       <c r="B306" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -5248,7 +5657,7 @@
         <v>105</v>
       </c>
       <c r="B307" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -5256,7 +5665,7 @@
         <v>106</v>
       </c>
       <c r="B308" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -5264,7 +5673,7 @@
         <v>107</v>
       </c>
       <c r="B309" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -5272,40 +5681,40 @@
         <v>108</v>
       </c>
       <c r="B310" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B311" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B312" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B313" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -5313,7 +5722,7 @@
         <v>109</v>
       </c>
       <c r="B314" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -5321,509 +5730,1293 @@
         <v>110</v>
       </c>
       <c r="B315" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B316" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D316" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B317" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D317" s="25" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B318" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D318" s="25" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B319" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D319" s="25" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B320" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D320" s="25" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B321" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B322" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D322" s="26" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B323" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B324" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B325" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B326" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D326" s="26" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B327" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D327" s="27" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B328" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D328" s="27" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B329" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D329" s="27" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B330" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D330" s="26" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B331" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D331" s="27" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B332" t="s">
+        <v>499</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D332" s="27" t="s">
         <v>507</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="D332" s="27" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B333" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>531</v>
+        <v>610</v>
       </c>
       <c r="D333" s="27" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B334" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>532</v>
+        <v>611</v>
       </c>
       <c r="D334" s="27" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B335" t="s">
         <v>499</v>
       </c>
-      <c r="B335" t="s">
-        <v>507</v>
-      </c>
       <c r="C335" s="2" t="s">
-        <v>533</v>
+        <v>612</v>
       </c>
       <c r="D335" s="27" t="s">
-        <v>518</v>
+        <v>564</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="B336" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>534</v>
+        <v>613</v>
       </c>
       <c r="D336" s="27" t="s">
-        <v>519</v>
+        <v>565</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="B337" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="D337" s="27" t="s">
-        <v>520</v>
+        <v>568</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>500</v>
+        <v>557</v>
       </c>
       <c r="B338" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>536</v>
+        <v>615</v>
       </c>
       <c r="D338" s="27" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>501</v>
+        <v>558</v>
       </c>
       <c r="B339" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>537</v>
+        <v>616</v>
       </c>
       <c r="D339" s="27" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B340" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>538</v>
+        <v>617</v>
       </c>
       <c r="D340" s="27" t="s">
-        <v>523</v>
+        <v>569</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>506</v>
+        <v>559</v>
       </c>
       <c r="B341" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C341" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D341" s="27" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A342" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B342" t="s">
+        <v>499</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D342" s="27" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A343" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B343" t="s">
+        <v>499</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D343" s="27" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A344" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B344" t="s">
+        <v>499</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D344" s="27" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B345" t="s">
+        <v>499</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D345" s="34" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A346" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B346" t="s">
+        <v>499</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D346" s="27" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A347" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B347" t="s">
+        <v>499</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D347" s="27" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A348" s="35" t="s">
+        <v>639</v>
+      </c>
+      <c r="B348" t="s">
+        <v>499</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D348" s="36" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A349" s="35" t="s">
+        <v>578</v>
+      </c>
+      <c r="B349" t="s">
+        <v>141</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D349" s="27"/>
+    </row>
+    <row r="350" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A350" s="35" t="s">
+        <v>640</v>
+      </c>
+      <c r="B350" t="s">
+        <v>499</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D350" s="36" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A351" s="35" t="s">
+        <v>579</v>
+      </c>
+      <c r="B351" t="s">
+        <v>141</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D351" s="27"/>
+    </row>
+    <row r="352" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A352" s="35" t="s">
+        <v>641</v>
+      </c>
+      <c r="B352" t="s">
+        <v>499</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D352" s="36" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A353" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="B353" t="s">
+        <v>141</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D353" s="27"/>
+    </row>
+    <row r="354" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A354" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="B354" t="s">
+        <v>499</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D354" s="36" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A355" s="35" t="s">
+        <v>581</v>
+      </c>
+      <c r="B355" t="s">
+        <v>141</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D355" s="27"/>
+    </row>
+    <row r="356" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A356" s="35" t="s">
+        <v>643</v>
+      </c>
+      <c r="B356" t="s">
+        <v>499</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D356" s="36" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A357" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="B357" t="s">
+        <v>141</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D357" s="27"/>
+    </row>
+    <row r="358" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A358" s="35" t="s">
+        <v>644</v>
+      </c>
+      <c r="B358" t="s">
+        <v>499</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D358" s="36" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A359" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="B359" t="s">
+        <v>141</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D359" s="27"/>
+    </row>
+    <row r="360" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A360" s="35" t="s">
+        <v>645</v>
+      </c>
+      <c r="B360" t="s">
+        <v>499</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D360" s="36" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A361" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="B361" t="s">
+        <v>141</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D361" s="27"/>
+    </row>
+    <row r="362" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A362" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="B362" t="s">
+        <v>499</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D362" s="36" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A363" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="B363" t="s">
+        <v>141</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D363" s="36"/>
+    </row>
+    <row r="364" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A364" s="35" t="s">
+        <v>647</v>
+      </c>
+      <c r="B364" t="s">
+        <v>499</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D364" s="36" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A365" s="35" t="s">
+        <v>586</v>
+      </c>
+      <c r="B365" t="s">
+        <v>141</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D365" s="27"/>
+    </row>
+    <row r="366" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A366" s="35" t="s">
+        <v>648</v>
+      </c>
+      <c r="B366" t="s">
+        <v>499</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D366" s="36" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A367" s="35" t="s">
+        <v>587</v>
+      </c>
+      <c r="B367" t="s">
+        <v>141</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D367" s="27"/>
+    </row>
+    <row r="368" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A368" s="35" t="s">
+        <v>649</v>
+      </c>
+      <c r="B368" t="s">
+        <v>499</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D368" s="36" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A369" s="35" t="s">
+        <v>588</v>
+      </c>
+      <c r="B369" t="s">
+        <v>141</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D369" s="27"/>
+    </row>
+    <row r="370" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A370" s="35" t="s">
+        <v>650</v>
+      </c>
+      <c r="B370" t="s">
+        <v>499</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D370" s="36" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A371" s="35" t="s">
+        <v>589</v>
+      </c>
+      <c r="B371" t="s">
+        <v>141</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D371" s="27"/>
+    </row>
+    <row r="372" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A372" s="35" t="s">
+        <v>651</v>
+      </c>
+      <c r="B372" t="s">
+        <v>499</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D372" s="36" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A373" s="35" t="s">
+        <v>590</v>
+      </c>
+      <c r="B373" t="s">
+        <v>141</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D373" s="27"/>
+    </row>
+    <row r="374" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A374" s="35" t="s">
+        <v>652</v>
+      </c>
+      <c r="B374" t="s">
+        <v>499</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D374" s="36" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A375" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="B375" t="s">
+        <v>141</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D375" s="27"/>
+    </row>
+    <row r="376" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A376" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="B376" t="s">
+        <v>499</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D376" s="36" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A377" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="B377" t="s">
+        <v>141</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D377" s="27"/>
+    </row>
+    <row r="378" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A378" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="B378" t="s">
+        <v>499</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D378" s="27" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A379" s="37" t="s">
+        <v>657</v>
+      </c>
+      <c r="B379" t="s">
+        <v>499</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D379" s="27" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A380" s="36" t="s">
+        <v>658</v>
+      </c>
+      <c r="B380" t="s">
+        <v>499</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D380" s="27" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A381" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B381" t="s">
+        <v>499</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D381" s="27" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A382" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B382" t="s">
+        <v>499</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D382" s="27" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A383" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B383" t="s">
+        <v>499</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="D383" s="27" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A384" s="2"/>
+      <c r="C384" s="2"/>
+      <c r="D384" s="27"/>
+    </row>
+    <row r="385" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A385" s="37" t="s">
+        <v>672</v>
+      </c>
+      <c r="C385" s="2"/>
+      <c r="D385" s="27"/>
+    </row>
+    <row r="386" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A386" s="2"/>
+      <c r="C386" s="2"/>
+      <c r="D386" s="27"/>
+    </row>
+    <row r="387" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A387" s="2"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="27"/>
+    </row>
+    <row r="388" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A388" s="2"/>
+      <c r="C388" s="2"/>
+      <c r="D388" s="27"/>
+    </row>
+    <row r="389" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A389" s="2"/>
+      <c r="C389" s="2"/>
+      <c r="D389" s="27"/>
+    </row>
+    <row r="390" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A390" s="2"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="27"/>
+    </row>
+    <row r="391" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A391" s="2"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="27"/>
+    </row>
+    <row r="392" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A392" s="2"/>
+      <c r="C392" s="2"/>
+      <c r="D392" s="27"/>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>113</v>
+      </c>
+      <c r="B393" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A394" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B394" t="s">
+        <v>140</v>
+      </c>
+      <c r="D394" s="26" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A395" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B395" t="s">
+        <v>140</v>
+      </c>
+      <c r="D395" s="27" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>114</v>
+      </c>
+      <c r="B396" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B397" t="s">
+        <v>140</v>
+      </c>
+      <c r="D397" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>115</v>
+      </c>
+      <c r="B398" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A399" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B399" t="s">
+        <v>140</v>
+      </c>
+      <c r="D399" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B400" t="s">
+        <v>499</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D400" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B401" t="s">
+        <v>499</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D401" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B402" t="s">
+        <v>499</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D402" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B403" t="s">
+        <v>499</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D403" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B404" t="s">
+        <v>499</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D404" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B405" t="s">
+        <v>499</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D405" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B406" t="s">
+        <v>499</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D406" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A407" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B407" t="s">
+        <v>140</v>
+      </c>
+      <c r="C407" s="2"/>
+      <c r="D407" s="26" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A408" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B408" t="s">
+        <v>140</v>
+      </c>
+      <c r="C408" s="2"/>
+      <c r="D408" s="10" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B409" t="s">
+        <v>499</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D409" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B410" t="s">
+        <v>499</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D410" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A411" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B411" t="s">
+        <v>499</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D411" t="s">
         <v>539</v>
       </c>
-      <c r="D341" s="27" t="s">
+    </row>
+    <row r="412" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A412" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="B412" t="s">
+        <v>499</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D412" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B413" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D413" s="29"/>
+    </row>
+    <row r="414" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A414" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B414" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="B415" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A416" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="B416" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A417" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="B417" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A418" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B418" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A419" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B419" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C419" s="2"/>
+    </row>
+    <row r="420" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A420" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="B420" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A421" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="B421" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C421" s="10"/>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="B422" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C422" s="28"/>
+      <c r="D422" s="29"/>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C424" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>113</v>
-      </c>
-      <c r="B342" t="s">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C425" s="2" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>114</v>
-      </c>
-      <c r="B343" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>115</v>
-      </c>
-      <c r="B344" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A345" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B345" t="s">
-        <v>507</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D345" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A346" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B346" t="s">
-        <v>507</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D346" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A347" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B347" t="s">
-        <v>507</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D347" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A348" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B348" t="s">
-        <v>507</v>
-      </c>
-      <c r="C348" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D348" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A349" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B349" t="s">
-        <v>507</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D349" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A350" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B350" t="s">
-        <v>507</v>
-      </c>
-      <c r="C350" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D350" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A351" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B351" t="s">
-        <v>507</v>
-      </c>
-      <c r="C351" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D351" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A352" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C352" s="2"/>
-      <c r="D352" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C353" s="2"/>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C354" s="2"/>
-      <c r="D354" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C355" s="2"/>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C356" s="2"/>
-      <c r="D356" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A357" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C357" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AFBCCB-0010-4767-8C7C-316D7B9CF0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7977D509-C76A-44CF-A89E-AFB9B54262F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="0" windowWidth="14685" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="693">
   <si>
     <t>tag_name</t>
   </si>
@@ -2161,9 +2161,6 @@
     <t>kii_wash_provider</t>
   </si>
   <si>
-    <t xml:space="preserve">Service provider key informant interviews will be purposefully selected based on staff available for interview. These staff should be individuals with direct knowledge or involvement in service provision for the affected population. @text_kii_health_facility . @text_kii_nutrition_facility . @text_kii_fsl_provider . @text_kii_wash_provider . One interview will be conducted with staff from each health facility or service provider NGO in the assessment area. Eligible staff are preferably program or facility managers with an understanding of the service delivery challenges but may also be senior officers, health or nutrition practitioners if needed. </t>
-  </si>
-  <si>
     <t>nutrition facilities,</t>
   </si>
   <si>
@@ -2177,6 +2174,69 @@
   </si>
   <si>
     <t>@text_methodology_obs_community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service provider key informant interviews will be purposefully selected based on staff available for interview. These staff should be individuals with direct knowledge or involvement in service provision for the affected population. This includes interviews with staff from: @text_kii_health_facility , @text_kii_nutrition_facility , @text_kii_fsl_provider , @text_kii_wash_provider . One interview will be conducted with staff from each health facility or service provider NGO in the assessment area. Eligible staff are preferably program or facility managers with an understanding of the service delivery challenges but may also be senior officers, health or nutrition practitioners if needed. </t>
+  </si>
+  <si>
+    <t>@text_methodology_obs_service_providers</t>
+  </si>
+  <si>
+    <t>obs_community</t>
+  </si>
+  <si>
+    <t>obs_service_providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community observation checklists will be implemented in each assessed site to triangulate observable facts against household and key informant reporting. Observations will be made by making a transect walk through the community focusing on environmental conditions, damage, and community norms. </t>
+  </si>
+  <si>
+    <t>@text_obs_water_point</t>
+  </si>
+  <si>
+    <t>@text_obs_latrines</t>
+  </si>
+  <si>
+    <t>obs_water_point</t>
+  </si>
+  <si>
+    <t>obs_latrines</t>
+  </si>
+  <si>
+    <t>obs_health_facility</t>
+  </si>
+  <si>
+    <t>obs_crops_livestock</t>
+  </si>
+  <si>
+    <t>@text_obs_health_facility</t>
+  </si>
+  <si>
+    <t>@text_obs_crops_livestock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialized observation tools will be implemented at @text_obs_water_point , @text_obs_latrines , @text_obs_health_facility to evaluate basic infrastructure and functionality. @text_obs_crops_livestock . </t>
+  </si>
+  <si>
+    <t>water points</t>
+  </si>
+  <si>
+    <t>latrines</t>
+  </si>
+  <si>
+    <t>health facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An observation tool will be used to assess the condition of crops and/or livestock in the community using a transect walk through purposively selected locations. </t>
+  </si>
+  <si>
+    <t>@header_population_of_interest</t>
+  </si>
+  <si>
+    <t>Population of interest</t>
+  </si>
+  <si>
+    <t>@total_population_size</t>
   </si>
 </sst>
 </file>
@@ -2733,7 +2793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D425"/>
+  <dimension ref="A1:D437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -6524,7 +6584,7 @@
       <c r="D377" s="27"/>
     </row>
     <row r="378" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A378" s="27" t="s">
+      <c r="A378" s="36" t="s">
         <v>654</v>
       </c>
       <c r="B378" t="s">
@@ -6548,7 +6608,7 @@
         <v>662</v>
       </c>
       <c r="D379" s="27" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -6562,7 +6622,7 @@
         <v>663</v>
       </c>
       <c r="D380" s="27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -6576,7 +6636,7 @@
         <v>664</v>
       </c>
       <c r="D381" s="27" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -6590,7 +6650,7 @@
         <v>665</v>
       </c>
       <c r="D382" s="27" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -6604,417 +6664,536 @@
         <v>666</v>
       </c>
       <c r="D383" s="27" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A384" s="37" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="384" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A384" s="2"/>
-      <c r="C384" s="2"/>
-      <c r="D384" s="27"/>
+      <c r="B384" t="s">
+        <v>499</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D384" s="27" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="385" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A385" s="37" t="s">
-        <v>672</v>
-      </c>
-      <c r="C385" s="2"/>
-      <c r="D385" s="27"/>
+        <v>673</v>
+      </c>
+      <c r="B385" t="s">
+        <v>499</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D385" s="27" t="s">
+        <v>685</v>
+      </c>
     </row>
     <row r="386" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A386" s="2"/>
-      <c r="C386" s="2"/>
-      <c r="D386" s="27"/>
+      <c r="A386" s="36" t="s">
+        <v>677</v>
+      </c>
+      <c r="B386" t="s">
+        <v>499</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D386" s="27" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="387" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A387" s="2"/>
-      <c r="C387" s="2"/>
-      <c r="D387" s="27"/>
+      <c r="A387" s="36" t="s">
+        <v>678</v>
+      </c>
+      <c r="B387" t="s">
+        <v>499</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D387" s="27" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="388" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A388" s="2"/>
-      <c r="C388" s="2"/>
-      <c r="D388" s="27"/>
+      <c r="A388" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B388" t="s">
+        <v>499</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D388" s="27" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="389" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A389" s="2"/>
-      <c r="C389" s="2"/>
-      <c r="D389" s="27"/>
-    </row>
-    <row r="390" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A390" s="2"/>
-      <c r="C390" s="2"/>
-      <c r="D390" s="27"/>
-    </row>
-    <row r="391" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A391" s="2"/>
+      <c r="A389" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B389" t="s">
+        <v>499</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D389" s="27" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>113</v>
+      </c>
+      <c r="B390" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A391" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B391" t="s">
+        <v>140</v>
+      </c>
       <c r="C391" s="2"/>
-      <c r="D391" s="27"/>
+      <c r="D391" s="26" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="392" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A392" s="2"/>
+      <c r="A392" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B392" t="s">
+        <v>141</v>
+      </c>
       <c r="C392" s="2"/>
       <c r="D392" s="27"/>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>113</v>
-      </c>
-      <c r="B393" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="2" t="s">
+    <row r="393" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A393" s="2"/>
+      <c r="C393" s="2"/>
+      <c r="D393" s="27"/>
+    </row>
+    <row r="394" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A394" s="2"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="27"/>
+    </row>
+    <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A395" s="2"/>
+      <c r="C395" s="2"/>
+      <c r="D395" s="27"/>
+    </row>
+    <row r="396" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A396" s="2"/>
+      <c r="C396" s="2"/>
+      <c r="D396" s="27"/>
+    </row>
+    <row r="397" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A397" s="2"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="27"/>
+    </row>
+    <row r="398" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A398" s="2"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="27"/>
+    </row>
+    <row r="399" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A399" s="2"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="27"/>
+    </row>
+    <row r="400" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A400" s="2"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="27"/>
+    </row>
+    <row r="401" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A401" s="2"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="27"/>
+    </row>
+    <row r="402" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A402" s="2"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="27"/>
+    </row>
+    <row r="403" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A403" s="2"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="27"/>
+    </row>
+    <row r="404" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A404" s="2"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="27"/>
+    </row>
+    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A406" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B394" t="s">
-        <v>140</v>
-      </c>
-      <c r="D394" s="26" t="s">
+      <c r="B406" t="s">
+        <v>140</v>
+      </c>
+      <c r="D406" s="26" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A395" s="2" t="s">
+    <row r="407" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A407" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B395" t="s">
-        <v>140</v>
-      </c>
-      <c r="D395" s="27" t="s">
+      <c r="B407" t="s">
+        <v>140</v>
+      </c>
+      <c r="D407" s="27" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
         <v>114</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B408" t="s">
         <v>511</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A397" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="B397" t="s">
-        <v>140</v>
-      </c>
-      <c r="D397" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>115</v>
-      </c>
-      <c r="B398" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A399" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B399" t="s">
-        <v>140</v>
-      </c>
-      <c r="D399" s="33" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A400" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B400" t="s">
-        <v>499</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D400" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A401" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B401" t="s">
-        <v>499</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D401" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A402" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B402" t="s">
-        <v>499</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D402" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A403" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B403" t="s">
-        <v>499</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D403" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A404" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B404" t="s">
-        <v>499</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D404" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A405" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B405" t="s">
-        <v>499</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D405" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A406" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B406" t="s">
-        <v>499</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D406" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B407" t="s">
-        <v>140</v>
-      </c>
-      <c r="C407" s="2"/>
-      <c r="D407" s="26" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A408" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B408" t="s">
-        <v>140</v>
-      </c>
-      <c r="C408" s="2"/>
-      <c r="D408" s="10" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="B409" t="s">
-        <v>499</v>
-      </c>
-      <c r="C409" s="2" t="s">
-        <v>523</v>
+        <v>140</v>
       </c>
       <c r="D409" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A410" s="2" t="s">
-        <v>530</v>
+      <c r="A410" t="s">
+        <v>115</v>
       </c>
       <c r="B410" t="s">
-        <v>499</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D410" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A411" s="30" t="s">
-        <v>537</v>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A411" s="2" t="s">
+        <v>547</v>
       </c>
       <c r="B411" t="s">
-        <v>499</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D411" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A412" s="30" t="s">
-        <v>538</v>
+        <v>140</v>
+      </c>
+      <c r="D411" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B412" t="s">
         <v>499</v>
       </c>
       <c r="C412" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D412" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B413" t="s">
+        <v>499</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D413" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B414" t="s">
+        <v>499</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D414" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B415" t="s">
+        <v>499</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D415" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B416" t="s">
+        <v>499</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D416" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B417" t="s">
+        <v>499</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D417" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B418" t="s">
+        <v>499</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D418" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A419" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B419" t="s">
+        <v>140</v>
+      </c>
+      <c r="C419" s="2"/>
+      <c r="D419" s="26" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A420" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B420" t="s">
+        <v>140</v>
+      </c>
+      <c r="C420" s="2"/>
+      <c r="D420" s="10" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B421" t="s">
+        <v>499</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D421" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B422" t="s">
+        <v>499</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D422" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A423" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B423" t="s">
+        <v>499</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D423" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A424" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="B424" t="s">
+        <v>499</v>
+      </c>
+      <c r="C424" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D412" t="s">
+      <c r="D424" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A413" s="28" t="s">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="28" t="s">
         <v>520</v>
       </c>
-      <c r="B413" s="28" t="s">
+      <c r="B425" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D413" s="29"/>
-    </row>
-    <row r="414" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A414" s="31" t="s">
+      <c r="D425" s="29"/>
+    </row>
+    <row r="426" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A426" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="B414" s="28" t="s">
+      <c r="B426" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A415" s="28" t="s">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="28" t="s">
         <v>534</v>
       </c>
-      <c r="B415" s="28" t="s">
+      <c r="B427" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A416" s="32" t="s">
+    <row r="428" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A428" s="32" t="s">
         <v>535</v>
       </c>
-      <c r="B416" s="28" t="s">
+      <c r="B428" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A417" s="31" t="s">
+    <row r="429" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A429" s="31" t="s">
         <v>527</v>
       </c>
-      <c r="B417" s="28" t="s">
+      <c r="B429" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A418" s="31" t="s">
+    <row r="430" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A430" s="31" t="s">
         <v>529</v>
       </c>
-      <c r="B418" s="28" t="s">
+      <c r="B430" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A419" s="10" t="s">
+    <row r="431" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A431" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="B419" s="28" t="s">
+      <c r="B431" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C419" s="2"/>
-    </row>
-    <row r="420" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A420" s="31" t="s">
+      <c r="C431" s="2"/>
+    </row>
+    <row r="432" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A432" s="31" t="s">
         <v>528</v>
       </c>
-      <c r="B420" s="28" t="s">
+      <c r="B432" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A421" s="32" t="s">
+    <row r="433" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A433" s="32" t="s">
         <v>536</v>
       </c>
-      <c r="B421" s="28" t="s">
+      <c r="B433" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C421" s="10"/>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A422" s="28" t="s">
+      <c r="C433" s="10"/>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434" s="28" t="s">
         <v>521</v>
       </c>
-      <c r="B422" s="28" t="s">
+      <c r="B434" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C422" s="28"/>
-      <c r="D422" s="29"/>
-    </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A423" s="2" t="s">
+      <c r="C434" s="28"/>
+      <c r="D434" s="29"/>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B423" s="2" t="s">
+      <c r="B435" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C423" s="2" t="s">
+      <c r="C435" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A424" s="2" t="s">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B424" s="2" t="s">
+      <c r="B436" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C424" s="2" t="s">
+      <c r="C436" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A425" s="2" t="s">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B425" s="2" t="s">
+      <c r="B437" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C425" s="2" t="s">
+      <c r="C437" s="2" t="s">
         <v>525</v>
       </c>
     </row>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7977D509-C76A-44CF-A89E-AFB9B54262F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B5D175-2FF5-41FB-B51E-8968E44ABDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="765">
   <si>
     <t>tag_name</t>
   </si>
@@ -2238,12 +2238,229 @@
   <si>
     <t>@total_population_size</t>
   </si>
+  <si>
+    <t>@total_population_size_strata</t>
+  </si>
+  <si>
+    <t>@inc_muac_children</t>
+  </si>
+  <si>
+    <t>@inc_iycfe</t>
+  </si>
+  <si>
+    <t>@inc_muac_plw</t>
+  </si>
+  <si>
+    <t>@inc_cdr</t>
+  </si>
+  <si>
+    <t>@inc_u5dr</t>
+  </si>
+  <si>
+    <t>ind_muac_children</t>
+  </si>
+  <si>
+    <t>ind_iycfe</t>
+  </si>
+  <si>
+    <t>ind_cdr</t>
+  </si>
+  <si>
+    <t>ind_u5dr</t>
+  </si>
+  <si>
+    <t>ind_muac_plw</t>
+  </si>
+  <si>
+    <t>@inc_ecfies</t>
+  </si>
+  <si>
+    <t>ind_ecfies</t>
+  </si>
+  <si>
+    <t>@inc_measles_vaccination</t>
+  </si>
+  <si>
+    <t>@inc_vitamin_a_coverage</t>
+  </si>
+  <si>
+    <t>ind_measles_vaccination</t>
+  </si>
+  <si>
+    <t>ind_vitamin_a_coverage</t>
+  </si>
+  <si>
+    <t>@text_ind_muac_children</t>
+  </si>
+  <si>
+    <t>@text_ind_muac_plw</t>
+  </si>
+  <si>
+    <t>@text_ind_measles_vaccination</t>
+  </si>
+  <si>
+    <t>@text_ind_vitamin_a_coverage</t>
+  </si>
+  <si>
+    <t>@text_ind_ecfies</t>
+  </si>
+  <si>
+    <t>@text_ind_iycfe</t>
+  </si>
+  <si>
+    <t>@text_ind_cdr</t>
+  </si>
+  <si>
+    <t>@text_ind_u5dr</t>
+  </si>
+  <si>
+    <t>All sampled households within the target population</t>
+  </si>
+  <si>
+    <t>All children 6-59 months of age within sampled households</t>
+  </si>
+  <si>
+    <t>All children 9-59 months of age within sampled households</t>
+  </si>
+  <si>
+    <t>All children 0-23 months of age within sampled households</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All women 15-49 years of age that are pregnant or breastfeeding a child 0-5 months of age within sampled households </t>
+  </si>
+  <si>
+    <t>All individuals within sampled households</t>
+  </si>
+  <si>
+    <t>@header_poptable_population</t>
+  </si>
+  <si>
+    <t>@header_poptable_indicator</t>
+  </si>
+  <si>
+    <t>Indicator(s)</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>@text_ind_general_population</t>
+  </si>
+  <si>
+    <t>General Household Indicators</t>
+  </si>
+  <si>
+    <t>@text_indname_general</t>
+  </si>
+  <si>
+    <t>@text_indname_muac_children</t>
+  </si>
+  <si>
+    <t>@text_indname_vitamin_a_coverage</t>
+  </si>
+  <si>
+    <t>@text_indname_ecfies</t>
+  </si>
+  <si>
+    <t>@text_indname_iycfe</t>
+  </si>
+  <si>
+    <t>@text_indname_muac_plw</t>
+  </si>
+  <si>
+    <t>@text_indname_cdr</t>
+  </si>
+  <si>
+    <t>@text_indname_u5dr</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC</t>
+  </si>
+  <si>
+    <t>Measles Vaccination Coverage</t>
+  </si>
+  <si>
+    <t>Vitamin A Supplementation Coverage</t>
+  </si>
+  <si>
+    <t>Early Childhood Food Insecurity Scale (ECFIES)</t>
+  </si>
+  <si>
+    <t>Infant and Young Child Feeding in Emergencies (IYCF-E) Questions</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC for Pregnant and Lactating Women</t>
+  </si>
+  <si>
+    <t>Crude Death Rate</t>
+  </si>
+  <si>
+    <t>Under-5 Death Rate</t>
+  </si>
+  <si>
+    <t>@text_population_of_interest</t>
+  </si>
+  <si>
+    <t>@text_population_strata</t>
+  </si>
+  <si>
+    <t>multiple_strata</t>
+  </si>
+  <si>
+    <t>This assessment will assess @total_population_size_strata .</t>
+  </si>
+  <si>
+    <t>@text_indname_measles_vaccination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The population of interest is @total_population_size people. @text_population_strata . @geographic_coverage .
+Within this population, specific indicators will target sub-populations, including: </t>
+  </si>
+  <si>
+    <t>@header_household_surveys</t>
+  </si>
+  <si>
+    <t>@header_sample_size</t>
+  </si>
+  <si>
+    <t>Household surveys</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t>@header_site_selection_methods</t>
+  </si>
+  <si>
+    <t>Site Selection Methods</t>
+  </si>
+  <si>
+    <t>@text_site_selection_srs</t>
+  </si>
+  <si>
+    <t>@text_site_selection_systematic</t>
+  </si>
+  <si>
+    <t>@site_selection_exhaustive</t>
+  </si>
+  <si>
+    <t>@site_selection_purposive</t>
+  </si>
+  <si>
+    <t>@text_site_selection_cluster</t>
+  </si>
+  <si>
+    <t>@text_site_selection_noncluster</t>
+  </si>
+  <si>
+    <t>Due to a lack of reliable population data, sites will be selected with simple random sampling with each site having an equal change of selection.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2401,6 +2618,12 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2428,7 +2651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2490,6 +2713,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2793,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D437"/>
+  <dimension ref="A1:D467"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -6771,430 +7001,858 @@
         <v>691</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" ht="66" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B392" t="s">
+        <v>140</v>
+      </c>
+      <c r="C392" s="2"/>
+      <c r="D392" s="40" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A393" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B393" t="s">
         <v>141</v>
       </c>
-      <c r="C392" s="2"/>
-      <c r="D392" s="27"/>
-    </row>
-    <row r="393" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A393" s="2"/>
       <c r="C393" s="2"/>
       <c r="D393" s="27"/>
     </row>
     <row r="394" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A394" s="2"/>
-      <c r="C394" s="2"/>
-      <c r="D394" s="27"/>
+      <c r="A394" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B394" t="s">
+        <v>140</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D394" s="27" t="s">
+        <v>749</v>
+      </c>
     </row>
     <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A395" s="2"/>
+      <c r="A395" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B395" t="s">
+        <v>141</v>
+      </c>
       <c r="C395" s="2"/>
       <c r="D395" s="27"/>
     </row>
     <row r="396" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A396" s="2"/>
-      <c r="C396" s="2"/>
+      <c r="A396" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B396" t="s">
+        <v>302</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>699</v>
+      </c>
       <c r="D396" s="27"/>
     </row>
     <row r="397" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A397" s="2"/>
-      <c r="C397" s="2"/>
+      <c r="A397" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B397" t="s">
+        <v>302</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>708</v>
+      </c>
       <c r="D397" s="27"/>
     </row>
     <row r="398" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A398" s="2"/>
-      <c r="C398" s="2"/>
+      <c r="A398" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B398" t="s">
+        <v>302</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>709</v>
+      </c>
       <c r="D398" s="27"/>
     </row>
     <row r="399" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A399" s="2"/>
-      <c r="C399" s="2"/>
+      <c r="A399" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B399" t="s">
+        <v>302</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>705</v>
+      </c>
       <c r="D399" s="27"/>
     </row>
     <row r="400" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A400" s="2"/>
-      <c r="C400" s="2"/>
+      <c r="A400" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B400" t="s">
+        <v>302</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>700</v>
+      </c>
       <c r="D400" s="27"/>
     </row>
     <row r="401" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A401" s="2"/>
-      <c r="C401" s="2"/>
+      <c r="A401" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B401" t="s">
+        <v>302</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>703</v>
+      </c>
       <c r="D401" s="27"/>
     </row>
     <row r="402" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A402" s="2"/>
-      <c r="C402" s="2"/>
+      <c r="A402" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B402" t="s">
+        <v>302</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>701</v>
+      </c>
       <c r="D402" s="27"/>
     </row>
     <row r="403" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A403" s="2"/>
-      <c r="C403" s="2"/>
+      <c r="A403" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B403" t="s">
+        <v>302</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>702</v>
+      </c>
       <c r="D403" s="27"/>
     </row>
-    <row r="404" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A404" s="2"/>
+    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A404" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B404" t="s">
+        <v>140</v>
+      </c>
       <c r="C404" s="2"/>
-      <c r="D404" s="27"/>
-    </row>
-    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D404" s="26" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A405" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B405" t="s">
+        <v>140</v>
+      </c>
+      <c r="C405" s="2"/>
+      <c r="D405" s="26" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>549</v>
+        <v>730</v>
       </c>
       <c r="B406" t="s">
         <v>140</v>
       </c>
-      <c r="D406" s="26" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C406" s="2"/>
+      <c r="D406" s="38" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>550</v>
+        <v>731</v>
       </c>
       <c r="B407" t="s">
         <v>140</v>
       </c>
-      <c r="D407" s="27" t="s">
-        <v>552</v>
+      <c r="C407" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D407" s="39" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
-        <v>114</v>
+      <c r="A408" s="2" t="s">
+        <v>750</v>
       </c>
       <c r="B408" t="s">
-        <v>511</v>
+        <v>140</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D408" s="39" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>553</v>
+        <v>732</v>
       </c>
       <c r="B409" t="s">
         <v>140</v>
       </c>
-      <c r="D409" t="s">
-        <v>554</v>
+      <c r="C409" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D409" s="39" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>115</v>
+      <c r="A410" s="2" t="s">
+        <v>733</v>
       </c>
       <c r="B410" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D410" s="39" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>547</v>
+        <v>734</v>
       </c>
       <c r="B411" t="s">
         <v>140</v>
       </c>
-      <c r="D411" s="33" t="s">
-        <v>548</v>
+      <c r="C411" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D411" s="39" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>128</v>
+        <v>735</v>
       </c>
       <c r="B412" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D412" t="s">
-        <v>129</v>
+        <v>703</v>
+      </c>
+      <c r="D412" s="39" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>116</v>
+        <v>736</v>
       </c>
       <c r="B413" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D413" t="s">
-        <v>122</v>
+        <v>701</v>
+      </c>
+      <c r="D413" s="39" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>126</v>
+        <v>737</v>
       </c>
       <c r="B414" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D414" t="s">
-        <v>127</v>
+        <v>702</v>
+      </c>
+      <c r="D414" s="39" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>117</v>
+        <v>728</v>
       </c>
       <c r="B415" t="s">
-        <v>499</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D415" t="s">
-        <v>121</v>
+        <v>140</v>
+      </c>
+      <c r="C415" s="2"/>
+      <c r="D415" s="38" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>118</v>
+        <v>710</v>
       </c>
       <c r="B416" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D416" t="s">
-        <v>123</v>
+        <v>699</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>119</v>
+        <v>712</v>
       </c>
       <c r="B417" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D417" t="s">
-        <v>125</v>
+        <v>708</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>120</v>
+        <v>713</v>
       </c>
       <c r="B418" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D418" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>543</v>
+        <v>714</v>
       </c>
       <c r="B419" t="s">
         <v>140</v>
       </c>
-      <c r="C419" s="2"/>
-      <c r="D419" s="26" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C419" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>545</v>
+        <v>715</v>
       </c>
       <c r="B420" t="s">
         <v>140</v>
       </c>
-      <c r="C420" s="2"/>
-      <c r="D420" s="10" t="s">
-        <v>546</v>
+      <c r="C420" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>522</v>
+        <v>711</v>
       </c>
       <c r="B421" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D421" t="s">
-        <v>526</v>
+        <v>703</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>530</v>
+        <v>716</v>
       </c>
       <c r="B422" t="s">
+        <v>140</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B423" t="s">
+        <v>140</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A424" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B424" t="s">
+        <v>140</v>
+      </c>
+      <c r="D424" s="26" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A425" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B425" t="s">
+        <v>140</v>
+      </c>
+      <c r="D425" s="27" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>114</v>
+      </c>
+      <c r="B426" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B427" t="s">
+        <v>140</v>
+      </c>
+      <c r="D427" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>115</v>
+      </c>
+      <c r="B428" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A429" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B429" t="s">
+        <v>140</v>
+      </c>
+      <c r="D429" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B430" t="s">
         <v>499</v>
       </c>
-      <c r="C422" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D422" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A423" s="30" t="s">
-        <v>537</v>
-      </c>
-      <c r="B423" t="s">
+      <c r="C430" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D430" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B431" t="s">
         <v>499</v>
       </c>
-      <c r="C423" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D423" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A424" s="30" t="s">
-        <v>538</v>
-      </c>
-      <c r="B424" t="s">
+      <c r="C431" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D431" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B432" t="s">
         <v>499</v>
       </c>
-      <c r="C424" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D424" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A425" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="B425" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="D425" s="29"/>
-    </row>
-    <row r="426" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A426" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="B426" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A427" s="28" t="s">
-        <v>534</v>
-      </c>
-      <c r="B427" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A428" s="32" t="s">
-        <v>535</v>
-      </c>
-      <c r="B428" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A429" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="B429" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A430" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="B430" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A431" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="B431" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C431" s="2"/>
-    </row>
-    <row r="432" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A432" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="B432" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="433" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A433" s="32" t="s">
-        <v>536</v>
-      </c>
-      <c r="B433" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C433" s="10"/>
+      <c r="C432" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D432" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B433" t="s">
+        <v>499</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D433" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A434" s="28" t="s">
-        <v>521</v>
-      </c>
-      <c r="B434" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C434" s="28"/>
-      <c r="D434" s="29"/>
+      <c r="A434" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B434" t="s">
+        <v>499</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D434" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B435" s="2" t="s">
-        <v>542</v>
+        <v>119</v>
+      </c>
+      <c r="B435" t="s">
+        <v>499</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
+      </c>
+      <c r="D435" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B436" t="s">
+        <v>499</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D436" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A437" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B437" t="s">
+        <v>140</v>
+      </c>
+      <c r="C437" s="2"/>
+      <c r="D437" s="26" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A438" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B438" t="s">
+        <v>140</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" s="10" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A439" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B439" t="s">
+        <v>140</v>
+      </c>
+      <c r="C439" s="2"/>
+      <c r="D439" s="10" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A440" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B440" t="s">
+        <v>140</v>
+      </c>
+      <c r="C440" s="2"/>
+      <c r="D440" s="10" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B441" t="s">
+        <v>499</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D441" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B442" t="s">
+        <v>499</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D442" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A443" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B443" t="s">
+        <v>499</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D443" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A444" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="B444" t="s">
+        <v>499</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D444" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B445" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D445" s="29"/>
+    </row>
+    <row r="446" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A446" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B446" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="B447" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A448" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="B448" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A449" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="B449" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A450" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B450" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A451" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B451" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C451" s="2"/>
+    </row>
+    <row r="452" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A452" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="B452" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A453" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="B453" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C453" s="10"/>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="B454" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C454" s="28"/>
+      <c r="D454" s="29"/>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C455" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B436" s="2" t="s">
+      <c r="B456" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C436" s="2" t="s">
+      <c r="C456" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A437" s="2" t="s">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B437" s="2" t="s">
+      <c r="B457" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C437" s="2" t="s">
+      <c r="C457" s="2" t="s">
         <v>525</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A458" s="2"/>
+      <c r="C458" s="2"/>
+      <c r="D458" s="10"/>
+    </row>
+    <row r="459" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A459" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B459" t="s">
+        <v>140</v>
+      </c>
+      <c r="C459" s="2"/>
+      <c r="D459" s="10" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A460" s="2"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="10"/>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A463" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D463" s="10" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="2" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B5D175-2FF5-41FB-B51E-8968E44ABDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA6647F-01F9-4D99-9E7E-337BD841E90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="936">
   <si>
     <t>tag_name</t>
   </si>
@@ -1786,9 +1786,6 @@
     <t>Sample sizes were calculated at a 95% confidence level in @r_version for both @ind_indicator and @rate_indicator with the highest sample size between the two indicators being selected per strata. The sampling parameters for each parameter are summarized in the tables below. The resulting final household sample size across strata is @sample_size_hh_final.</t>
   </si>
   <si>
-    <t>conditional_table</t>
-  </si>
-  <si>
     <t>@header_primary_data_collection</t>
   </si>
   <si>
@@ -1960,15 +1957,6 @@
     <t>systematic_site_selection, rlc_household_selection,multiple_methods_yes</t>
   </si>
   <si>
-    <t>proportional_site_selection, srs_household_selection,multiple_methods_yes</t>
-  </si>
-  <si>
-    <t>proportional_site_selection, systematic_household_selection,multiple_methods_yes</t>
-  </si>
-  <si>
-    <t>proportional_site_selection, rlc_household_selection,multiple_methods_yes</t>
-  </si>
-  <si>
     <t>cluster_site_selection, srs_household_selection,multiple_methods_yes</t>
   </si>
   <si>
@@ -2005,15 +1993,6 @@
     <t>systematic_site_selection, rlc_household_selection,multiple_methods_no</t>
   </si>
   <si>
-    <t>proportional_site_selection, srs_household_selection,multiple_methods_no</t>
-  </si>
-  <si>
-    <t>proportional_site_selection, systematic_household_selection,multiple_methods_no</t>
-  </si>
-  <si>
-    <t>proportional_site_selection, rlc_household_selection,multiple_methods_no</t>
-  </si>
-  <si>
     <t>cluster_site_selection, srs_household_selection,multiple_methods_no</t>
   </si>
   <si>
@@ -2413,54 +2392,669 @@
     <t>@text_indname_measles_vaccination</t>
   </si>
   <si>
+    <t>@header_household_surveys</t>
+  </si>
+  <si>
+    <t>@header_sample_size</t>
+  </si>
+  <si>
+    <t>Household surveys</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t>@header_site_selection_methods</t>
+  </si>
+  <si>
+    <t>@text_site_selection_srs</t>
+  </si>
+  <si>
+    <t>@text_site_selection_systematic</t>
+  </si>
+  <si>
+    <t>@site_selection_exhaustive</t>
+  </si>
+  <si>
+    <t>@site_selection_purposive</t>
+  </si>
+  <si>
+    <t>@text_site_selection_cluster</t>
+  </si>
+  <si>
+    <t>@strata_names</t>
+  </si>
+  <si>
+    <t>@cluster_size</t>
+  </si>
+  <si>
+    <t>systematic_site_selection</t>
+  </si>
+  <si>
+    <t>srs_site_selection</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, srs_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, systematic_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, rlc_household_selection,multiple_methods_no</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, srs_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, systematic_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection, rlc_household_selection,multiple_methods_yes</t>
+  </si>
+  <si>
+    <t>exhaustive_site_selection</t>
+  </si>
+  <si>
+    <t>A total of @n_sites sites will be selected for the assessment covering @strata_names . Due to a lack of reliable population data, these sites will be selected with simple random sampling with each site having an equal change of selection. This method for site selection is only applicable when no population data is available, however teams must evaluate population size, find estimates at field level, or evaluate relative population size between sites for later analysis. The sample will be evenly allocated across selected sites with @cluster_size households planned per site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A total of @n_sites sites will be selected for the assessment covering @strata_names . Due to a lack of reliable population data, these sites will be selected with systematic random sampling with the list of eligible sites being ordered geographically in a list from north to south or east to west, and sites selected based on a sampling interval and random start. This method for site selection is only applicable when no population data is available, however teams must evaluate population size, find estimates at field level, or evaluate relative population size between sites for later analysis. The sample will be evenly allocated across selected sites with @cluster_size households planned per site. Data collection teams will find     
+•	Ordering the Sampling Frame – Order the sites in the sampling frame geographically either from north to south or east to west. This will help ensure some geographic representative. 
+•	Determining the sampling interval – This will be estimated by dividing the total number of eligible sites in the sampling frame by the number of required sites. 
+o	E.g. 42 sites total and 6 sites needed means sampling interval = 42 / 6 = 7. 
+•	Select the first sampling unit – To select a random start, randomly select a number N between 1-X, with X being the sampling interval. Starting from the top of the list, count to Nth site and that will be the first interview.
+o	E.g. randomly select the number 4 between 1 and 7… the 4th site will be the first one selected. 
+•	Select the following sampling units – From the 1st site selected, keep counting down the sampling frame  counting the number of sites equal to the sampling interval until you reach the next site to select. Continue doing this until you’ve selected all sites.
+o	E.g. First sites selected is #4, the 2nd selected is #11 (4+7), the 3rd household is #18 (11+7). 
+o	If the sampling interval has a decimal, you may need to adjust how you count to ensure you don’t run out of sites or exclude sites at the end of the sampling frame. The following rules can apply:
+	Decimal between 0 – 0.2, then round sampling interval down. E.g. with a sampling interval of 3.2; 1st site is 5, 2nd site is 5+3=8, 3rd site is 8+3=11.  
+	Decimal between 0.3 – 0.7, alternate between rounding sampling interval down and up. E.g. with a sampling interval of 3.5; 1st site is 5, 2nd site is 5+3=8, 3rd site is 8+4=12.  
+	Decimal between 0.8 – 0.9, then round sampling interval up. E.g. with a sampling interval of 3.9; 1st site is 5, 2nd site is 5+4=9, 3rd site is 9+4=13.  </t>
+  </si>
+  <si>
+    <t>All eligible sites will be exhaustively selected and included in the assessment for a total of @n_sites sites will be selected for the assessment covering @strata_names. The sample will be allocated across these sites proportional to the population size of these sites.</t>
+  </si>
+  <si>
+    <t>cluster_site_selection</t>
+  </si>
+  <si>
+    <t>A total of @n_sites PSUs/clusters will be selected using probability proportional to size (PPS) sampling with the probability of selection proportional the population size of the PSU, covering @strata_names. Sampling with replacement will be used meaning selected PSU may have the chance to have multiple survey clusters. Each PSU/cluster will have a set cluster size of @cluster_size households.</t>
+  </si>
+  <si>
+    <t>A total of @n_sites sites will be selected purposively based on their accessibility at the time of assessment. The sample will be equally distributed across sites with @cluster_size households per site. [PLEASE UPDATE FOR SELECTION CRITERIA].</t>
+  </si>
+  <si>
+    <t>purposive_site_selection</t>
+  </si>
+  <si>
+    <t>Site or Cluster Selection Methods</t>
+  </si>
+  <si>
+    <t>@header_household_selection_methods</t>
+  </si>
+  <si>
+    <t>Household selection methods</t>
+  </si>
+  <si>
     <t xml:space="preserve">The population of interest is @total_population_size people. @text_population_strata . @geographic_coverage .
-Within this population, specific indicators will target sub-populations, including: </t>
-  </si>
-  <si>
-    <t>@header_household_surveys</t>
-  </si>
-  <si>
-    <t>@header_sample_size</t>
-  </si>
-  <si>
-    <t>Household surveys</t>
-  </si>
-  <si>
-    <t>Sample Size</t>
-  </si>
-  <si>
-    <t>@header_site_selection_methods</t>
-  </si>
-  <si>
-    <t>Site Selection Methods</t>
-  </si>
-  <si>
-    <t>@text_site_selection_srs</t>
-  </si>
-  <si>
-    <t>@text_site_selection_systematic</t>
-  </si>
-  <si>
-    <t>@site_selection_exhaustive</t>
-  </si>
-  <si>
-    <t>@site_selection_purposive</t>
-  </si>
-  <si>
-    <t>@text_site_selection_cluster</t>
-  </si>
-  <si>
-    <t>@text_site_selection_noncluster</t>
-  </si>
-  <si>
-    <t>Due to a lack of reliable population data, sites will be selected with simple random sampling with each site having an equal change of selection.</t>
+Within this population, specific indicators will target sub-populations. All eligible sub-populations within sampled households will be included in the survey. Sub-populations for indicators include: </t>
+  </si>
+  <si>
+    <t>@text_household_selection_srs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within selected sites, households will be selected using simple random sampling methods. Acceptable options for field teams to implement simple random sampling will include (a) sampling from a pre-existing list or map at the community level, (b) creating a rapid listing of households with the support of community leaders, (c) creating a rapid map of households with the support of community leaders walking through the site. If a pre-existing list or map is used at the community level, supervisors should probe and ensure with community leaders that it is up to date with households that may have joined or left the community. 
+If the site has greater than 100 households, the team should segment the site into smaller manageable areas of 100 households or less. Supervisors should discuss with community leaders on how best to practically split up the community along roads, rivers, or other meaningful landmarks and estimating to the best of their ability the number of households per segment. The supervisor should utilize PPS sampling between these segments to select the number of PSUs needed for that site. 
+ The final list or map of households for the site, or within selected segments, should be numbered sequentially from 1-n. The teams should utilize a random number generator on a phone to randomly select @cluster_size households from the list or map. </t>
+  </si>
+  <si>
+    <t>srs_household_selection</t>
+  </si>
+  <si>
+    <t>systematic_household_selection</t>
+  </si>
+  <si>
+    <t>rlc_household_selection</t>
+  </si>
+  <si>
+    <t>@text_household_selection_rlc</t>
+  </si>
+  <si>
+    <t>@text_household_selection_systematic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within selected sites, @cluster_size households will be selected for each site/PSU/cluster using systematic random sampling. Systematic random sampling is used when households are arranged in an ordered fashion such as rows in camps or streets and the total number of units is known. . Systematic random sampling will be conducted with the following steps:
+•	Determining the sampling interval – This will be estimated by dividing the total number of households in the site by the X target households per site. 
+o	E.g. 960 households total and 30 households needed means sampling interval = 960 / 30 = 32. 
+•	Select the first sampling unit – To select a random start, randomly select a number N between 1-X, with X being the sampling interval. Starting from one side of the assessment site, count to Nth household and that will be the first interview.
+o	E.g. randomly select the number 5 between 1 and 32… the 5th household will be the first one interviewed. 
+•	Select the following sampling units – From the 1st household interviews, keeping moving along the ordered households counting the number of households equal to the sampling interval until you reach the next household to interview. Continue doing this until you’ve completed all your target households.
+o	E.g. First household interviewed is #5, the 2nd household is #37 (5+32), the 3rd household is #69 (37+32). 
+o	If the sampling interval has a decimal, you may need to adjust how you count households to ensure you don’t run out of households or miss households at the end of the site. The following rules can apply:
+	Decimal between 0 – 0.2, then round sampling interval down. E.g. with a sampling interval of 3.2; 1st household is 5, 2nd household is 5+3=8, 3rd household is 8+3=11.  
+	Decimal between 0.3 – 0.7, alternate between rounding sampling interval down and up. E.g. with a sampling interval of 3.5; 1st household is 5, 2nd household is 5+3=8, 3rd household is 8+4=12.  
+	Decimal between 0.8 – 0.9, then round sampling interval up. E.g. with a sampling interval of 3.9; 1st household is 5, 2nd household is 5+4=9, 3rd household is 9+4=13.  
+If the site has greater than 100 households, the team should segment the site into smaller manageable areas of 100 households or less. Supervisors should discuss with community leaders on how best to practically split up the community along roads, rivers, or other meaningful landmarks and estimating to the best of their ability the number of households per segment. The supervisor should utilize PPS sampling between these segments to select the number of PSUs needed for that site. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within selected sites, households will be selected using Random Location Cluster (RLC) sampling. In RLC sampling, random GPS points are generated within the boundary of selected sites. The boundaries and GPS points can be either set beforehand using GIS software, or while in the field with tools like REACH GeoRand. At each generated GPS points, enumerators are to start exactly, or as close as possible, to that point and then select the three physically closest households for interview. The enumerators should interview the selected household and then either (a) take the GPS point of that household or (b) estimate the approximate meters from the initial GPS point to the household. </t>
+  </si>
+  <si>
+    <t>@header_site_selection_special_situations</t>
+  </si>
+  <si>
+    <t>@header_site_selection_special_situation_actions</t>
+  </si>
+  <si>
+    <t>Special Situations</t>
+  </si>
+  <si>
+    <t>Actions</t>
+  </si>
+  <si>
+    <t>@text_site_selection_issue_inaccessible</t>
+  </si>
+  <si>
+    <t>@text_site_selection_action_inaccessible</t>
+  </si>
+  <si>
+    <t>The cluster or site is physically inaccessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the cluster or site is inaccessible to due insecurity, flooding, or other physical interference, then the assessment lead should be consulted and a new cluster or site selected from the set of available reserve sites/clusters. </t>
+  </si>
+  <si>
+    <t>The community leader refuses to allow the team to assess the cluster or site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the community leader refuses to allow the team to assess the cluster or site, even after explanation and discussion, then their wishes should be respected and the teams move to another site. The supervisor should inform the assessment lead the reasons for the refusal. The assessment lead should be consulted and a new cluster or site selected from the set of available reserve sites/clusters.  </t>
+  </si>
+  <si>
+    <t>@text_site_selection_issue_refusal</t>
+  </si>
+  <si>
+    <t>@text_site_selection_action_refusal</t>
+  </si>
+  <si>
+    <t>@text_site_selection_issue_abandoned</t>
+  </si>
+  <si>
+    <t>@text_site_selection_action_abandoned</t>
+  </si>
+  <si>
+    <t>@header_household_selection_special_situations</t>
+  </si>
+  <si>
+    <t>@header_household_selection_special_situation_actions</t>
+  </si>
+  <si>
+    <t>@inc_rlc</t>
+  </si>
+  <si>
+    <t>People try to select the household for you</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If community leaders or members try to influence which households are selected for interview, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>the supervisor or enumerators should explain that we have specific procedures we need to follow so the results are credible. If the interference persists and prevents proper sampling in the site, consult with the supervisor whether work should continue in that location.</t>
+    </r>
+  </si>
+  <si>
+    <t>Selected households refuse to participate</t>
+  </si>
+  <si>
+    <r>
+      <t>If the selected household refuses to participate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, they should still be counted as an interview and saved as non-consent and submitted. This counts towards your sample size as it was considered in your non-response rate or buffer. </t>
+    </r>
+  </si>
+  <si>
+    <t>Selected households are absent at time of selection</t>
+  </si>
+  <si>
+    <r>
+      <t>If the selected household is absent at the time of selection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, the field supervisor can evaluate whether the household is absent (household is just not at home) by asking neighbours. If time allows and the household can return during the fieldwork, the supervisor should instruct the team to interview the household later in the day. If time is not available, the supervisor should mark the household was not available and not replace the household. </t>
+    </r>
+  </si>
+  <si>
+    <t>Selected household is empty or abandoned</t>
+  </si>
+  <si>
+    <r>
+      <t>If the selected household has been abandoned</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, this means it should never have been eligible for selection. The supervisor can replace this household by standing in front of the household facing it, and selecting the next eligible household directly to the right of the abandoned household. </t>
+    </r>
+  </si>
+  <si>
+    <t>Selected structure has multiple families or households</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If the selected household/structure has multiple families, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">please check your household definition and use this to determine whether you are dealing with a single or multiple households. If multiple households, randomly choose which household to interview within the structure.  </t>
+    </r>
+  </si>
+  <si>
+    <t>Selected household has eligible children for MUAC who are absent at the time of assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the selected household has age eligible children for anthropometric measurements, such as MUAC, however they are not present at the time of the assessment, the supervisor should evaluate with the household the reason the child is absent and if it is possible for the child to be measured while the team is in the community. The supervisor should note the reason the child is absent, particularly if the child is in a stabilization center or other inpatient care. </t>
+  </si>
+  <si>
+    <t>GPS point falls on a building</t>
+  </si>
+  <si>
+    <t>If the generated GPS point falls on top of a multi-story building with multiple households or families, the supervisor should inquire as to the number of household or families living in the building, then randomly select one of them for interview. If conducting RLC sampling, randomly select three of the households. If the building is unstable or unsafe, please report to assessment lead to identify an alternative GPS point.</t>
+  </si>
+  <si>
+    <t>No households near GPS point</t>
+  </si>
+  <si>
+    <t>If the generated GPS point does not have any nearby households within 100 meters of the GPS point, then likely the GPS point was created in an unpopulated location. The supervisor should report this to the assessment lead to identify an alternative GPS point.</t>
+  </si>
+  <si>
+    <t>Less than three households near GPS point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If there are fewer than three households within 100 meters of the generated GPS point (with RLC sampling), please complete the household interviews with the available one or two households and report to the assessment lead that there were not enough nearby households to assess. You do not need to replace this location.  </t>
+  </si>
+  <si>
+    <t>No access to GPS point location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the survey team does not have physical access to the GPS point due to insecurity or private access that is refused, the supervisor should ascertain whether it is safe to continue the assessment in that location. If safe, they can start at the closest accessible location to the inaccessible GPS point. If not safe, then the supervisor can report to the assessment lead to replace the GPS point.  </t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_influence</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_influence</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_refusal</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_refusal</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_absent</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_absent</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_abandoned</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_abandoned</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_multiple</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_multiple</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_absent_child</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_absent_child</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_gps_building</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_gps_building</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_less_three_hh</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_less_three_hh</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_no_nearby_hh</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_no_nearby_hh</t>
+  </si>
+  <si>
+    <t>@text_household_selection_issue_no_access_gps</t>
+  </si>
+  <si>
+    <t>@text_household_selection_action_no_access_gps</t>
+  </si>
+  <si>
+    <t>@header_key_informant_interviews</t>
+  </si>
+  <si>
+    <t>Key Informant Interviews</t>
+  </si>
+  <si>
+    <t>@text_intro_key_informant_interviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are several core and supplemental key informant tools within the IPHRA toolkit, however for the purposes of this assessment the following key informant interviews are planned: </t>
+  </si>
+  <si>
+    <t>@header_kii_tool_name</t>
+  </si>
+  <si>
+    <t>@header_kii_information_assessed</t>
+  </si>
+  <si>
+    <t>@header_kii_number_kii_planned</t>
+  </si>
+  <si>
+    <t>Key Informant Interview Tool</t>
+  </si>
+  <si>
+    <t>Information Assessed</t>
+  </si>
+  <si>
+    <t>Number of KIIs Planned</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_community</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_health</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_nutrition</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_market</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_wash</t>
+  </si>
+  <si>
+    <t>@text_kii_tool_name_fsl</t>
+  </si>
+  <si>
+    <t>Community Leader and Community Member KII</t>
+  </si>
+  <si>
+    <t>Health Facility KII</t>
+  </si>
+  <si>
+    <t>Market Vendor KII</t>
+  </si>
+  <si>
+    <t>WASH Provider KII</t>
+  </si>
+  <si>
+    <t>FSL Assistance Provider KII</t>
+  </si>
+  <si>
+    <t>Nutrition Facility KII</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_community</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_health</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_nutrition</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_market</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_wash</t>
+  </si>
+  <si>
+    <t>@text_kii_information_assessed_fsl</t>
+  </si>
+  <si>
+    <t>Perceived priority needs, perception of vulnerable groups, main barriers and challenges to accessing basic needs and services</t>
+  </si>
+  <si>
+    <t>Health Service Adequacy</t>
+  </si>
+  <si>
+    <t>Nutrition Service Adequacy</t>
+  </si>
+  <si>
+    <t>Market Availability, Accessibility and Functionality</t>
+  </si>
+  <si>
+    <t>WASH Service Adequacy</t>
+  </si>
+  <si>
+    <t>Emergency FSL Programming Adequacy</t>
+  </si>
+  <si>
+    <t>At least one community leader per site or cluster, 1-2 male and 1-2 female community members per site or cluster</t>
+  </si>
+  <si>
+    <t>One interview per health facility serving the assessed population</t>
+  </si>
+  <si>
+    <t>One interview per nutrition site serving the assessed population</t>
+  </si>
+  <si>
+    <t>One to two interviews per market serving the assessed population</t>
+  </si>
+  <si>
+    <t>One interview per NGO providing FSL services</t>
+  </si>
+  <si>
+    <t>One interview per NGO providing WASH services</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_community</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_health</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_nutrition</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_market</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_wash</t>
+  </si>
+  <si>
+    <t>@text_kii_number_planned_fsl</t>
+  </si>
+  <si>
+    <t>@header_key_informant_selection_methods</t>
+  </si>
+  <si>
+    <t>Key Informant Selection Methods</t>
+  </si>
+  <si>
+    <t>Community leaders and specialized key informants such as market vendors, health facility staff, WASH or FSL service providers should be selected by purposive selection methods based on their leadership positions in the community or as service providers. Community members can act as informants and are included to balance out perspectives that may be missed if only community leaders are interviewed. A semi-random process can be used to randomly select community informants within selected sites. See IPHRA guidance for suggestions.
+In the event of specific at-risk or difficult to identify groups within the population, it may be necessary to identify key informants through snowball sampling by asking local service providers for referrals. Consider this if there are specific groups that you want their views represented in the assessment.</t>
+  </si>
+  <si>
+    <t>@text_key_informant_selection_methods</t>
+  </si>
+  <si>
+    <t>@header_observation_tools</t>
+  </si>
+  <si>
+    <t>Observation Tools</t>
+  </si>
+  <si>
+    <t>@text_intro_observation_tools</t>
+  </si>
+  <si>
+    <t>There are several core and supplemental observation checklist tools within the IPHRA toolkit, however for the purposes of this assessment the following tools will be applied:</t>
+  </si>
+  <si>
+    <t>Observation Tool</t>
+  </si>
+  <si>
+    <t>Number of Observation Checklists Planned</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_name_community</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_name_water_point</t>
+  </si>
+  <si>
+    <t>@header_obs_tool_name</t>
+  </si>
+  <si>
+    <t>@header_obs_tool_information_assessed</t>
+  </si>
+  <si>
+    <t>@header_obs_tool_number_planned</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_name_latrine</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_name_health</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_name_crops_livestock</t>
+  </si>
+  <si>
+    <t>Crops and Livestock Tool</t>
+  </si>
+  <si>
+    <t>Natural and Built Environment; Living Conditions;</t>
+  </si>
+  <si>
+    <t>Natural and Built Environment (Sanitation)</t>
+  </si>
+  <si>
+    <t>Household Food Security (Availability), Livelihoods (Availability)</t>
+  </si>
+  <si>
+    <t>1 per assessment location</t>
+  </si>
+  <si>
+    <t>1x per water point serving assessed location</t>
+  </si>
+  <si>
+    <t>1x per latrine stand serving assessed location</t>
+  </si>
+  <si>
+    <t>1 per health facility</t>
+  </si>
+  <si>
+    <t>If needed reach to PHU</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_information_assessed_community</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_information_assessed_water_point</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_information_assessed_latrine</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_information_assessed_health</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_information_assessed_crops_livestock</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_number_planned_community</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_number_planned_water_point</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_number_planned_latrine</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_number_planned_health</t>
+  </si>
+  <si>
+    <t>@text_obs_tool_number_planned_crops_livestock</t>
+  </si>
+  <si>
+    <t>@header_tool_obs_crops_livestock</t>
+  </si>
+  <si>
+    <t>@obs_crops_livestock_inc</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_crops_livestock_purposive</t>
+  </si>
+  <si>
+    <t>@sampling_obs_crops_livestock_purposive</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_crops_livestock_other</t>
+  </si>
+  <si>
+    <t>@sampling_obs_crops_livestock_other</t>
+  </si>
+  <si>
+    <t>@header_sampling_obs_crops_livestock_target</t>
+  </si>
+  <si>
+    <t>@sampling_obs_crops_livestock_target</t>
+  </si>
+  <si>
+    <t>@num_obs_crops_livestock_target</t>
+  </si>
+  <si>
+    <t>Crops and Livestock Observation Tool</t>
+  </si>
+  <si>
+    <t>Crop/Livestock observations (Target #):</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2624,6 +3218,41 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2639,7 +3268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2647,11 +3276,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2720,6 +3377,27 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3023,7 +3701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D467"/>
+  <dimension ref="A1:D555"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -4706,7 +5384,7 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B173" t="s">
@@ -4828,7 +5506,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B186" t="s">
@@ -4903,7 +5581,7 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B195" t="s">
@@ -4984,7 +5662,7 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B204" t="s">
@@ -5068,7 +5746,7 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B213" t="s">
@@ -5236,7 +5914,7 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="A231" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B231" t="s">
@@ -5560,39 +6238,39 @@
         <v>171</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>424</v>
+        <v>925</v>
       </c>
       <c r="B266" t="s">
         <v>140</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>425</v>
+      <c r="D266" s="24" t="s">
+        <v>934</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>420</v>
+        <v>926</v>
       </c>
       <c r="B267" t="s">
-        <v>140</v>
-      </c>
-      <c r="D267" t="s">
-        <v>421</v>
+        <v>302</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>84</v>
+      <c r="A268" s="2" t="s">
+        <v>927</v>
       </c>
       <c r="B268" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="D268" s="22" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>85</v>
+      <c r="A269" s="2" t="s">
+        <v>928</v>
       </c>
       <c r="B269" t="s">
         <v>142</v>
@@ -5600,18 +6278,18 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>423</v>
+        <v>929</v>
       </c>
       <c r="B270" t="s">
         <v>140</v>
       </c>
-      <c r="D270" t="s">
-        <v>422</v>
+      <c r="D270" s="23" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>426</v>
+        <v>930</v>
       </c>
       <c r="B271" t="s">
         <v>142</v>
@@ -5619,59 +6297,56 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>427</v>
+        <v>931</v>
       </c>
       <c r="B272" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="D272" s="14" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>431</v>
+        <v>932</v>
       </c>
       <c r="B273" t="s">
-        <v>140</v>
-      </c>
-      <c r="D273" t="s">
-        <v>432</v>
+        <v>142</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>428</v>
+      <c r="A274" t="s">
+        <v>933</v>
       </c>
       <c r="B274" t="s">
-        <v>140</v>
-      </c>
-      <c r="D274" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B275" t="s">
         <v>140</v>
       </c>
-      <c r="D275" t="s">
-        <v>456</v>
+      <c r="D275" s="13" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B276" t="s">
         <v>140</v>
       </c>
-      <c r="D276" s="17" t="s">
-        <v>229</v>
+      <c r="D276" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B277" t="s">
         <v>142</v>
@@ -5679,216 +6354,231 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>85</v>
+      </c>
+      <c r="B278" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B279" t="s">
+        <v>140</v>
+      </c>
+      <c r="D279" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B280" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B281" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B282" t="s">
+        <v>140</v>
+      </c>
+      <c r="D282" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B283" t="s">
+        <v>140</v>
+      </c>
+      <c r="D283" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B284" t="s">
+        <v>140</v>
+      </c>
+      <c r="D284" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B285" t="s">
+        <v>140</v>
+      </c>
+      <c r="D285" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>86</v>
+      </c>
+      <c r="B286" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
         <v>87</v>
       </c>
-      <c r="B278" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="B287" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
         <v>88</v>
       </c>
-      <c r="B279" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A280" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="B280" t="s">
-        <v>140</v>
-      </c>
-      <c r="D280" s="7" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A281" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B281" t="s">
-        <v>140</v>
-      </c>
-      <c r="D281" s="10" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A282" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B282" t="s">
-        <v>140</v>
-      </c>
-      <c r="D282" s="10" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A283" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="B283" t="s">
-        <v>140</v>
-      </c>
-      <c r="D283" s="10" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A284" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B284" t="s">
-        <v>140</v>
-      </c>
-      <c r="D284" s="10" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A285" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B285" t="s">
-        <v>140</v>
-      </c>
-      <c r="D285" s="10" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>440</v>
-      </c>
-      <c r="B286" t="s">
-        <v>140</v>
-      </c>
-      <c r="D286" s="10" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A287" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B287" t="s">
-        <v>140</v>
-      </c>
-      <c r="D287" s="10" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A288" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="B288" t="s">
-        <v>140</v>
-      </c>
-      <c r="D288" s="10" t="s">
-        <v>452</v>
+        <v>142</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B289" t="s">
         <v>140</v>
       </c>
-      <c r="D289" s="10" t="s">
-        <v>453</v>
+      <c r="D289" s="7" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B290" t="s">
+        <v>140</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A291" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B291" t="s">
+        <v>140</v>
+      </c>
+      <c r="D291" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A292" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B292" t="s">
+        <v>140</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A293" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B293" t="s">
+        <v>140</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A294" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B294" t="s">
+        <v>140</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>440</v>
+      </c>
+      <c r="B295" t="s">
+        <v>140</v>
+      </c>
+      <c r="D295" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A296" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B296" t="s">
+        <v>140</v>
+      </c>
+      <c r="D296" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A297" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B297" t="s">
+        <v>140</v>
+      </c>
+      <c r="D297" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A298" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B298" t="s">
+        <v>140</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A299" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B290" t="s">
-        <v>140</v>
-      </c>
-      <c r="D290" s="17" t="s">
+      <c r="B299" t="s">
+        <v>140</v>
+      </c>
+      <c r="D299" s="17" t="s">
         <v>454</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>89</v>
-      </c>
-      <c r="B291" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>90</v>
-      </c>
-      <c r="B292" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>91</v>
-      </c>
-      <c r="B293" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>92</v>
-      </c>
-      <c r="B294" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>93</v>
-      </c>
-      <c r="B295" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>94</v>
-      </c>
-      <c r="B296" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>95</v>
-      </c>
-      <c r="B297" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>96</v>
-      </c>
-      <c r="B298" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>97</v>
-      </c>
-      <c r="B299" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B300" t="s">
         <v>142</v>
@@ -5896,1963 +6586,2966 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B301" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B302" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B303" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B304" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B305" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B306" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B307" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B308" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B309" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B310" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A311" s="2" t="s">
-        <v>457</v>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>100</v>
       </c>
       <c r="B311" t="s">
-        <v>140</v>
-      </c>
-      <c r="D311" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A312" s="2" t="s">
-        <v>458</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>101</v>
       </c>
       <c r="B312" t="s">
-        <v>140</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A313" s="2" t="s">
-        <v>459</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>102</v>
       </c>
       <c r="B313" t="s">
-        <v>140</v>
-      </c>
-      <c r="D313" s="10" t="s">
-        <v>462</v>
+        <v>171</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B314" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B315" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A316" s="2" t="s">
-        <v>463</v>
+      <c r="A316" t="s">
+        <v>105</v>
       </c>
       <c r="B316" t="s">
-        <v>140</v>
-      </c>
-      <c r="D316" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A317" s="2" t="s">
-        <v>464</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>106</v>
       </c>
       <c r="B317" t="s">
-        <v>140</v>
-      </c>
-      <c r="D317" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A318" s="2" t="s">
-        <v>465</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>107</v>
       </c>
       <c r="B318" t="s">
-        <v>140</v>
-      </c>
-      <c r="D318" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A319" s="2" t="s">
-        <v>466</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>108</v>
       </c>
       <c r="B319" t="s">
-        <v>140</v>
-      </c>
-      <c r="D319" s="25" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B320" t="s">
         <v>140</v>
       </c>
-      <c r="D320" s="25" t="s">
-        <v>472</v>
+      <c r="D320" s="8" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B321" t="s">
         <v>140</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B322" t="s">
         <v>140</v>
       </c>
-      <c r="D322" s="26" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A323" s="2" t="s">
-        <v>478</v>
+      <c r="D322" s="10" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>109</v>
       </c>
       <c r="B323" t="s">
-        <v>140</v>
-      </c>
-      <c r="D323" s="27" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A324" s="2" t="s">
-        <v>479</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>110</v>
       </c>
       <c r="B324" t="s">
-        <v>140</v>
-      </c>
-      <c r="D324" s="27" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="B325" t="s">
         <v>140</v>
       </c>
-      <c r="D325" s="27" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D325" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="B326" t="s">
         <v>140</v>
       </c>
-      <c r="D326" s="26" t="s">
-        <v>484</v>
+      <c r="D326" s="25" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="B327" t="s">
         <v>140</v>
       </c>
-      <c r="D327" s="27" t="s">
-        <v>485</v>
+      <c r="D327" s="25" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B328" t="s">
         <v>140</v>
       </c>
-      <c r="D328" s="27" t="s">
-        <v>486</v>
+      <c r="D328" s="25" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="B329" t="s">
         <v>140</v>
       </c>
-      <c r="D329" s="27" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D329" s="25" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="B330" t="s">
         <v>140</v>
       </c>
-      <c r="D330" s="26" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D330" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="B331" t="s">
         <v>140</v>
       </c>
-      <c r="D331" s="27" t="s">
-        <v>494</v>
+      <c r="D331" s="26" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="B332" t="s">
-        <v>499</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>609</v>
+        <v>140</v>
       </c>
       <c r="D332" s="27" t="s">
-        <v>507</v>
+        <v>477</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="B333" t="s">
-        <v>499</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>610</v>
+        <v>140</v>
       </c>
       <c r="D333" s="27" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B334" t="s">
-        <v>499</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>611</v>
+        <v>140</v>
       </c>
       <c r="D334" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>555</v>
+        <v>483</v>
       </c>
       <c r="B335" t="s">
-        <v>499</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D335" s="27" t="s">
-        <v>564</v>
+        <v>140</v>
+      </c>
+      <c r="D335" s="26" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>556</v>
+        <v>487</v>
       </c>
       <c r="B336" t="s">
-        <v>499</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>613</v>
+        <v>140</v>
       </c>
       <c r="D336" s="27" t="s">
-        <v>565</v>
+        <v>485</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B337" t="s">
-        <v>499</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>614</v>
+        <v>140</v>
       </c>
       <c r="D337" s="27" t="s">
-        <v>568</v>
+        <v>486</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>557</v>
+        <v>489</v>
       </c>
       <c r="B338" t="s">
-        <v>499</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>615</v>
+        <v>140</v>
       </c>
       <c r="D338" s="27" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>558</v>
+        <v>490</v>
       </c>
       <c r="B339" t="s">
-        <v>499</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="D339" s="27" t="s">
-        <v>567</v>
+        <v>140</v>
+      </c>
+      <c r="D339" s="26" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B340" t="s">
-        <v>499</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>617</v>
+        <v>140</v>
       </c>
       <c r="D340" s="27" t="s">
-        <v>569</v>
+        <v>494</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>559</v>
+        <v>501</v>
       </c>
       <c r="B341" t="s">
         <v>499</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="D341" s="27" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="B342" t="s">
         <v>499</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="D342" s="27" t="s">
-        <v>574</v>
+        <v>508</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B343" t="s">
         <v>499</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="D343" s="27" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B344" t="s">
         <v>499</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="D344" s="27" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B345" t="s">
         <v>499</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D345" s="34" t="s">
-        <v>571</v>
+        <v>609</v>
+      </c>
+      <c r="D345" s="27" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>563</v>
+        <v>497</v>
       </c>
       <c r="B346" t="s">
         <v>499</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="B347" t="s">
         <v>499</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>593</v>
+        <v>758</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A348" s="35" t="s">
-        <v>639</v>
+      <c r="A348" s="2" t="s">
+        <v>557</v>
       </c>
       <c r="B348" t="s">
         <v>499</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="D348" s="36" t="s">
-        <v>636</v>
+        <v>759</v>
+      </c>
+      <c r="D348" s="27" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A349" s="35" t="s">
-        <v>578</v>
+      <c r="A349" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="B349" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="D349" s="27"/>
+        <v>760</v>
+      </c>
+      <c r="D349" s="27" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="350" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A350" s="35" t="s">
-        <v>640</v>
+      <c r="A350" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="B350" t="s">
         <v>499</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D350" s="36" t="s">
-        <v>637</v>
+        <v>611</v>
+      </c>
+      <c r="D350" s="27" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A351" s="35" t="s">
-        <v>579</v>
+      <c r="A351" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="B351" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D351" s="27"/>
+        <v>612</v>
+      </c>
+      <c r="D351" s="27" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="352" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A352" s="35" t="s">
-        <v>641</v>
+      <c r="A352" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="B352" t="s">
         <v>499</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="D352" s="36" t="s">
-        <v>638</v>
+        <v>613</v>
+      </c>
+      <c r="D352" s="27" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A353" s="35" t="s">
-        <v>580</v>
+      <c r="A353" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="B353" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="D353" s="27"/>
-    </row>
-    <row r="354" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A354" s="35" t="s">
-        <v>642</v>
+        <v>614</v>
+      </c>
+      <c r="D353" s="27" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="B354" t="s">
         <v>499</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D354" s="36" t="s">
-        <v>625</v>
+        <v>615</v>
+      </c>
+      <c r="D354" s="34" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A355" s="35" t="s">
-        <v>581</v>
+      <c r="A355" s="2" t="s">
+        <v>562</v>
       </c>
       <c r="B355" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D355" s="27"/>
+        <v>616</v>
+      </c>
+      <c r="D355" s="27" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="356" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A356" s="35" t="s">
-        <v>643</v>
+      <c r="A356" s="2" t="s">
+        <v>575</v>
       </c>
       <c r="B356" t="s">
         <v>499</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D356" s="36" t="s">
-        <v>624</v>
+        <v>592</v>
+      </c>
+      <c r="D356" s="27" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A357" s="35" t="s">
-        <v>582</v>
+        <v>632</v>
       </c>
       <c r="B357" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D357" s="27"/>
+        <v>593</v>
+      </c>
+      <c r="D357" s="36" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="358" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A358" s="35" t="s">
-        <v>644</v>
+        <v>577</v>
       </c>
       <c r="B358" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D358" s="36" t="s">
-        <v>626</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="D358" s="27"/>
     </row>
     <row r="359" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A359" s="35" t="s">
-        <v>583</v>
+        <v>633</v>
       </c>
       <c r="B359" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D359" s="27"/>
+        <v>594</v>
+      </c>
+      <c r="D359" s="36" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="360" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A360" s="35" t="s">
-        <v>645</v>
+        <v>578</v>
       </c>
       <c r="B360" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D360" s="36" t="s">
-        <v>627</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="D360" s="27"/>
     </row>
     <row r="361" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A361" s="35" t="s">
-        <v>584</v>
+        <v>634</v>
       </c>
       <c r="B361" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D361" s="27"/>
+        <v>595</v>
+      </c>
+      <c r="D361" s="36" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="362" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A362" s="35" t="s">
-        <v>646</v>
+        <v>579</v>
       </c>
       <c r="B362" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D362" s="36" t="s">
-        <v>628</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="D362" s="27"/>
     </row>
     <row r="363" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A363" s="35" t="s">
-        <v>585</v>
+        <v>635</v>
       </c>
       <c r="B363" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D363" s="36"/>
+        <v>596</v>
+      </c>
+      <c r="D363" s="36" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="364" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A364" s="35" t="s">
-        <v>647</v>
+        <v>580</v>
       </c>
       <c r="B364" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D364" s="36" t="s">
-        <v>629</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="D364" s="27"/>
     </row>
     <row r="365" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A365" s="35" t="s">
-        <v>586</v>
+        <v>636</v>
       </c>
       <c r="B365" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D365" s="27"/>
+        <v>597</v>
+      </c>
+      <c r="D365" s="36" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="366" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A366" s="35" t="s">
-        <v>648</v>
+        <v>581</v>
       </c>
       <c r="B366" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="D366" s="36" t="s">
-        <v>630</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="D366" s="27"/>
     </row>
     <row r="367" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A367" s="35" t="s">
-        <v>587</v>
+        <v>637</v>
       </c>
       <c r="B367" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="D367" s="27"/>
+        <v>598</v>
+      </c>
+      <c r="D367" s="36" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="368" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A368" s="35" t="s">
-        <v>649</v>
+        <v>582</v>
       </c>
       <c r="B368" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D368" s="36" t="s">
-        <v>631</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="D368" s="27"/>
     </row>
     <row r="369" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A369" s="35" t="s">
-        <v>588</v>
+        <v>638</v>
       </c>
       <c r="B369" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D369" s="27"/>
+        <v>761</v>
+      </c>
+      <c r="D369" s="36" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="370" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A370" s="35" t="s">
-        <v>650</v>
+        <v>583</v>
       </c>
       <c r="B370" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D370" s="36" t="s">
-        <v>632</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="D370" s="27"/>
     </row>
     <row r="371" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A371" s="35" t="s">
-        <v>589</v>
+        <v>639</v>
       </c>
       <c r="B371" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D371" s="27"/>
+        <v>762</v>
+      </c>
+      <c r="D371" s="36" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="372" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A372" s="35" t="s">
-        <v>651</v>
+        <v>584</v>
       </c>
       <c r="B372" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="D372" s="36" t="s">
-        <v>633</v>
-      </c>
+        <v>762</v>
+      </c>
+      <c r="D372" s="36"/>
     </row>
     <row r="373" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A373" s="35" t="s">
-        <v>590</v>
+        <v>640</v>
       </c>
       <c r="B373" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="D373" s="27"/>
+        <v>763</v>
+      </c>
+      <c r="D373" s="36" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="374" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A374" s="35" t="s">
-        <v>652</v>
+        <v>585</v>
       </c>
       <c r="B374" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D374" s="36" t="s">
-        <v>634</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="D374" s="27"/>
     </row>
     <row r="375" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A375" s="35" t="s">
-        <v>591</v>
+        <v>641</v>
       </c>
       <c r="B375" t="s">
-        <v>141</v>
+        <v>499</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D375" s="27"/>
+        <v>599</v>
+      </c>
+      <c r="D375" s="36" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="376" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A376" s="35" t="s">
-        <v>653</v>
+        <v>586</v>
       </c>
       <c r="B376" t="s">
+        <v>141</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D376" s="27"/>
+    </row>
+    <row r="377" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A377" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="B377" t="s">
         <v>499</v>
       </c>
-      <c r="C376" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D376" s="36" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A377" s="36" t="s">
-        <v>592</v>
-      </c>
-      <c r="B377" t="s">
+      <c r="C377" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D377" s="36" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A378" s="35" t="s">
+        <v>587</v>
+      </c>
+      <c r="B378" t="s">
         <v>141</v>
       </c>
-      <c r="C377" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D377" s="27"/>
-    </row>
-    <row r="378" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A378" s="36" t="s">
-        <v>654</v>
-      </c>
-      <c r="B378" t="s">
-        <v>499</v>
-      </c>
       <c r="C378" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D378" s="27" t="s">
-        <v>655</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="D378" s="27"/>
     </row>
     <row r="379" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A379" s="37" t="s">
-        <v>657</v>
+      <c r="A379" s="35" t="s">
+        <v>643</v>
       </c>
       <c r="B379" t="s">
         <v>499</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D379" s="27" t="s">
-        <v>672</v>
+        <v>601</v>
+      </c>
+      <c r="D379" s="36" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A380" s="36" t="s">
-        <v>658</v>
+      <c r="A380" s="35" t="s">
+        <v>588</v>
       </c>
       <c r="B380" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="D380" s="27" t="s">
-        <v>668</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="D380" s="27"/>
     </row>
     <row r="381" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A381" s="2" t="s">
-        <v>659</v>
+      <c r="A381" s="35" t="s">
+        <v>644</v>
       </c>
       <c r="B381" t="s">
         <v>499</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="D381" s="27" t="s">
-        <v>667</v>
+        <v>602</v>
+      </c>
+      <c r="D381" s="36" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A382" s="2" t="s">
-        <v>660</v>
+      <c r="A382" s="35" t="s">
+        <v>589</v>
       </c>
       <c r="B382" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D382" s="27" t="s">
-        <v>669</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="D382" s="27"/>
     </row>
     <row r="383" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A383" s="2" t="s">
-        <v>661</v>
+      <c r="A383" s="35" t="s">
+        <v>645</v>
       </c>
       <c r="B383" t="s">
         <v>499</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D383" s="27" t="s">
-        <v>670</v>
+        <v>603</v>
+      </c>
+      <c r="D383" s="36" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A384" s="37" t="s">
-        <v>671</v>
+      <c r="A384" s="35" t="s">
+        <v>590</v>
       </c>
       <c r="B384" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="D384" s="27" t="s">
-        <v>676</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="D384" s="27"/>
     </row>
     <row r="385" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A385" s="37" t="s">
-        <v>673</v>
+      <c r="A385" s="35" t="s">
+        <v>646</v>
       </c>
       <c r="B385" t="s">
         <v>499</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D385" s="27" t="s">
-        <v>685</v>
+        <v>604</v>
+      </c>
+      <c r="D385" s="36" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A386" s="36" t="s">
-        <v>677</v>
+        <v>591</v>
       </c>
       <c r="B386" t="s">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D386" s="27" t="s">
-        <v>686</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="D386" s="27"/>
     </row>
     <row r="387" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A387" s="36" t="s">
-        <v>678</v>
+        <v>647</v>
       </c>
       <c r="B387" t="s">
         <v>499</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>680</v>
+        <v>649</v>
       </c>
       <c r="D387" s="27" t="s">
-        <v>687</v>
+        <v>648</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A388" s="2" t="s">
-        <v>683</v>
+      <c r="A388" s="37" t="s">
+        <v>650</v>
       </c>
       <c r="B388" t="s">
         <v>499</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="D388" s="27" t="s">
-        <v>688</v>
+        <v>665</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A389" s="2" t="s">
-        <v>684</v>
+      <c r="A389" s="36" t="s">
+        <v>651</v>
       </c>
       <c r="B389" t="s">
         <v>499</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>682</v>
+        <v>656</v>
       </c>
       <c r="D389" s="27" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>113</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A390" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="B390" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D390" s="27" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="B391" t="s">
-        <v>140</v>
-      </c>
-      <c r="C391" s="2"/>
-      <c r="D391" s="26" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" ht="66" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D391" s="27" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>746</v>
+        <v>654</v>
       </c>
       <c r="B392" t="s">
-        <v>140</v>
-      </c>
-      <c r="C392" s="2"/>
-      <c r="D392" s="40" t="s">
-        <v>751</v>
+        <v>499</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D392" s="27" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A393" s="2" t="s">
-        <v>692</v>
+      <c r="A393" s="37" t="s">
+        <v>664</v>
       </c>
       <c r="B393" t="s">
-        <v>141</v>
-      </c>
-      <c r="C393" s="2"/>
-      <c r="D393" s="27"/>
+        <v>499</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D393" s="27" t="s">
+        <v>669</v>
+      </c>
     </row>
     <row r="394" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A394" s="2" t="s">
-        <v>747</v>
+      <c r="A394" s="37" t="s">
+        <v>666</v>
       </c>
       <c r="B394" t="s">
-        <v>140</v>
+        <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>748</v>
+        <v>668</v>
       </c>
       <c r="D394" s="27" t="s">
-        <v>749</v>
+        <v>678</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A395" s="2" t="s">
-        <v>693</v>
+      <c r="A395" s="36" t="s">
+        <v>670</v>
       </c>
       <c r="B395" t="s">
-        <v>141</v>
-      </c>
-      <c r="C395" s="2"/>
-      <c r="D395" s="27"/>
+        <v>499</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D395" s="27" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="396" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A396" s="2" t="s">
-        <v>694</v>
+      <c r="A396" s="36" t="s">
+        <v>671</v>
       </c>
       <c r="B396" t="s">
-        <v>302</v>
+        <v>499</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="D396" s="27"/>
+        <v>673</v>
+      </c>
+      <c r="D396" s="27" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="397" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>706</v>
+        <v>676</v>
       </c>
       <c r="B397" t="s">
-        <v>302</v>
+        <v>499</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="D397" s="27"/>
+        <v>674</v>
+      </c>
+      <c r="D397" s="27" t="s">
+        <v>681</v>
+      </c>
     </row>
     <row r="398" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>707</v>
+        <v>677</v>
       </c>
       <c r="B398" t="s">
-        <v>302</v>
+        <v>499</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D398" s="27"/>
-    </row>
-    <row r="399" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A399" s="2" t="s">
-        <v>704</v>
+        <v>675</v>
+      </c>
+      <c r="D398" s="27" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>113</v>
       </c>
       <c r="B399" t="s">
-        <v>302</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D399" s="27"/>
-    </row>
-    <row r="400" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="B400" t="s">
-        <v>302</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D400" s="27"/>
-    </row>
-    <row r="401" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="C400" s="2"/>
+      <c r="D400" s="26" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="99" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>696</v>
+        <v>739</v>
       </c>
       <c r="B401" t="s">
-        <v>302</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D401" s="27"/>
+        <v>140</v>
+      </c>
+      <c r="C401" s="2"/>
+      <c r="D401" s="40" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="402" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B402" t="s">
-        <v>302</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>701</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C402" s="2"/>
       <c r="D402" s="27"/>
     </row>
     <row r="403" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B403" t="s">
+        <v>140</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D403" s="27" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A404" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B404" t="s">
+        <v>141</v>
+      </c>
+      <c r="C404" s="2"/>
+      <c r="D404" s="27"/>
+    </row>
+    <row r="405" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A405" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B405" t="s">
+        <v>302</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D405" s="27"/>
+    </row>
+    <row r="406" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A406" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B406" t="s">
+        <v>302</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D406" s="27"/>
+    </row>
+    <row r="407" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A407" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B407" t="s">
+        <v>302</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D407" s="27"/>
+    </row>
+    <row r="408" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A408" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B408" t="s">
+        <v>302</v>
+      </c>
+      <c r="C408" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B403" t="s">
+      <c r="D408" s="27"/>
+    </row>
+    <row r="409" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A409" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B409" t="s">
         <v>302</v>
       </c>
-      <c r="C403" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="D403" s="27"/>
-    </row>
-    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B404" t="s">
-        <v>140</v>
-      </c>
-      <c r="C404" s="2"/>
-      <c r="D404" s="26" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B405" t="s">
-        <v>140</v>
-      </c>
-      <c r="C405" s="2"/>
-      <c r="D405" s="26" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A406" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B406" t="s">
-        <v>140</v>
-      </c>
-      <c r="C406" s="2"/>
-      <c r="D406" s="38" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A407" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B407" t="s">
-        <v>140</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="D407" s="39" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A408" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="B408" t="s">
-        <v>140</v>
-      </c>
-      <c r="C408" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="D408" s="39" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A409" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="B409" t="s">
-        <v>140</v>
-      </c>
       <c r="C409" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D409" s="39" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+      <c r="D409" s="27"/>
+    </row>
+    <row r="410" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>733</v>
+        <v>689</v>
       </c>
       <c r="B410" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D410" s="39" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+      <c r="D410" s="27"/>
+    </row>
+    <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>734</v>
+        <v>690</v>
       </c>
       <c r="B411" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D411" s="39" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+      <c r="D411" s="27"/>
+    </row>
+    <row r="412" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>735</v>
+        <v>691</v>
       </c>
       <c r="B412" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D412" s="39" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+      <c r="D412" s="27"/>
+    </row>
+    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="B413" t="s">
         <v>140</v>
       </c>
-      <c r="C413" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D413" s="39" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C413" s="2"/>
+      <c r="D413" s="26" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="B414" t="s">
         <v>140</v>
       </c>
-      <c r="C414" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="D414" s="39" t="s">
-        <v>745</v>
+      <c r="C414" s="2"/>
+      <c r="D414" s="26" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B415" t="s">
         <v>140</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="38" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="B416" t="s">
         <v>140</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="D416" s="2" t="s">
-        <v>718</v>
+        <v>692</v>
+      </c>
+      <c r="D416" s="39" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>712</v>
+        <v>743</v>
       </c>
       <c r="B417" t="s">
         <v>140</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="D417" s="2" t="s">
-        <v>719</v>
+        <v>701</v>
+      </c>
+      <c r="D417" s="39" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="B418" t="s">
         <v>140</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D418" s="2" t="s">
-        <v>720</v>
+        <v>702</v>
+      </c>
+      <c r="D418" s="39" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B419" t="s">
         <v>140</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D419" s="2" t="s">
-        <v>719</v>
+        <v>698</v>
+      </c>
+      <c r="D419" s="39" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="B420" t="s">
         <v>140</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D420" s="2" t="s">
-        <v>721</v>
+        <v>693</v>
+      </c>
+      <c r="D420" s="39" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="B421" t="s">
         <v>140</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D421" s="2" t="s">
-        <v>721</v>
+        <v>696</v>
+      </c>
+      <c r="D421" s="39" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="B422" t="s">
         <v>140</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D422" s="2" t="s">
-        <v>722</v>
+        <v>694</v>
+      </c>
+      <c r="D422" s="39" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="B423" t="s">
         <v>140</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="D423" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+      <c r="D423" s="39" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>549</v>
+        <v>721</v>
       </c>
       <c r="B424" t="s">
         <v>140</v>
       </c>
-      <c r="D424" s="26" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C424" s="2"/>
+      <c r="D424" s="38" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>550</v>
+        <v>703</v>
       </c>
       <c r="B425" t="s">
         <v>140</v>
       </c>
-      <c r="D425" s="27" t="s">
-        <v>552</v>
+      <c r="C425" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
-        <v>114</v>
+      <c r="A426" s="2" t="s">
+        <v>705</v>
       </c>
       <c r="B426" t="s">
-        <v>511</v>
+        <v>140</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>553</v>
+        <v>706</v>
       </c>
       <c r="B427" t="s">
         <v>140</v>
       </c>
-      <c r="D427" t="s">
-        <v>554</v>
+      <c r="C427" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
-        <v>115</v>
+      <c r="A428" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="B428" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>547</v>
+        <v>708</v>
       </c>
       <c r="B429" t="s">
         <v>140</v>
       </c>
-      <c r="D429" s="33" t="s">
-        <v>548</v>
+      <c r="C429" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>128</v>
+        <v>704</v>
       </c>
       <c r="B430" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D430" t="s">
-        <v>129</v>
+        <v>696</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>116</v>
+        <v>709</v>
       </c>
       <c r="B431" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D431" t="s">
-        <v>122</v>
+        <v>694</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>126</v>
+        <v>710</v>
       </c>
       <c r="B432" t="s">
-        <v>499</v>
+        <v>140</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D432" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>117</v>
+        <v>548</v>
       </c>
       <c r="B433" t="s">
-        <v>499</v>
-      </c>
-      <c r="C433" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D433" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="D433" s="26" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>118</v>
+        <v>549</v>
       </c>
       <c r="B434" t="s">
-        <v>499</v>
-      </c>
-      <c r="C434" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D434" t="s">
-        <v>123</v>
+        <v>140</v>
+      </c>
+      <c r="D434" s="27" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A435" s="2" t="s">
-        <v>119</v>
+      <c r="A435" t="s">
+        <v>114</v>
       </c>
       <c r="B435" t="s">
-        <v>499</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D435" t="s">
-        <v>125</v>
+        <v>511</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>120</v>
+        <v>552</v>
       </c>
       <c r="B436" t="s">
+        <v>140</v>
+      </c>
+      <c r="D436" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>115</v>
+      </c>
+      <c r="B437" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A438" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B438" t="s">
+        <v>140</v>
+      </c>
+      <c r="D438" s="33" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B439" t="s">
         <v>499</v>
       </c>
-      <c r="C436" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D436" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B437" t="s">
-        <v>140</v>
-      </c>
-      <c r="C437" s="2"/>
-      <c r="D437" s="26" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="438" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A438" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B438" t="s">
-        <v>140</v>
-      </c>
-      <c r="C438" s="2"/>
-      <c r="D438" s="10" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="439" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A439" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="B439" t="s">
-        <v>140</v>
-      </c>
-      <c r="C439" s="2"/>
-      <c r="D439" s="10" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="440" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C439" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D439" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>753</v>
+        <v>116</v>
       </c>
       <c r="B440" t="s">
-        <v>140</v>
-      </c>
-      <c r="C440" s="2"/>
-      <c r="D440" s="10" t="s">
-        <v>755</v>
+        <v>499</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D440" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>522</v>
+        <v>126</v>
       </c>
       <c r="B441" t="s">
         <v>499</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D441" t="s">
-        <v>526</v>
+        <v>127</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>530</v>
+        <v>117</v>
       </c>
       <c r="B442" t="s">
         <v>499</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D442" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="443" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A443" s="30" t="s">
-        <v>537</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B443" t="s">
         <v>499</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D443" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="444" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A444" s="30" t="s">
-        <v>538</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B444" t="s">
         <v>499</v>
       </c>
       <c r="C444" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D444" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B445" t="s">
+        <v>499</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D445" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A446" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B446" t="s">
+        <v>140</v>
+      </c>
+      <c r="C446" s="2"/>
+      <c r="D446" s="26" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A447" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B447" t="s">
+        <v>140</v>
+      </c>
+      <c r="C447" s="2"/>
+      <c r="D447" s="10" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A448" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B448" t="s">
+        <v>140</v>
+      </c>
+      <c r="C448" s="2"/>
+      <c r="D448" s="10" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A449" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B449" t="s">
+        <v>140</v>
+      </c>
+      <c r="C449" s="2"/>
+      <c r="D449" s="10" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B450" t="s">
+        <v>140</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D450" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B451" t="s">
+        <v>140</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D451" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A452" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B452" t="s">
+        <v>140</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D452" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A453" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="B453" t="s">
+        <v>140</v>
+      </c>
+      <c r="C453" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D444" t="s">
+      <c r="D453" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A445" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="B445" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="D445" s="29"/>
-    </row>
-    <row r="446" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A446" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="B446" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A447" s="28" t="s">
-        <v>534</v>
-      </c>
-      <c r="B447" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="448" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A448" s="32" t="s">
-        <v>535</v>
-      </c>
-      <c r="B448" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="449" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A449" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="B449" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="450" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A450" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="B450" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="451" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A451" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="B451" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C451" s="2"/>
-    </row>
-    <row r="452" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A452" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="B452" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="453" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A453" s="32" t="s">
-        <v>536</v>
-      </c>
-      <c r="B453" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C453" s="10"/>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B454" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C454" s="28"/>
       <c r="D454" s="29"/>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A455" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C455" s="2" t="s">
-        <v>523</v>
+    <row r="455" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A455" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B455" s="28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A456" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C456" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A457" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B457" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C457" s="2" t="s">
-        <v>525</v>
+      <c r="A456" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="B456" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A457" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="B457" s="28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A458" s="2"/>
-      <c r="C458" s="2"/>
-      <c r="D458" s="10"/>
+      <c r="A458" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="B458" s="28" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="459" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A459" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="B459" t="s">
-        <v>140</v>
-      </c>
-      <c r="C459" s="2"/>
-      <c r="D459" s="10" t="s">
-        <v>757</v>
+      <c r="A459" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B459" s="28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A460" s="2"/>
+      <c r="A460" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B460" s="28" t="s">
+        <v>141</v>
+      </c>
       <c r="C460" s="2"/>
-      <c r="D460" s="10"/>
-    </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A461" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="463" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A463" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="D463" s="10" t="s">
-        <v>764</v>
-      </c>
+    </row>
+    <row r="461" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A461" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="B461" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A462" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="B462" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C462" s="10"/>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="B463" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C463" s="28"/>
+      <c r="D463" s="29"/>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>761</v>
+        <v>748</v>
+      </c>
+      <c r="B467" t="s">
+        <v>140</v>
+      </c>
+      <c r="D467" s="10" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A468" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B468" t="s">
+        <v>140</v>
+      </c>
+      <c r="C468" t="s">
+        <v>757</v>
+      </c>
+      <c r="D468" s="10" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B469" t="s">
+        <v>140</v>
+      </c>
+      <c r="C469" t="s">
+        <v>756</v>
+      </c>
+      <c r="D469" s="41" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B470" t="s">
+        <v>140</v>
+      </c>
+      <c r="C470" t="s">
+        <v>764</v>
+      </c>
+      <c r="D470" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B471" t="s">
+        <v>140</v>
+      </c>
+      <c r="C471" t="s">
+        <v>768</v>
+      </c>
+      <c r="D471" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B472" t="s">
+        <v>140</v>
+      </c>
+      <c r="C472" t="s">
+        <v>771</v>
+      </c>
+      <c r="D472" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B473" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B474" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A475" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B475" t="s">
+        <v>140</v>
+      </c>
+      <c r="C475" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="D475" s="43" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A476" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B476" t="s">
+        <v>140</v>
+      </c>
+      <c r="D476" s="43" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B477" t="s">
+        <v>140</v>
+      </c>
+      <c r="D477" s="38" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B478" t="s">
+        <v>140</v>
+      </c>
+      <c r="D478" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B479" t="s">
+        <v>140</v>
+      </c>
+      <c r="D479" s="38" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B480" t="s">
+        <v>140</v>
+      </c>
+      <c r="D480" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B481" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B482" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A483" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B483" t="s">
+        <v>140</v>
+      </c>
+      <c r="D483" s="10" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B484" t="s">
+        <v>140</v>
+      </c>
+      <c r="C484" t="s">
+        <v>778</v>
+      </c>
+      <c r="D484" s="41" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B485" t="s">
+        <v>140</v>
+      </c>
+      <c r="C485" t="s">
+        <v>779</v>
+      </c>
+      <c r="D485" s="41" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B486" t="s">
+        <v>140</v>
+      </c>
+      <c r="C486" t="s">
+        <v>780</v>
+      </c>
+      <c r="D486" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A487" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B487" t="s">
+        <v>140</v>
+      </c>
+      <c r="C487" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="D487" s="43" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A488" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B488" t="s">
+        <v>140</v>
+      </c>
+      <c r="D488" s="43" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B489" t="s">
+        <v>140</v>
+      </c>
+      <c r="D489" s="38" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B490" t="s">
+        <v>140</v>
+      </c>
+      <c r="D490" s="44" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B491" t="s">
+        <v>140</v>
+      </c>
+      <c r="D491" s="38" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B492" t="s">
+        <v>140</v>
+      </c>
+      <c r="D492" s="45" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B493" t="s">
+        <v>140</v>
+      </c>
+      <c r="D493" s="38" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B494" t="s">
+        <v>140</v>
+      </c>
+      <c r="D494" s="45" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B495" t="s">
+        <v>140</v>
+      </c>
+      <c r="D495" s="38" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B496" t="s">
+        <v>140</v>
+      </c>
+      <c r="D496" s="45" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B497" t="s">
+        <v>140</v>
+      </c>
+      <c r="D497" s="38" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B498" t="s">
+        <v>140</v>
+      </c>
+      <c r="D498" s="45" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B499" t="s">
+        <v>140</v>
+      </c>
+      <c r="D499" s="39" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B500" t="s">
+        <v>140</v>
+      </c>
+      <c r="D500" s="38" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B501" t="s">
+        <v>140</v>
+      </c>
+      <c r="D501" s="39" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B502" t="s">
+        <v>140</v>
+      </c>
+      <c r="D502" s="38" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B503" t="s">
+        <v>140</v>
+      </c>
+      <c r="D503" s="39" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B504" t="s">
+        <v>140</v>
+      </c>
+      <c r="D504" s="38" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B505" t="s">
+        <v>140</v>
+      </c>
+      <c r="D505" s="39" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B506" t="s">
+        <v>140</v>
+      </c>
+      <c r="D506" s="38" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B507" t="s">
+        <v>140</v>
+      </c>
+      <c r="D507" s="39" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B508" t="s">
+        <v>140</v>
+      </c>
+      <c r="D508" s="38" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B509" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B510" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A511" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B511" t="s">
+        <v>140</v>
+      </c>
+      <c r="D511" s="46" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A512" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B512" t="s">
+        <v>140</v>
+      </c>
+      <c r="D512" s="47" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A513" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B513" t="s">
+        <v>140</v>
+      </c>
+      <c r="D513" s="43" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A514" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B514" t="s">
+        <v>140</v>
+      </c>
+      <c r="D514" s="43" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A515" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B515" t="s">
+        <v>140</v>
+      </c>
+      <c r="D515" s="43" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B516" t="s">
+        <v>140</v>
+      </c>
+      <c r="D516" s="38" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B517" t="s">
+        <v>140</v>
+      </c>
+      <c r="D517" s="38" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="B518" t="s">
+        <v>140</v>
+      </c>
+      <c r="D518" s="38" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B519" t="s">
+        <v>140</v>
+      </c>
+      <c r="D519" s="38" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B520" t="s">
+        <v>140</v>
+      </c>
+      <c r="D520" s="38" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B521" t="s">
+        <v>140</v>
+      </c>
+      <c r="D521" s="38" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B522" t="s">
+        <v>140</v>
+      </c>
+      <c r="D522" s="38" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B523" t="s">
+        <v>140</v>
+      </c>
+      <c r="D523" s="38" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B524" t="s">
+        <v>140</v>
+      </c>
+      <c r="D524" s="38" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B525" t="s">
+        <v>140</v>
+      </c>
+      <c r="D525" s="38" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B526" t="s">
+        <v>140</v>
+      </c>
+      <c r="D526" s="38" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B527" t="s">
+        <v>140</v>
+      </c>
+      <c r="D527" s="38" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A528" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B528" t="s">
+        <v>140</v>
+      </c>
+      <c r="D528" s="48" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A529" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B529" t="s">
+        <v>140</v>
+      </c>
+      <c r="D529" s="49" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B530" t="s">
+        <v>140</v>
+      </c>
+      <c r="D530" s="49" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B531" t="s">
+        <v>140</v>
+      </c>
+      <c r="D531" s="49" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B532" t="s">
+        <v>140</v>
+      </c>
+      <c r="D532" s="49" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A533" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B533" t="s">
+        <v>140</v>
+      </c>
+      <c r="D533" s="49" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A534" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B534" t="s">
+        <v>140</v>
+      </c>
+      <c r="D534" s="10" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" ht="210" x14ac:dyDescent="0.25">
+      <c r="A535" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B535" t="s">
+        <v>140</v>
+      </c>
+      <c r="D535" s="13" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A536" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B536" t="s">
+        <v>140</v>
+      </c>
+      <c r="D536" s="46" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A537" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B537" t="s">
+        <v>140</v>
+      </c>
+      <c r="D537" s="27" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A538" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B538" t="s">
+        <v>140</v>
+      </c>
+      <c r="D538" s="43" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A539" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B539" t="s">
+        <v>140</v>
+      </c>
+      <c r="D539" s="43" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A540" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B540" t="s">
+        <v>140</v>
+      </c>
+      <c r="D540" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A541" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B541" t="s">
+        <v>140</v>
+      </c>
+      <c r="D541" s="50" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A542" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B542" t="s">
+        <v>140</v>
+      </c>
+      <c r="D542" s="51" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A543" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B543" t="s">
+        <v>140</v>
+      </c>
+      <c r="D543" s="51" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A544" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B544" t="s">
+        <v>140</v>
+      </c>
+      <c r="D544" s="51" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A545" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B545" t="s">
+        <v>140</v>
+      </c>
+      <c r="D545" s="51" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A546" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B546" t="s">
+        <v>140</v>
+      </c>
+      <c r="D546" s="50" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B547" t="s">
+        <v>140</v>
+      </c>
+      <c r="D547" s="51" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B548" t="s">
+        <v>140</v>
+      </c>
+      <c r="D548" s="51" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A549" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="B549" t="s">
+        <v>140</v>
+      </c>
+      <c r="D549" s="51" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A550" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B550" t="s">
+        <v>140</v>
+      </c>
+      <c r="D550" s="51" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A551" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="B551" t="s">
+        <v>140</v>
+      </c>
+      <c r="D551" s="50" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A552" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B552" t="s">
+        <v>140</v>
+      </c>
+      <c r="D552" s="51" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A553" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B553" t="s">
+        <v>140</v>
+      </c>
+      <c r="D553" s="51" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B554" t="s">
+        <v>140</v>
+      </c>
+      <c r="D554" s="51" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A555" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B555" t="s">
+        <v>140</v>
+      </c>
+      <c r="D555" s="51" t="s">
+        <v>914</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA6647F-01F9-4D99-9E7E-337BD841E90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BF67D-99B0-49B8-99A6-0DE7E5559656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="986">
   <si>
     <t>tag_name</t>
   </si>
@@ -1708,12 +1708,6 @@
     <t>definition_muac</t>
   </si>
   <si>
-    <t>definition_cdr</t>
-  </si>
-  <si>
-    <t>definition_u5dr</t>
-  </si>
-  <si>
     <t>definition_complementary_feeding</t>
   </si>
   <si>
@@ -2240,12 +2234,6 @@
   </si>
   <si>
     <t>ind_iycfe</t>
-  </si>
-  <si>
-    <t>ind_cdr</t>
-  </si>
-  <si>
-    <t>ind_u5dr</t>
   </si>
   <si>
     <t>ind_muac_plw</t>
@@ -3048,6 +3036,175 @@
   </si>
   <si>
     <t>Crop/Livestock observations (Target #):</t>
+  </si>
+  <si>
+    <t>@num_enumerators_per_team</t>
+  </si>
+  <si>
+    <t>@num_days_data_collection</t>
+  </si>
+  <si>
+    <t>@text_training_mortality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dedicated session on collecting mortality data will be included. </t>
+  </si>
+  <si>
+    <t>@text_training_muac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An additional session will be included for training on MUAC measurements as well as a half day of training for a MUAC standardization test. </t>
+  </si>
+  <si>
+    <t>Team Composition, Training, and Quality Assurance</t>
+  </si>
+  <si>
+    <t>The exact composition of teams will depend on the number of tools being implemented. For household surveys, teams will consist of one field supervisor and @num_enumerators_per_team enumerators (@num_enumerators_per_team enumerators : 1 ratio). Where possible, teams should incorporate a mix of male and female enumerators. For key informant and observational tools, dedicated enumerators separate from the household survey enumerators will be selected and trained to implement them. One enumerator should not implement more than one or two specific tools to ensure adequate time for use in the field and data quality. 
+Teams will receive a base three-day training prior to data collection covering purpose of the survey, good interview practices and ethical conduct during public health assessment, field sampling procedures, and review of the survey, key informant and observational tools, and a one-day for pilot and planning activities. @text_training_mortality It is recommended to divide the team for separate tool review sessions to efficiently make use of training time. @text_training_muac 
+Field supervisors will have a key role in ensuring research quality during data collection. Key responsibilities will include:
+-	Providing daily feedback sessions to the data collection team
+-	Monitoring completion of assessment against planned targets
+-	Completing cluster control forms
+-	Ensuring proper household sampling techniques are applied
+-	Providing supportive supervision to enumerators</t>
+  </si>
+  <si>
+    <t>@header_team_comp_quality</t>
+  </si>
+  <si>
+    <t>@text_team_comp_quality</t>
+  </si>
+  <si>
+    <t>@header_data_collection_plan</t>
+  </si>
+  <si>
+    <t>Data Collection Plan</t>
+  </si>
+  <si>
+    <t>@text_intro_data_collection_plan</t>
+  </si>
+  <si>
+    <t>@data_collection_plan_table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The below table summarizes the planning assumptions for the household survey component of the IPHRA and the estimate for days needed to complete the assessment. Key informant and observation tools will be conducted simultaneously to the household survey. Overall, data collection will be conducted for @num_days_data_collection.   </t>
+  </si>
+  <si>
+    <t>mortality_survey</t>
+  </si>
+  <si>
+    <t>Household Survey</t>
+  </si>
+  <si>
+    <t>Data Processing &amp; Analysis</t>
+  </si>
+  <si>
+    <t>@header_data_processing_analysis</t>
+  </si>
+  <si>
+    <t>@header_kii_obs_analysis</t>
+  </si>
+  <si>
+    <t>@header_household_survey_analysis</t>
+  </si>
+  <si>
+    <t>@header_integrated_analysis</t>
+  </si>
+  <si>
+    <t>@text_analysis_exhaustive_srs_systematic_unstratified</t>
+  </si>
+  <si>
+    <t>The finite population correction factor will be applied since the target population is less than 10,000 individuals.</t>
+  </si>
+  <si>
+    <t>@text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>For specific stratum where the population is less than 10,000 individuals, the finite population correction factor will be applied.</t>
+  </si>
+  <si>
+    <t>@text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>Data will be collected using a contextualized IPHRA ODK tool. Cleaning and analysis will be done using a pre-prepared IPHRA application built in @r_version.</t>
+  </si>
+  <si>
+    <t>@text_intro_data_processing_analysis</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a simple random sampling design across sites without applying survey weights. @text_analysis_fpc_unstratified.</t>
+  </si>
+  <si>
+    <t>@text_analysis_exhaustive_srs_systematic_stratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a simple random sampling design across sites. Survey weights will be generated for aggregation of results between strata. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_srs_systematic_srs_systematic_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_srs_systematic_srs_systematic_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a weighted analysis and survey weights will be generated between sites to correct for under- or over-sampling between sites based on the best available population estimated the field teams were able to recover. If no adequate population data was available during the assessment, the final analysis will be unweighted. @text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a weighted analysis and survey weights will be generated between sites to correct for under- or over-sampling between sites based on the best available population estimated the field teams were able to recover. If no adequate population data was available during the assessment, the final analysis will be unweighted. An additional set of weights will be generated between strata to account for under- or over-sampling of population groups. Each set of weights will be multiplied together at the household level to generate a single set of composite weights for aggregated analysis. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_cluster_srs_systematic_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design without applying survey weights. Sites/PSUs will be treated as clusters in the analysis. @text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_cluster_srs_systematic_stratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design and sites/PSUs will be treated as clusters in the analysis. Survey weights will be generated for aggregation of results between strata. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_exhaustive_rlc_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design across sites with groupings of households at each GPS point treated as the clusters in the analysis. If population density is assessed to be very different within or across assessment sites, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. @text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_exhaustive_rlc_stratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design across sites with groupings of households at each GPS point treated as the clusters in the analysis. If population density is assessed to be very different within or across assessment sites, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. An additional set of weights will be generated between strata to account for under- or over-sampling of population groups. Each set of weights will be multiplied together at the household level to generate a single set of composite weights for aggregated analysis. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_srs_systematic_rlc_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a weighted cluster design across sites with groupings of households at each GPS point treated as the clusters in the analysis. Survey weights will be generated between sites to correct for under- or over-sampling between sites based on the best available population estimated the field teams were able to recover. If no adequate population data was available during the assessment, the final analysis will be unweighted. If population density is assessed to be very different within or across assessment sites, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. An additional set of weights will be generated between strata to account for under- or over-sampling of population groups. Each set of weights will be multiplied together at the household level to generate a single set of composite weights for aggregated analysis. @text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_srs_systematic_rlc_stratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a weighted cluster design across sites with groupings of households at each GPS point treated as the clusters in the analysis. Survey weights will be generated between sites to correct for under- or over-sampling between sites based on the best available population estimated the field teams were able to recover. If no adequate population data was available during the assessment, the final analysis will be unweighted. If population density is assessed to be very different within or across assessment sites, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. An additional set of weights will be generated between strata to account for under- or over-sampling of population groups. Each set of weights will be multiplied together at the household level to generate a single set of composite weights for aggregated analysis. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_cluster_rlc_unstratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design with sites/PSU being the primary clusters assigned in the analysis. Within these PSUs, additional clustering effects may be taking place as three households are sampled per random location cluster (GPS point) however this clustering effect will not be explicitly accounted for in the analysis. If population density is assessed to be very different within assessment sites/PSUs, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each random location cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. @text_analysis_fpc_unstratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_cluster_rlc_stratified</t>
+  </si>
+  <si>
+    <t>The household analysis will be treated as a cluster design with sites/PSU being the primary clusters assigned in the analysis. Within these PSUs, additional clustering effects may be taking place as three households are sampled per random location cluster (GPS point) however this clustering effect will not be explicitly accounted for in the analysis. If population density is assessed to be very different within assessment sites/PSUs, survey weights will be used for each random location cluster equivalent to the inverse of the population density of each random location cluster. This is intended to correct for any bias due to an uneven population density across the assessment area to make sure households have a more equal representation in the dataset. Population density is estimated based on the number of people in households within a random location cluster divided by the area of the circle formed by the locations of the three households and the GPS point of that random location cluster. An additional set of weights will be generated between strata to account for under- or over-sampling of population groups. Each set of weights will be multiplied together at the household level to generate a single set of composite weights for aggregated analysis. @text_analysis_fpc_stratified</t>
+  </si>
+  <si>
+    <t>@text_analysis_muac_age_correction</t>
+  </si>
+  <si>
+    <t>The ratio of children 0-23 months of age to children 24-59 months of age in the sample will be evaluated to determine if additional age weighting is needed for analysis of the indicator Global or Severe Acute Malnutrition by MUAC. If strong differences are observed against an expected proportion of two-thirds children 24-59 months out of all under-5 year old children, then a set of weights will be applied if the child is 0-23 months or 24-59 months for this specific indicator. The age weights will be multiplied with any household level weights to generate a single set of composite weight for analysis.</t>
   </si>
 </sst>
 </file>
@@ -3308,7 +3465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3378,7 +3535,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3398,6 +3554,10 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3701,7 +3861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D555"/>
+  <dimension ref="A1:D591"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -6240,18 +6400,18 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B266" t="s">
         <v>140</v>
       </c>
       <c r="D266" s="24" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B267" t="s">
         <v>302</v>
@@ -6259,7 +6419,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B268" t="s">
         <v>140</v>
@@ -6270,7 +6430,7 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B269" t="s">
         <v>142</v>
@@ -6278,7 +6438,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B270" t="s">
         <v>140</v>
@@ -6289,7 +6449,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B271" t="s">
         <v>142</v>
@@ -6297,18 +6457,18 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B272" t="s">
+        <v>140</v>
+      </c>
+      <c r="D272" s="14" t="s">
         <v>931</v>
-      </c>
-      <c r="B272" t="s">
-        <v>140</v>
-      </c>
-      <c r="D272" s="14" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B273" t="s">
         <v>142</v>
@@ -6316,7 +6476,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s">
         <v>171</v>
@@ -6969,7 +7129,7 @@
         <v>499</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D341" s="27" t="s">
         <v>507</v>
@@ -6983,7 +7143,7 @@
         <v>499</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D342" s="27" t="s">
         <v>508</v>
@@ -6997,7 +7157,7 @@
         <v>499</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D343" s="27" t="s">
         <v>509</v>
@@ -7005,30 +7165,30 @@
     </row>
     <row r="344" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B344" t="s">
         <v>499</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D344" s="27" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B345" t="s">
         <v>499</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D345" s="27" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -7039,38 +7199,38 @@
         <v>499</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B347" t="s">
         <v>499</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B348" t="s">
         <v>499</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -7081,38 +7241,38 @@
         <v>499</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D349" s="27" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B350" t="s">
         <v>499</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B351" t="s">
         <v>499</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -7123,624 +7283,624 @@
         <v>499</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B353" t="s">
         <v>499</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B354" t="s">
         <v>499</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D354" s="34" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B355" t="s">
         <v>499</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D355" s="27" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B356" t="s">
         <v>499</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D356" s="27" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A357" s="35" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B357" t="s">
         <v>499</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D357" s="36" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A358" s="35" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B358" t="s">
         <v>141</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D358" s="27"/>
     </row>
     <row r="359" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A359" s="35" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B359" t="s">
         <v>499</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D359" s="36" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A360" s="35" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B360" t="s">
         <v>141</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D360" s="27"/>
     </row>
     <row r="361" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A361" s="35" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B361" t="s">
         <v>499</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D361" s="36" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A362" s="35" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B362" t="s">
         <v>141</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D362" s="27"/>
     </row>
     <row r="363" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A363" s="35" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B363" t="s">
         <v>499</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D363" s="36" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A364" s="35" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B364" t="s">
         <v>141</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D364" s="27"/>
     </row>
     <row r="365" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A365" s="35" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B365" t="s">
         <v>499</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D365" s="36" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A366" s="35" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B366" t="s">
         <v>141</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D366" s="27"/>
     </row>
     <row r="367" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A367" s="35" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B367" t="s">
         <v>499</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D367" s="36" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A368" s="35" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B368" t="s">
         <v>141</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D368" s="27"/>
     </row>
     <row r="369" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A369" s="35" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B369" t="s">
         <v>499</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D369" s="36" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A370" s="35" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B370" t="s">
         <v>141</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D370" s="27"/>
     </row>
     <row r="371" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A371" s="35" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B371" t="s">
         <v>499</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D371" s="36" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A372" s="35" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B372" t="s">
         <v>141</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D372" s="36"/>
     </row>
     <row r="373" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A373" s="35" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B373" t="s">
         <v>499</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="D373" s="36" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A374" s="35" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B374" t="s">
         <v>141</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="D374" s="27"/>
     </row>
     <row r="375" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A375" s="35" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B375" t="s">
         <v>499</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D375" s="36" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A376" s="35" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B376" t="s">
         <v>141</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D376" s="27"/>
     </row>
     <row r="377" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A377" s="35" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B377" t="s">
         <v>499</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D377" s="36" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A378" s="35" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B378" t="s">
         <v>141</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D378" s="27"/>
     </row>
     <row r="379" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A379" s="35" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B379" t="s">
         <v>499</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D379" s="36" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A380" s="35" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B380" t="s">
         <v>141</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D380" s="27"/>
     </row>
     <row r="381" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A381" s="35" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B381" t="s">
         <v>499</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D381" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A382" s="35" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B382" t="s">
         <v>141</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D382" s="27"/>
     </row>
     <row r="383" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A383" s="35" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B383" t="s">
         <v>499</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D383" s="36" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A384" s="35" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B384" t="s">
         <v>141</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D384" s="27"/>
     </row>
     <row r="385" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A385" s="35" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B385" t="s">
         <v>499</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D385" s="36" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A386" s="36" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B386" t="s">
         <v>141</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D386" s="27"/>
     </row>
     <row r="387" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A387" s="36" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B387" t="s">
         <v>499</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D387" s="27" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A388" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B388" t="s">
         <v>499</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D388" s="27" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A389" s="36" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B389" t="s">
         <v>499</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D389" s="27" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B390" t="s">
         <v>499</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D390" s="27" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B391" t="s">
         <v>499</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D391" s="27" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B392" t="s">
         <v>499</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D392" s="27" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A393" s="37" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B393" t="s">
         <v>499</v>
       </c>
       <c r="C393" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D393" s="27" t="s">
         <v>667</v>
-      </c>
-      <c r="D393" s="27" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A394" s="37" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B394" t="s">
         <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D394" s="27" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A395" s="36" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B395" t="s">
         <v>499</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D395" s="27" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A396" s="36" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B396" t="s">
         <v>499</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D396" s="27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B397" t="s">
         <v>499</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D397" s="27" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B398" t="s">
         <v>499</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D398" s="27" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7753,31 +7913,31 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B400" t="s">
         <v>140</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="26" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="99" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B401" t="s">
         <v>140</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="40" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B402" t="s">
         <v>141</v>
@@ -7787,21 +7947,21 @@
     </row>
     <row r="403" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B403" t="s">
         <v>140</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="D403" s="27" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B404" t="s">
         <v>141</v>
@@ -7811,392 +7971,392 @@
     </row>
     <row r="405" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B405" t="s">
         <v>302</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D405" s="27"/>
     </row>
     <row r="406" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B406" t="s">
         <v>302</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D406" s="27"/>
     </row>
     <row r="407" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B407" t="s">
         <v>302</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D407" s="27"/>
     </row>
     <row r="408" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B408" t="s">
         <v>302</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D408" s="27"/>
     </row>
     <row r="409" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B409" t="s">
         <v>302</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D409" s="27"/>
     </row>
     <row r="410" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B410" t="s">
         <v>302</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D410" s="27"/>
     </row>
     <row r="411" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B411" t="s">
         <v>302</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>694</v>
+        <v>947</v>
       </c>
       <c r="D411" s="27"/>
     </row>
     <row r="412" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B412" t="s">
         <v>302</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>695</v>
+        <v>947</v>
       </c>
       <c r="D412" s="27"/>
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B413" t="s">
         <v>140</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" s="26" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B414" t="s">
         <v>140</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" s="26" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B415" t="s">
         <v>140</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="38" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B416" t="s">
         <v>140</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D416" s="39" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B417" t="s">
         <v>140</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D417" s="39" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B418" t="s">
         <v>140</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D418" s="39" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B419" t="s">
         <v>140</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D419" s="39" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B420" t="s">
         <v>140</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D420" s="39" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B421" t="s">
         <v>140</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D421" s="39" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B422" t="s">
         <v>140</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>694</v>
+        <v>947</v>
       </c>
       <c r="D422" s="39" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B423" t="s">
         <v>140</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>695</v>
+        <v>947</v>
       </c>
       <c r="D423" s="39" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B424" t="s">
         <v>140</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" s="38" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B425" t="s">
         <v>140</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B426" t="s">
         <v>140</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B427" t="s">
         <v>140</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B428" t="s">
         <v>140</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B429" t="s">
         <v>140</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B430" t="s">
         <v>140</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B431" t="s">
         <v>140</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>694</v>
+        <v>947</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B432" t="s">
         <v>140</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>695</v>
+        <v>947</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B433" t="s">
+        <v>140</v>
+      </c>
+      <c r="D433" s="26" t="s">
         <v>548</v>
-      </c>
-      <c r="B433" t="s">
-        <v>140</v>
-      </c>
-      <c r="D433" s="26" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B434" t="s">
+        <v>140</v>
+      </c>
+      <c r="D434" s="27" t="s">
         <v>549</v>
-      </c>
-      <c r="B434" t="s">
-        <v>140</v>
-      </c>
-      <c r="D434" s="27" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -8209,13 +8369,13 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B436" t="s">
         <v>140</v>
       </c>
       <c r="D436" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -8228,13 +8388,13 @@
     </row>
     <row r="438" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B438" t="s">
         <v>140</v>
       </c>
       <c r="D438" s="33" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -8259,7 +8419,7 @@
         <v>499</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D440" t="s">
         <v>122</v>
@@ -8301,7 +8461,7 @@
         <v>499</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>516</v>
+        <v>947</v>
       </c>
       <c r="D443" t="s">
         <v>123</v>
@@ -8315,7 +8475,7 @@
         <v>499</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>517</v>
+        <v>947</v>
       </c>
       <c r="D444" t="s">
         <v>125</v>
@@ -8329,7 +8489,7 @@
         <v>499</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D445" t="s">
         <v>124</v>
@@ -8337,111 +8497,111 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B446" t="s">
         <v>140</v>
       </c>
       <c r="C446" s="2"/>
       <c r="D446" s="26" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B447" t="s">
         <v>140</v>
       </c>
       <c r="C447" s="2"/>
       <c r="D447" s="10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B448" t="s">
         <v>140</v>
       </c>
       <c r="C448" s="2"/>
       <c r="D448" s="10" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B449" t="s">
         <v>140</v>
       </c>
       <c r="C449" s="2"/>
       <c r="D449" s="10" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B450" t="s">
         <v>140</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D450" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B451" t="s">
+        <v>140</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D451" t="s">
         <v>530</v>
-      </c>
-      <c r="B451" t="s">
-        <v>140</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D451" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A452" s="30" t="s">
+        <v>535</v>
+      </c>
+      <c r="B452" t="s">
+        <v>140</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D452" t="s">
         <v>537</v>
-      </c>
-      <c r="B452" t="s">
-        <v>140</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D452" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A453" s="30" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B453" t="s">
         <v>140</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D453" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="28" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B454" s="28" t="s">
         <v>141</v>
@@ -8450,7 +8610,7 @@
     </row>
     <row r="455" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A455" s="31" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B455" s="28" t="s">
         <v>141</v>
@@ -8458,7 +8618,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="28" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B456" s="28" t="s">
         <v>141</v>
@@ -8466,7 +8626,7 @@
     </row>
     <row r="457" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A457" s="32" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B457" s="28" t="s">
         <v>141</v>
@@ -8474,7 +8634,7 @@
     </row>
     <row r="458" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A458" s="31" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B458" s="28" t="s">
         <v>141</v>
@@ -8482,7 +8642,7 @@
     </row>
     <row r="459" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A459" s="31" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B459" s="28" t="s">
         <v>141</v>
@@ -8490,7 +8650,7 @@
     </row>
     <row r="460" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A460" s="10" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B460" s="28" t="s">
         <v>141</v>
@@ -8499,7 +8659,7 @@
     </row>
     <row r="461" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A461" s="31" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B461" s="28" t="s">
         <v>141</v>
@@ -8507,7 +8667,7 @@
     </row>
     <row r="462" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A462" s="32" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B462" s="28" t="s">
         <v>141</v>
@@ -8516,7 +8676,7 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" s="28" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B463" s="28" t="s">
         <v>141</v>
@@ -8532,7 +8692,7 @@
         <v>510</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -8543,7 +8703,7 @@
         <v>510</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -8554,93 +8714,93 @@
         <v>510</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B467" t="s">
         <v>140</v>
       </c>
       <c r="D467" s="10" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B468" t="s">
         <v>140</v>
       </c>
       <c r="C468" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D468" s="10" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B469" t="s">
         <v>140</v>
       </c>
       <c r="C469" t="s">
-        <v>756</v>
-      </c>
-      <c r="D469" s="41" t="s">
-        <v>766</v>
+        <v>752</v>
+      </c>
+      <c r="D469" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B470" t="s">
         <v>140</v>
       </c>
       <c r="C470" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D470" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B471" t="s">
         <v>140</v>
       </c>
       <c r="C471" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D471" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B472" t="s">
         <v>140</v>
       </c>
       <c r="C472" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D472" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B473" t="s">
         <v>141</v>
@@ -8648,7 +8808,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B474" t="s">
         <v>141</v>
@@ -8656,76 +8816,76 @@
     </row>
     <row r="475" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B475" t="s">
         <v>140</v>
       </c>
-      <c r="C475" s="42" t="s">
-        <v>787</v>
-      </c>
-      <c r="D475" s="43" t="s">
-        <v>787</v>
+      <c r="C475" s="41" t="s">
+        <v>783</v>
+      </c>
+      <c r="D475" s="42" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="476" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B476" t="s">
         <v>140</v>
       </c>
-      <c r="D476" s="43" t="s">
-        <v>788</v>
+      <c r="D476" s="42" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B477" t="s">
         <v>140</v>
       </c>
       <c r="D477" s="38" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B478" t="s">
         <v>140</v>
       </c>
       <c r="D478" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B479" t="s">
         <v>140</v>
       </c>
       <c r="D479" s="38" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B480" t="s">
         <v>140</v>
       </c>
       <c r="D480" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B481" t="s">
         <v>140</v>
@@ -8733,7 +8893,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B482" t="s">
         <v>140</v>
@@ -8741,305 +8901,305 @@
     </row>
     <row r="483" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B483" t="s">
         <v>140</v>
       </c>
       <c r="D483" s="10" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B484" t="s">
         <v>140</v>
       </c>
       <c r="C484" t="s">
-        <v>778</v>
-      </c>
-      <c r="D484" s="41" t="s">
-        <v>777</v>
+        <v>774</v>
+      </c>
+      <c r="D484" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B485" t="s">
         <v>140</v>
       </c>
       <c r="C485" t="s">
+        <v>775</v>
+      </c>
+      <c r="D485" t="s">
         <v>779</v>
-      </c>
-      <c r="D485" s="41" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B486" t="s">
         <v>140</v>
       </c>
       <c r="C486" t="s">
+        <v>776</v>
+      </c>
+      <c r="D486" t="s">
         <v>780</v>
-      </c>
-      <c r="D486" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B487" t="s">
         <v>140</v>
       </c>
-      <c r="C487" s="42" t="s">
-        <v>787</v>
-      </c>
-      <c r="D487" s="43" t="s">
-        <v>787</v>
+      <c r="C487" s="41" t="s">
+        <v>783</v>
+      </c>
+      <c r="D487" s="42" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B488" t="s">
         <v>140</v>
       </c>
-      <c r="D488" s="43" t="s">
-        <v>788</v>
+      <c r="D488" s="42" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B489" t="s">
         <v>140</v>
       </c>
       <c r="D489" s="38" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B490" t="s">
         <v>140</v>
       </c>
-      <c r="D490" s="44" t="s">
-        <v>803</v>
+      <c r="D490" s="43" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B491" t="s">
         <v>140</v>
       </c>
       <c r="D491" s="38" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B492" t="s">
         <v>140</v>
       </c>
-      <c r="D492" s="45" t="s">
-        <v>805</v>
+      <c r="D492" s="44" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B493" t="s">
         <v>140</v>
       </c>
       <c r="D493" s="38" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B494" t="s">
         <v>140</v>
       </c>
-      <c r="D494" s="45" t="s">
-        <v>807</v>
+      <c r="D494" s="44" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B495" t="s">
         <v>140</v>
       </c>
       <c r="D495" s="38" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B496" t="s">
         <v>140</v>
       </c>
-      <c r="D496" s="45" t="s">
-        <v>809</v>
+      <c r="D496" s="44" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B497" t="s">
         <v>140</v>
       </c>
       <c r="D497" s="38" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B498" t="s">
         <v>140</v>
       </c>
-      <c r="D498" s="45" t="s">
-        <v>811</v>
+      <c r="D498" s="44" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B499" t="s">
         <v>140</v>
       </c>
       <c r="D499" s="39" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B500" t="s">
         <v>140</v>
       </c>
       <c r="D500" s="38" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B501" t="s">
         <v>140</v>
       </c>
       <c r="D501" s="39" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B502" t="s">
         <v>140</v>
       </c>
       <c r="D502" s="38" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B503" t="s">
         <v>140</v>
       </c>
       <c r="D503" s="39" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B504" t="s">
         <v>140</v>
       </c>
       <c r="D504" s="38" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B505" t="s">
         <v>140</v>
       </c>
       <c r="D505" s="39" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B506" t="s">
         <v>140</v>
       </c>
       <c r="D506" s="38" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B507" t="s">
         <v>140</v>
       </c>
       <c r="D507" s="39" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B508" t="s">
         <v>140</v>
       </c>
       <c r="D508" s="38" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B509" t="s">
         <v>302</v>
@@ -9047,7 +9207,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B510" t="s">
         <v>302</v>
@@ -9055,497 +9215,745 @@
     </row>
     <row r="511" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B511" t="s">
         <v>140</v>
       </c>
-      <c r="D511" s="46" t="s">
-        <v>843</v>
+      <c r="D511" s="45" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="512" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B512" t="s">
         <v>140</v>
       </c>
-      <c r="D512" s="47" t="s">
-        <v>845</v>
+      <c r="D512" s="46" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="513" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B513" t="s">
         <v>140</v>
       </c>
-      <c r="D513" s="43" t="s">
-        <v>849</v>
+      <c r="D513" s="42" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="514" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B514" t="s">
         <v>140</v>
       </c>
-      <c r="D514" s="43" t="s">
-        <v>850</v>
+      <c r="D514" s="42" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="515" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B515" t="s">
         <v>140</v>
       </c>
-      <c r="D515" s="43" t="s">
-        <v>851</v>
+      <c r="D515" s="42" t="s">
+        <v>847</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B516" t="s">
         <v>140</v>
       </c>
       <c r="D516" s="38" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B517" t="s">
         <v>140</v>
       </c>
       <c r="D517" s="38" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B518" t="s">
         <v>140</v>
       </c>
       <c r="D518" s="38" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B519" t="s">
         <v>140</v>
       </c>
       <c r="D519" s="38" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B520" t="s">
         <v>140</v>
       </c>
       <c r="D520" s="38" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B521" t="s">
         <v>140</v>
       </c>
       <c r="D521" s="38" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B522" t="s">
         <v>140</v>
       </c>
       <c r="D522" s="38" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B523" t="s">
         <v>140</v>
       </c>
       <c r="D523" s="38" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B524" t="s">
         <v>140</v>
       </c>
       <c r="D524" s="38" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B525" t="s">
         <v>140</v>
       </c>
       <c r="D525" s="38" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B526" t="s">
         <v>140</v>
       </c>
       <c r="D526" s="38" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="527" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B527" t="s">
         <v>140</v>
       </c>
       <c r="D527" s="38" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="528" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B528" t="s">
         <v>140</v>
       </c>
-      <c r="D528" s="48" t="s">
-        <v>876</v>
+      <c r="D528" s="47" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="529" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B529" t="s">
         <v>140</v>
       </c>
-      <c r="D529" s="49" t="s">
-        <v>877</v>
+      <c r="D529" s="48" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="530" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B530" t="s">
         <v>140</v>
       </c>
-      <c r="D530" s="49" t="s">
-        <v>878</v>
+      <c r="D530" s="48" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="531" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B531" t="s">
         <v>140</v>
       </c>
-      <c r="D531" s="49" t="s">
-        <v>879</v>
+      <c r="D531" s="48" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="532" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B532" t="s">
         <v>140</v>
       </c>
-      <c r="D532" s="49" t="s">
-        <v>880</v>
+      <c r="D532" s="48" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="533" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B533" t="s">
         <v>140</v>
       </c>
-      <c r="D533" s="49" t="s">
-        <v>881</v>
+      <c r="D533" s="48" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="534" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B534" t="s">
         <v>140</v>
       </c>
       <c r="D534" s="10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="535" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B535" t="s">
         <v>140</v>
       </c>
       <c r="D535" s="13" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="536" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B536" t="s">
         <v>140</v>
       </c>
-      <c r="D536" s="46" t="s">
-        <v>893</v>
+      <c r="D536" s="45" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="537" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B537" t="s">
         <v>140</v>
       </c>
       <c r="D537" s="27" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="538" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B538" t="s">
         <v>140</v>
       </c>
-      <c r="D538" s="43" t="s">
-        <v>896</v>
+      <c r="D538" s="42" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="539" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B539" t="s">
         <v>140</v>
       </c>
-      <c r="D539" s="43" t="s">
-        <v>850</v>
+      <c r="D539" s="42" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="540" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B540" t="s">
         <v>140</v>
       </c>
       <c r="D540" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="541" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B541" t="s">
         <v>140</v>
       </c>
-      <c r="D541" s="50" t="s">
+      <c r="D541" s="49" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="542" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B542" t="s">
         <v>140</v>
       </c>
-      <c r="D542" s="51" t="s">
+      <c r="D542" s="50" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="543" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B543" t="s">
         <v>140</v>
       </c>
-      <c r="D543" s="51" t="s">
+      <c r="D543" s="50" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="544" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B544" t="s">
         <v>140</v>
       </c>
-      <c r="D544" s="51" t="s">
+      <c r="D544" s="50" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="545" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B545" t="s">
         <v>140</v>
       </c>
-      <c r="D545" s="51" t="s">
-        <v>906</v>
+      <c r="D545" s="50" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="546" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B546" t="s">
         <v>140</v>
       </c>
-      <c r="D546" s="50" t="s">
-        <v>907</v>
+      <c r="D546" s="49" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="547" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B547" t="s">
         <v>140</v>
       </c>
-      <c r="D547" s="51" t="s">
-        <v>874</v>
+      <c r="D547" s="50" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="548" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B548" t="s">
         <v>140</v>
       </c>
-      <c r="D548" s="51" t="s">
-        <v>908</v>
+      <c r="D548" s="50" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="549" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B549" t="s">
         <v>140</v>
       </c>
-      <c r="D549" s="51" t="s">
-        <v>871</v>
+      <c r="D549" s="50" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="550" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B550" t="s">
         <v>140</v>
       </c>
-      <c r="D550" s="51" t="s">
-        <v>909</v>
+      <c r="D550" s="50" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="551" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B551" t="s">
         <v>140</v>
       </c>
-      <c r="D551" s="50" t="s">
-        <v>910</v>
+      <c r="D551" s="49" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="552" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B552" t="s">
         <v>140</v>
       </c>
-      <c r="D552" s="51" t="s">
-        <v>911</v>
+      <c r="D552" s="50" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="553" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B553" t="s">
         <v>140</v>
       </c>
-      <c r="D553" s="51" t="s">
-        <v>912</v>
+      <c r="D553" s="50" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="554" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B554" t="s">
         <v>140</v>
       </c>
-      <c r="D554" s="51" t="s">
-        <v>913</v>
+      <c r="D554" s="50" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="555" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B555" t="s">
         <v>140</v>
       </c>
-      <c r="D555" s="51" t="s">
-        <v>914</v>
+      <c r="D555" s="50" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A556" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B556" t="s">
+        <v>140</v>
+      </c>
+      <c r="D556" s="10" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B557" t="s">
+        <v>140</v>
+      </c>
+      <c r="D557" s="51" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A558" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B558" t="s">
+        <v>140</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D558" s="27" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B559" t="s">
+        <v>140</v>
+      </c>
+      <c r="D559" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A560" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B560" t="s">
+        <v>140</v>
+      </c>
+      <c r="D560" s="10" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A561" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B561" t="s">
+        <v>140</v>
+      </c>
+      <c r="D561" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562" s="28" t="s">
+        <v>945</v>
+      </c>
+      <c r="B562" s="29" t="s">
+        <v>510</v>
+      </c>
+      <c r="C562" s="29"/>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B563" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B564" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A565" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="D565" s="26" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A566" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="D566" s="10" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568" s="2" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A569" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="D569" s="52" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A570" s="30" t="s">
+        <v>954</v>
+      </c>
+      <c r="D570" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A571" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="D571" s="52" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A572" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="D572" s="10" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A573" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="D573" s="10" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A574" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="D574" s="10" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A575" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="D575" s="10" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A576" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="D576" s="10" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A577" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="D577" s="10" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A578" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="D578" s="10" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A579" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="D579" s="10" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A580" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="D580" s="10" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A581" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="D581" s="10" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A582" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="D582" s="10" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A590" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D590" s="10" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A591" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="D591" s="10" t="s">
+        <v>957</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BF67D-99B0-49B8-99A6-0DE7E5559656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF664CA5-BA30-46ED-829B-80A324E80FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="991">
   <si>
     <t>tag_name</t>
   </si>
@@ -3129,9 +3129,6 @@
     <t>Data will be collected using a contextualized IPHRA ODK tool. Cleaning and analysis will be done using a pre-prepared IPHRA application built in @r_version.</t>
   </si>
   <si>
-    <t>@text_intro_data_processing_analysis</t>
-  </si>
-  <si>
     <t>The household analysis will be treated as a simple random sampling design across sites without applying survey weights. @text_analysis_fpc_unstratified.</t>
   </si>
   <si>
@@ -3205,6 +3202,24 @@
   </si>
   <si>
     <t>The ratio of children 0-23 months of age to children 24-59 months of age in the sample will be evaluated to determine if additional age weighting is needed for analysis of the indicator Global or Severe Acute Malnutrition by MUAC. If strong differences are observed against an expected proportion of two-thirds children 24-59 months out of all under-5 year old children, then a set of weights will be applied if the child is 0-23 months or 24-59 months for this specific indicator. The age weights will be multiplied with any household level weights to generate a single set of composite weight for analysis.</t>
+  </si>
+  <si>
+    <t>@text_intro_household_survey_analysis</t>
+  </si>
+  <si>
+    <t>muac_survey</t>
+  </si>
+  <si>
+    <t>@header_analysis_kii_obs</t>
+  </si>
+  <si>
+    <t>Key Informant Interview and Observation Data</t>
+  </si>
+  <si>
+    <t>@text_analysis_kii_obs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community key informant interviews and community observation checklists will be qualitatively analysed using a data saturation grid, with the objectives of (a) triangulating the self-perceived needs of the population against quantitative data, and (b) attaining a better qualitative understanding of the nature of needs and barriers. The qualitative analysis uses a two-step process: Firstly, qualitative responses or observations are categorized as pertaining to one or more pillars or sub-pillars of the Acute Needs Framework to facilitate comparison of results across tools; and secondly a rapid coding is conducted to identify common themes and issues within pillars. Responses will be compared across gender and assessed sites. A standardized data saturation grid is used to facilitate this analysis. </t>
   </si>
 </sst>
 </file>
@@ -3465,7 +3480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3555,7 +3570,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
@@ -3861,7 +3875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D591"/>
+  <dimension ref="A1:D586"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -9726,7 +9740,7 @@
       <c r="B557" t="s">
         <v>140</v>
       </c>
-      <c r="D557" s="51" t="s">
+      <c r="D557" t="s">
         <v>939</v>
       </c>
     </row>
@@ -9751,6 +9765,9 @@
       <c r="B559" t="s">
         <v>140</v>
       </c>
+      <c r="C559" t="s">
+        <v>986</v>
+      </c>
       <c r="D559" t="s">
         <v>937</v>
       </c>
@@ -9806,6 +9823,9 @@
       <c r="A565" s="2" t="s">
         <v>950</v>
       </c>
+      <c r="B565" t="s">
+        <v>140</v>
+      </c>
       <c r="D565" s="26" t="s">
         <v>949</v>
       </c>
@@ -9814,6 +9834,9 @@
       <c r="A566" s="2" t="s">
         <v>952</v>
       </c>
+      <c r="B566" t="s">
+        <v>140</v>
+      </c>
       <c r="D566" s="10" t="s">
         <v>948</v>
       </c>
@@ -9822,17 +9845,26 @@
       <c r="A567" s="2" t="s">
         <v>951</v>
       </c>
+      <c r="B567" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>953</v>
       </c>
+      <c r="B568" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="569" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A569" s="10" t="s">
-        <v>960</v>
-      </c>
-      <c r="D569" s="52" t="s">
+      <c r="A569" s="30" t="s">
+        <v>985</v>
+      </c>
+      <c r="B569" t="s">
+        <v>140</v>
+      </c>
+      <c r="D569" s="51" t="s">
         <v>959</v>
       </c>
     </row>
@@ -9840,120 +9872,208 @@
       <c r="A570" s="30" t="s">
         <v>954</v>
       </c>
+      <c r="B570" t="s">
+        <v>140</v>
+      </c>
       <c r="D570" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="571" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A571" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="B571" t="s">
+        <v>140</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D571" s="51" t="s">
         <v>962</v>
-      </c>
-      <c r="D571" s="52" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="572" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A572" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="B572" t="s">
+        <v>140</v>
+      </c>
+      <c r="D572" s="10" t="s">
         <v>965</v>
-      </c>
-      <c r="D572" s="10" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="573" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A573" s="10" t="s">
-        <v>964</v>
+        <v>963</v>
+      </c>
+      <c r="B573" t="s">
+        <v>140</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>737</v>
       </c>
       <c r="D573" s="10" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="574" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A574" s="10" t="s">
+        <v>967</v>
+      </c>
+      <c r="B574" t="s">
+        <v>140</v>
+      </c>
+      <c r="D574" s="10" t="s">
         <v>968</v>
-      </c>
-      <c r="D574" s="10" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="575" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A575" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="B575" t="s">
+        <v>140</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D575" s="10" t="s">
         <v>970</v>
-      </c>
-      <c r="D575" s="10" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="576" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A576" s="10" t="s">
+        <v>971</v>
+      </c>
+      <c r="B576" t="s">
+        <v>140</v>
+      </c>
+      <c r="D576" s="10" t="s">
         <v>972</v>
-      </c>
-      <c r="D576" s="10" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="577" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A577" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="B577" t="s">
+        <v>140</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D577" s="10" t="s">
         <v>974</v>
-      </c>
-      <c r="D577" s="10" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="578" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A578" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="B578" t="s">
+        <v>140</v>
+      </c>
+      <c r="D578" s="10" t="s">
         <v>976</v>
-      </c>
-      <c r="D578" s="10" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="579" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A579" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="B579" t="s">
+        <v>140</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D579" s="10" t="s">
         <v>978</v>
-      </c>
-      <c r="D579" s="10" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="580" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A580" s="10" t="s">
+        <v>979</v>
+      </c>
+      <c r="B580" t="s">
+        <v>140</v>
+      </c>
+      <c r="D580" s="10" t="s">
         <v>980</v>
-      </c>
-      <c r="D580" s="10" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="581" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A581" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="B581" t="s">
+        <v>140</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D581" s="10" t="s">
         <v>982</v>
-      </c>
-      <c r="D581" s="10" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="582" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A582" s="10" t="s">
+        <v>983</v>
+      </c>
+      <c r="B582" t="s">
+        <v>140</v>
+      </c>
+      <c r="C582" t="s">
+        <v>986</v>
+      </c>
+      <c r="D582" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="D582" s="10" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="590" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A590" s="2" t="s">
+    </row>
+    <row r="583" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A583" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="D590" s="10" t="s">
+      <c r="B583" t="s">
+        <v>140</v>
+      </c>
+      <c r="D583" s="10" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A591" s="2" t="s">
+    <row r="584" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A584" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="D591" s="10" t="s">
+      <c r="B584" t="s">
+        <v>140</v>
+      </c>
+      <c r="D584" s="10" t="s">
         <v>957</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A585" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="B585" t="s">
+        <v>140</v>
+      </c>
+      <c r="D585" s="10" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A586" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B586" t="s">
+        <v>140</v>
+      </c>
+      <c r="D586" s="10" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -5713,7 +5713,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>conditional_replace</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>phr_doc_add_primary_data_sources_table</t>
+          <t>table_primary_data_sources</t>
         </is>
       </c>
     </row>
@@ -7638,11 +7638,7 @@
           <t>image</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>phr_doc_add_framework_image</t>
-        </is>
-      </c>
+      <c r="E435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -7674,7 +7670,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>phr_doc_add_secondary_data_sources_table</t>
+          <t>table_secondary_data_sources</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8148,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>phr_doc_add_sample_size_gen_table</t>
+          <t>table_sample_size_general</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8170,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>phr_doc_add_sample_size_ind_table</t>
+          <t>table_sample_size_individual</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8192,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>phr_doc_add_sample_size_mort_table</t>
+          <t>table_sample_size_mortality</t>
         </is>
       </c>
     </row>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDACB0E8-605B-4603-8541-000E94C627AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD3AB84-B756-4963-9990-7EF41B5A5AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD3AB84-B756-4963-9990-7EF41B5A5AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91078F0F-6136-4D23-9BFB-A88F51445A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1037">
   <si>
     <t>tag_name</t>
   </si>
@@ -823,9 +823,6 @@
   </si>
   <si>
     <t>@precision_ind_indicator</t>
-  </si>
-  <si>
-    <t>@precision_mort_indicator</t>
   </si>
   <si>
     <t>@header_tool_kii_community</t>
@@ -3039,12 +3036,154 @@
   <si>
     <t xml:space="preserve">Community key informant interviews and community observation checklists will be qualitatively analysed using a data saturation grid, with the objectives of (a) triangulating the self-perceived needs of the population against quantitative data, and (b) attaining a better qualitative understanding of the nature of needs and barriers. The qualitative analysis uses a two-step process: Firstly, qualitative responses or observations are categorized as pertaining to one or more pillars or sub-pillars of the Acute Needs Framework to facilitate comparison of results across tools; and secondly a rapid coding is conducted to identify common themes and issues within pillars. Responses will be compared across gender and assessed sites. A standardized data saturation grid is used to facilitate this analysis. </t>
   </si>
+  <si>
+    <t>num_report</t>
+  </si>
+  <si>
+    <t>num_profile</t>
+  </si>
+  <si>
+    <t>num_prelim_presentation</t>
+  </si>
+  <si>
+    <t>num_final_presentation</t>
+  </si>
+  <si>
+    <t>num_factsheet</t>
+  </si>
+  <si>
+    <t>num_dashboard</t>
+  </si>
+  <si>
+    <t>num_webmap</t>
+  </si>
+  <si>
+    <t>num_map</t>
+  </si>
+  <si>
+    <t>num_output_other</t>
+  </si>
+  <si>
+    <t>@precision_rate_indicator</t>
+  </si>
+  <si>
+    <t>@header_analysis_integrated</t>
+  </si>
+  <si>
+    <t>Integrated Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The IPHRA is a mixed methods approach that uses both quantitative and qualitative approaches to triangulate the severity of population needs and service gaps. In order to facilitate this, an integrated analysis is conducted to compare the responses across tools and assign an overall severity per ANA dimension. The objective of this exercise is to provide a holistic understanding and prioritization of different dimensions that may be threatening public health.  
+The integrated analysis is conducted in three steps. </t>
+  </si>
+  <si>
+    <t>@text_analysis_integrated</t>
+  </si>
+  <si>
+    <t>@text_analysis_integrated_step1</t>
+  </si>
+  <si>
+    <t>@text_analysis_integrated_step2</t>
+  </si>
+  <si>
+    <t>@text_analysis_integrated_step3</t>
+  </si>
+  <si>
+    <t>Step 1: Assign Severity for Quantitative Results</t>
+  </si>
+  <si>
+    <t>Step 2: Assign Severity for Qualitative Results</t>
+  </si>
+  <si>
+    <t>Step 3: Assign an Overall Severity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In order to have a holistic understanding of the severity of public health needs and service gaps, it is suggested to include an integrated analysis table. This table will assign severity to one of the RoEM domains based on the evidence captured within the IPHRA assessment. The analyst can use the recommended thresholds in the standards tables located in the IPHRA Guidance document to help assign severity, however these are just recommendations based on standards and if needed these thresholds may be contextualized at the country level. </t>
+  </si>
+  <si>
+    <t>@text_analysis_integrated2</t>
+  </si>
+  <si>
+    <t>@text_low</t>
+  </si>
+  <si>
+    <t>@text_medium</t>
+  </si>
+  <si>
+    <t>@text_high</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>@text_not_assessed</t>
+  </si>
+  <si>
+    <t>Not assessed</t>
+  </si>
+  <si>
+    <t>@header_example_analysis_interated_table</t>
+  </si>
+  <si>
+    <t>Example Integrated Analysis Table</t>
+  </si>
+  <si>
+    <t>@header_category</t>
+  </si>
+  <si>
+    <t>@header_pillar</t>
+  </si>
+  <si>
+    <t>@header_sub_pillar</t>
+  </si>
+  <si>
+    <t>@header_severity</t>
+  </si>
+  <si>
+    <t>@header_group1</t>
+  </si>
+  <si>
+    <t>@header_group2</t>
+  </si>
+  <si>
+    <t>@header_group3</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Pillar</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Sub-Pillar</t>
+  </si>
+  <si>
+    <t>Group 1</t>
+  </si>
+  <si>
+    <t>Group 2</t>
+  </si>
+  <si>
+    <t>Group 3</t>
+  </si>
+  <si>
+    <t>Limitations</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3229,6 +3368,13 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3284,7 +3430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3377,6 +3523,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3679,7 +3826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E586"/>
+  <dimension ref="A1:E605"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" customWidth="1"/>
@@ -5346,8 +5493,8 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>266</v>
+      <c r="A171" s="2" t="s">
+        <v>999</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
@@ -5355,18 +5502,18 @@
     </row>
     <row r="172" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B172" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" s="13" t="s">
         <v>267</v>
-      </c>
-      <c r="B172" t="s">
-        <v>6</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B173" t="s">
         <v>225</v>
@@ -5374,18 +5521,18 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B174" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" s="22" t="s">
         <v>270</v>
-      </c>
-      <c r="B174" t="s">
-        <v>6</v>
-      </c>
-      <c r="D174" s="22" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B175" t="s">
         <v>29</v>
@@ -5393,18 +5540,18 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B176" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" s="22" t="s">
         <v>273</v>
-      </c>
-      <c r="B176" t="s">
-        <v>6</v>
-      </c>
-      <c r="D176" s="22" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B177" t="s">
         <v>29</v>
@@ -5412,18 +5559,18 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B178" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" s="22" t="s">
         <v>276</v>
-      </c>
-      <c r="B178" t="s">
-        <v>6</v>
-      </c>
-      <c r="D178" s="22" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B179" t="s">
         <v>29</v>
@@ -5431,7 +5578,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B180" t="s">
         <v>6</v>
@@ -5442,7 +5589,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B181" t="s">
         <v>29</v>
@@ -5450,18 +5597,18 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B182" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" s="14" t="s">
         <v>281</v>
-      </c>
-      <c r="B182" t="s">
-        <v>6</v>
-      </c>
-      <c r="D182" s="14" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B183" t="s">
         <v>29</v>
@@ -5469,26 +5616,26 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B185" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" s="13" t="s">
         <v>285</v>
-      </c>
-      <c r="B185" t="s">
-        <v>6</v>
-      </c>
-      <c r="D185" s="13" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B186" t="s">
         <v>225</v>
@@ -5496,7 +5643,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B187" t="s">
         <v>6</v>
@@ -5504,7 +5651,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B188" t="s">
         <v>29</v>
@@ -5512,7 +5659,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B189" t="s">
         <v>6</v>
@@ -5520,7 +5667,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B190" t="s">
         <v>29</v>
@@ -5528,7 +5675,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B191" t="s">
         <v>6</v>
@@ -5536,7 +5683,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B192" t="s">
         <v>29</v>
@@ -5544,26 +5691,26 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" s="13" t="s">
         <v>295</v>
-      </c>
-      <c r="B194" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" s="13" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B195" t="s">
         <v>225</v>
@@ -5571,18 +5718,18 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B196" t="s">
         <v>6</v>
       </c>
       <c r="D196" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B197" t="s">
         <v>29</v>
@@ -5590,7 +5737,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B198" t="s">
         <v>6</v>
@@ -5601,7 +5748,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B199" t="s">
         <v>29</v>
@@ -5609,7 +5756,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B200" t="s">
         <v>6</v>
@@ -5617,7 +5764,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B201" t="s">
         <v>29</v>
@@ -5625,26 +5772,26 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B203" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="B203" t="s">
-        <v>6</v>
-      </c>
-      <c r="D203" s="13" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B204" t="s">
         <v>225</v>
@@ -5652,18 +5799,18 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B205" t="s">
         <v>6</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B206" t="s">
         <v>29</v>
@@ -5671,7 +5818,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B207" t="s">
         <v>6</v>
@@ -5682,7 +5829,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B208" t="s">
         <v>29</v>
@@ -5690,18 +5837,18 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B209" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" s="14" t="s">
         <v>312</v>
-      </c>
-      <c r="B209" t="s">
-        <v>6</v>
-      </c>
-      <c r="D209" s="14" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B210" t="s">
         <v>29</v>
@@ -5709,26 +5856,26 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="B212" t="s">
-        <v>6</v>
-      </c>
-      <c r="D212" s="13" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B213" t="s">
         <v>225</v>
@@ -5736,18 +5883,18 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B214" t="s">
         <v>6</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B215" t="s">
         <v>29</v>
@@ -5755,7 +5902,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B216" t="s">
         <v>6</v>
@@ -5766,7 +5913,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B217" t="s">
         <v>29</v>
@@ -5774,18 +5921,18 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B218" t="s">
         <v>6</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B219" t="s">
         <v>29</v>
@@ -5793,26 +5940,26 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B221" t="s">
+        <v>6</v>
+      </c>
+      <c r="D221" s="13" t="s">
         <v>326</v>
-      </c>
-      <c r="B221" t="s">
-        <v>6</v>
-      </c>
-      <c r="D221" s="13" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B222" t="s">
         <v>225</v>
@@ -5820,18 +5967,18 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B223" t="s">
         <v>6</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B224" t="s">
         <v>29</v>
@@ -5839,7 +5986,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B225" t="s">
         <v>6</v>
@@ -5850,7 +5997,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B226" t="s">
         <v>29</v>
@@ -5858,18 +6005,18 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B227" t="s">
         <v>6</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B228" t="s">
         <v>29</v>
@@ -5877,26 +6024,26 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B230" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" s="13" t="s">
         <v>336</v>
-      </c>
-      <c r="B230" t="s">
-        <v>6</v>
-      </c>
-      <c r="D230" s="13" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B231" t="s">
         <v>225</v>
@@ -5904,18 +6051,18 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B232" t="s">
         <v>6</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B233" t="s">
         <v>29</v>
@@ -5923,7 +6070,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B234" t="s">
         <v>6</v>
@@ -5934,7 +6081,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B235" t="s">
         <v>29</v>
@@ -5942,18 +6089,18 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B236" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="B236" t="s">
-        <v>6</v>
-      </c>
-      <c r="D236" s="14" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B237" t="s">
         <v>29</v>
@@ -5961,26 +6108,26 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B239" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>347</v>
-      </c>
-      <c r="B239" t="s">
-        <v>6</v>
-      </c>
-      <c r="D239" s="13" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B240" t="s">
         <v>225</v>
@@ -5988,18 +6135,18 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B241" t="s">
         <v>6</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B242" t="s">
         <v>29</v>
@@ -6007,7 +6154,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B243" t="s">
         <v>6</v>
@@ -6018,7 +6165,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B244" t="s">
         <v>29</v>
@@ -6026,18 +6173,18 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B245" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" s="14" t="s">
         <v>354</v>
-      </c>
-      <c r="B245" t="s">
-        <v>6</v>
-      </c>
-      <c r="D245" s="14" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B246" t="s">
         <v>29</v>
@@ -6045,26 +6192,26 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B248" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="B248" t="s">
-        <v>6</v>
-      </c>
-      <c r="D248" s="13" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B249" t="s">
         <v>225</v>
@@ -6072,18 +6219,18 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B250" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B251" t="s">
         <v>29</v>
@@ -6091,7 +6238,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B252" t="s">
         <v>6</v>
@@ -6102,7 +6249,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B253" t="s">
         <v>29</v>
@@ -6110,18 +6257,18 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B254" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="B254" t="s">
-        <v>6</v>
-      </c>
-      <c r="D254" s="14" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B255" t="s">
         <v>29</v>
@@ -6129,26 +6276,26 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B256" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B257" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" s="24" t="s">
         <v>369</v>
-      </c>
-      <c r="B257" t="s">
-        <v>6</v>
-      </c>
-      <c r="D257" s="24" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B258" t="s">
         <v>225</v>
@@ -6156,18 +6303,18 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B259" t="s">
         <v>6</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B260" t="s">
         <v>29</v>
@@ -6175,7 +6322,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B261" t="s">
         <v>6</v>
@@ -6186,7 +6333,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B262" t="s">
         <v>29</v>
@@ -6194,18 +6341,18 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B263" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" s="14" t="s">
         <v>376</v>
-      </c>
-      <c r="B263" t="s">
-        <v>6</v>
-      </c>
-      <c r="D263" s="14" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B264" t="s">
         <v>29</v>
@@ -6213,26 +6360,26 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B265" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B266" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" s="24" t="s">
         <v>380</v>
-      </c>
-      <c r="B266" t="s">
-        <v>6</v>
-      </c>
-      <c r="D266" s="24" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B267" t="s">
         <v>225</v>
@@ -6240,18 +6387,18 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B268" t="s">
         <v>6</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B269" t="s">
         <v>29</v>
@@ -6259,7 +6406,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B270" t="s">
         <v>6</v>
@@ -6270,7 +6417,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B271" t="s">
         <v>29</v>
@@ -6278,18 +6425,18 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B272" t="s">
+        <v>6</v>
+      </c>
+      <c r="D272" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="B272" t="s">
-        <v>6</v>
-      </c>
-      <c r="D272" s="14" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B273" t="s">
         <v>29</v>
@@ -6297,37 +6444,37 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B274" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B275" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="B275" t="s">
-        <v>6</v>
-      </c>
-      <c r="D275" s="13" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B276" t="s">
+        <v>6</v>
+      </c>
+      <c r="D276" t="s">
         <v>393</v>
-      </c>
-      <c r="B276" t="s">
-        <v>6</v>
-      </c>
-      <c r="D276" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B277" t="s">
         <v>29</v>
@@ -6335,7 +6482,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B278" t="s">
         <v>29</v>
@@ -6343,18 +6490,18 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B279" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" t="s">
         <v>397</v>
-      </c>
-      <c r="B279" t="s">
-        <v>6</v>
-      </c>
-      <c r="D279" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B280" t="s">
         <v>29</v>
@@ -6362,7 +6509,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B281" t="s">
         <v>29</v>
@@ -6370,40 +6517,40 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B282" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" t="s">
         <v>401</v>
-      </c>
-      <c r="B282" t="s">
-        <v>6</v>
-      </c>
-      <c r="D282" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B283" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" t="s">
         <v>403</v>
-      </c>
-      <c r="B283" t="s">
-        <v>6</v>
-      </c>
-      <c r="D283" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B284" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" t="s">
         <v>405</v>
-      </c>
-      <c r="B284" t="s">
-        <v>6</v>
-      </c>
-      <c r="D284" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B285" t="s">
         <v>6</v>
@@ -6414,7 +6561,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B286" t="s">
         <v>29</v>
@@ -6422,7 +6569,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B287" t="s">
         <v>29</v>
@@ -6430,7 +6577,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B288" t="s">
         <v>29</v>
@@ -6438,321 +6585,348 @@
     </row>
     <row r="289" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B289" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" s="7" t="s">
         <v>411</v>
-      </c>
-      <c r="B289" t="s">
-        <v>6</v>
-      </c>
-      <c r="D289" s="7" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B290" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" s="10" t="s">
         <v>413</v>
-      </c>
-      <c r="B290" t="s">
-        <v>6</v>
-      </c>
-      <c r="D290" s="10" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B291" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" s="10" t="s">
         <v>415</v>
-      </c>
-      <c r="B291" t="s">
-        <v>6</v>
-      </c>
-      <c r="D291" s="10" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B292" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292" s="10" t="s">
         <v>417</v>
-      </c>
-      <c r="B292" t="s">
-        <v>6</v>
-      </c>
-      <c r="D292" s="10" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B293" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="B293" t="s">
-        <v>6</v>
-      </c>
-      <c r="D293" s="10" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B294" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" s="10" t="s">
         <v>421</v>
-      </c>
-      <c r="B294" t="s">
-        <v>6</v>
-      </c>
-      <c r="D294" s="10" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
+        <v>422</v>
+      </c>
+      <c r="B295" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" s="10" t="s">
         <v>423</v>
-      </c>
-      <c r="B295" t="s">
-        <v>6</v>
-      </c>
-      <c r="D295" s="10" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B296" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" s="10" t="s">
         <v>425</v>
-      </c>
-      <c r="B296" t="s">
-        <v>6</v>
-      </c>
-      <c r="D296" s="10" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B297" t="s">
+        <v>6</v>
+      </c>
+      <c r="D297" s="10" t="s">
         <v>427</v>
-      </c>
-      <c r="B297" t="s">
-        <v>6</v>
-      </c>
-      <c r="D297" s="10" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B298" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" s="10" t="s">
         <v>429</v>
-      </c>
-      <c r="B298" t="s">
-        <v>6</v>
-      </c>
-      <c r="D298" s="10" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B299" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" s="17" t="s">
         <v>431</v>
-      </c>
-      <c r="B299" t="s">
-        <v>6</v>
-      </c>
-      <c r="D299" s="17" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B300" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B301" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B302" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B303" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B304" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B305" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B306" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B307" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B308" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B309" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B310" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C310" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B311" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C311" t="s">
+        <v>991</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B312" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C312" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B313" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C313" t="s">
+        <v>993</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="B314" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C314" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B315" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C315" t="s">
+        <v>995</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B316" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C316" t="s">
+        <v>996</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B317" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C317" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B318" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C318" t="s">
+        <v>998</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B319" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B320" t="s">
+        <v>6</v>
+      </c>
+      <c r="D320" s="8" t="s">
         <v>453</v>
-      </c>
-      <c r="B320" t="s">
-        <v>6</v>
-      </c>
-      <c r="D320" s="8" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B321" t="s">
+        <v>6</v>
+      </c>
+      <c r="D321" s="10" t="s">
         <v>455</v>
-      </c>
-      <c r="B321" t="s">
-        <v>6</v>
-      </c>
-      <c r="D321" s="10" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B322" t="s">
+        <v>6</v>
+      </c>
+      <c r="D322" s="10" t="s">
         <v>457</v>
-      </c>
-      <c r="B322" t="s">
-        <v>6</v>
-      </c>
-      <c r="D322" s="10" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B323" t="s">
         <v>29</v>
@@ -6760,7 +6934,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B324" t="s">
         <v>29</v>
@@ -6768,1000 +6942,1000 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B325" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" t="s">
         <v>461</v>
-      </c>
-      <c r="B325" t="s">
-        <v>6</v>
-      </c>
-      <c r="D325" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B326" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" s="25" t="s">
         <v>463</v>
-      </c>
-      <c r="B326" t="s">
-        <v>6</v>
-      </c>
-      <c r="D326" s="25" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B327" t="s">
+        <v>6</v>
+      </c>
+      <c r="D327" s="25" t="s">
         <v>465</v>
-      </c>
-      <c r="B327" t="s">
-        <v>6</v>
-      </c>
-      <c r="D327" s="25" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B328" t="s">
+        <v>6</v>
+      </c>
+      <c r="D328" s="25" t="s">
         <v>467</v>
-      </c>
-      <c r="B328" t="s">
-        <v>6</v>
-      </c>
-      <c r="D328" s="25" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B329" t="s">
+        <v>6</v>
+      </c>
+      <c r="D329" s="25" t="s">
         <v>469</v>
-      </c>
-      <c r="B329" t="s">
-        <v>6</v>
-      </c>
-      <c r="D329" s="25" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B330" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="B330" t="s">
-        <v>6</v>
-      </c>
-      <c r="D330" s="10" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B331" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" s="26" t="s">
         <v>473</v>
-      </c>
-      <c r="B331" t="s">
-        <v>6</v>
-      </c>
-      <c r="D331" s="26" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B332" t="s">
+        <v>6</v>
+      </c>
+      <c r="D332" s="27" t="s">
         <v>475</v>
-      </c>
-      <c r="B332" t="s">
-        <v>6</v>
-      </c>
-      <c r="D332" s="27" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B333" t="s">
+        <v>6</v>
+      </c>
+      <c r="D333" s="27" t="s">
         <v>477</v>
-      </c>
-      <c r="B333" t="s">
-        <v>6</v>
-      </c>
-      <c r="D333" s="27" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B334" t="s">
+        <v>6</v>
+      </c>
+      <c r="D334" s="27" t="s">
         <v>479</v>
-      </c>
-      <c r="B334" t="s">
-        <v>6</v>
-      </c>
-      <c r="D334" s="27" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B335" t="s">
+        <v>6</v>
+      </c>
+      <c r="D335" s="26" t="s">
         <v>481</v>
-      </c>
-      <c r="B335" t="s">
-        <v>6</v>
-      </c>
-      <c r="D335" s="26" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B336" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" s="27" t="s">
         <v>483</v>
-      </c>
-      <c r="B336" t="s">
-        <v>6</v>
-      </c>
-      <c r="D336" s="27" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B337" t="s">
+        <v>6</v>
+      </c>
+      <c r="D337" s="27" t="s">
         <v>485</v>
-      </c>
-      <c r="B337" t="s">
-        <v>6</v>
-      </c>
-      <c r="D337" s="27" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B338" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" s="27" t="s">
         <v>487</v>
-      </c>
-      <c r="B338" t="s">
-        <v>6</v>
-      </c>
-      <c r="D338" s="27" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B339" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="26" t="s">
         <v>489</v>
-      </c>
-      <c r="B339" t="s">
-        <v>6</v>
-      </c>
-      <c r="D339" s="26" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B340" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="27" t="s">
         <v>491</v>
-      </c>
-      <c r="B340" t="s">
-        <v>6</v>
-      </c>
-      <c r="D340" s="27" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B341" t="s">
+        <v>6</v>
+      </c>
+      <c r="C341" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B341" t="s">
-        <v>6</v>
-      </c>
-      <c r="C341" s="2" t="s">
+      <c r="D341" s="27" t="s">
         <v>494</v>
-      </c>
-      <c r="D341" s="27" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B342" t="s">
+        <v>6</v>
+      </c>
+      <c r="C342" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B342" t="s">
-        <v>6</v>
-      </c>
-      <c r="C342" s="2" t="s">
+      <c r="D342" s="27" t="s">
         <v>497</v>
-      </c>
-      <c r="D342" s="27" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B343" t="s">
+        <v>6</v>
+      </c>
+      <c r="C343" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B343" t="s">
-        <v>6</v>
-      </c>
-      <c r="C343" s="2" t="s">
+      <c r="D343" s="27" t="s">
         <v>500</v>
-      </c>
-      <c r="D343" s="27" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B344" t="s">
+        <v>6</v>
+      </c>
+      <c r="C344" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B344" t="s">
-        <v>6</v>
-      </c>
-      <c r="C344" s="2" t="s">
+      <c r="D344" s="27" t="s">
         <v>503</v>
-      </c>
-      <c r="D344" s="27" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B345" t="s">
+        <v>6</v>
+      </c>
+      <c r="C345" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B345" t="s">
-        <v>6</v>
-      </c>
-      <c r="C345" s="2" t="s">
+      <c r="D345" s="27" t="s">
         <v>506</v>
-      </c>
-      <c r="D345" s="27" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B346" t="s">
+        <v>6</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B346" t="s">
-        <v>6</v>
-      </c>
-      <c r="C346" s="2" t="s">
+      <c r="D346" s="27" t="s">
         <v>509</v>
-      </c>
-      <c r="D346" s="27" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B347" t="s">
+        <v>6</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B347" t="s">
-        <v>6</v>
-      </c>
-      <c r="C347" s="2" t="s">
+      <c r="D347" s="27" t="s">
         <v>512</v>
-      </c>
-      <c r="D347" s="27" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B348" t="s">
+        <v>6</v>
+      </c>
+      <c r="C348" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B348" t="s">
-        <v>6</v>
-      </c>
-      <c r="C348" s="2" t="s">
+      <c r="D348" s="27" t="s">
         <v>515</v>
-      </c>
-      <c r="D348" s="27" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B349" t="s">
+        <v>6</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B349" t="s">
-        <v>6</v>
-      </c>
-      <c r="C349" s="2" t="s">
+      <c r="D349" s="27" t="s">
         <v>518</v>
-      </c>
-      <c r="D349" s="27" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B350" t="s">
+        <v>6</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B350" t="s">
-        <v>6</v>
-      </c>
-      <c r="C350" s="2" t="s">
+      <c r="D350" s="27" t="s">
         <v>521</v>
-      </c>
-      <c r="D350" s="27" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B351" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B351" t="s">
-        <v>6</v>
-      </c>
-      <c r="C351" s="2" t="s">
+      <c r="D351" s="27" t="s">
         <v>524</v>
-      </c>
-      <c r="D351" s="27" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B352" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B352" t="s">
-        <v>6</v>
-      </c>
-      <c r="C352" s="2" t="s">
+      <c r="D352" s="27" t="s">
         <v>527</v>
-      </c>
-      <c r="D352" s="27" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B353" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B353" t="s">
-        <v>6</v>
-      </c>
-      <c r="C353" s="2" t="s">
+      <c r="D353" s="27" t="s">
         <v>530</v>
-      </c>
-      <c r="D353" s="27" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B354" t="s">
+        <v>6</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B354" t="s">
-        <v>6</v>
-      </c>
-      <c r="C354" s="2" t="s">
+      <c r="D354" s="34" t="s">
         <v>533</v>
-      </c>
-      <c r="D354" s="34" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B355" t="s">
+        <v>6</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B355" t="s">
-        <v>6</v>
-      </c>
-      <c r="C355" s="2" t="s">
+      <c r="D355" s="27" t="s">
         <v>536</v>
-      </c>
-      <c r="D355" s="27" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B356" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B356" t="s">
-        <v>6</v>
-      </c>
-      <c r="C356" s="2" t="s">
+      <c r="D356" s="27" t="s">
         <v>539</v>
-      </c>
-      <c r="D356" s="27" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="35" t="s">
+        <v>540</v>
+      </c>
+      <c r="B357" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B357" t="s">
-        <v>6</v>
-      </c>
-      <c r="C357" s="2" t="s">
+      <c r="D357" s="36" t="s">
         <v>542</v>
-      </c>
-      <c r="D357" s="36" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B358" t="s">
         <v>15</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D358" s="27"/>
     </row>
     <row r="359" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="35" t="s">
+        <v>544</v>
+      </c>
+      <c r="B359" t="s">
+        <v>6</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B359" t="s">
-        <v>6</v>
-      </c>
-      <c r="C359" s="2" t="s">
+      <c r="D359" s="36" t="s">
         <v>546</v>
-      </c>
-      <c r="D359" s="36" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="35" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B360" t="s">
         <v>15</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D360" s="27"/>
     </row>
     <row r="361" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="35" t="s">
+        <v>548</v>
+      </c>
+      <c r="B361" t="s">
+        <v>6</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B361" t="s">
-        <v>6</v>
-      </c>
-      <c r="C361" s="2" t="s">
+      <c r="D361" s="36" t="s">
         <v>550</v>
-      </c>
-      <c r="D361" s="36" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="35" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B362" t="s">
         <v>15</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D362" s="27"/>
     </row>
     <row r="363" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="B363" t="s">
+        <v>6</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B363" t="s">
-        <v>6</v>
-      </c>
-      <c r="C363" s="2" t="s">
+      <c r="D363" s="36" t="s">
         <v>554</v>
-      </c>
-      <c r="D363" s="36" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="35" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B364" t="s">
         <v>15</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D364" s="27"/>
     </row>
     <row r="365" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="B365" t="s">
+        <v>6</v>
+      </c>
+      <c r="C365" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B365" t="s">
-        <v>6</v>
-      </c>
-      <c r="C365" s="2" t="s">
+      <c r="D365" s="36" t="s">
         <v>558</v>
-      </c>
-      <c r="D365" s="36" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="35" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B366" t="s">
         <v>15</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D366" s="27"/>
     </row>
     <row r="367" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="B367" t="s">
+        <v>6</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B367" t="s">
-        <v>6</v>
-      </c>
-      <c r="C367" s="2" t="s">
+      <c r="D367" s="36" t="s">
         <v>562</v>
-      </c>
-      <c r="D367" s="36" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="35" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B368" t="s">
         <v>15</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D368" s="27"/>
     </row>
     <row r="369" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="B369" t="s">
+        <v>6</v>
+      </c>
+      <c r="C369" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B369" t="s">
-        <v>6</v>
-      </c>
-      <c r="C369" s="2" t="s">
+      <c r="D369" s="36" t="s">
         <v>566</v>
-      </c>
-      <c r="D369" s="36" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B370" t="s">
         <v>15</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D370" s="27"/>
     </row>
     <row r="371" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="B371" t="s">
+        <v>6</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B371" t="s">
-        <v>6</v>
-      </c>
-      <c r="C371" s="2" t="s">
+      <c r="D371" s="36" t="s">
         <v>570</v>
-      </c>
-      <c r="D371" s="36" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="35" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B372" t="s">
         <v>15</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D372" s="36"/>
     </row>
     <row r="373" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="B373" t="s">
+        <v>6</v>
+      </c>
+      <c r="C373" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B373" t="s">
-        <v>6</v>
-      </c>
-      <c r="C373" s="2" t="s">
+      <c r="D373" s="36" t="s">
         <v>574</v>
-      </c>
-      <c r="D373" s="36" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="35" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B374" t="s">
         <v>15</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D374" s="27"/>
     </row>
     <row r="375" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="B375" t="s">
+        <v>6</v>
+      </c>
+      <c r="C375" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B375" t="s">
-        <v>6</v>
-      </c>
-      <c r="C375" s="2" t="s">
+      <c r="D375" s="36" t="s">
         <v>578</v>
-      </c>
-      <c r="D375" s="36" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="35" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B376" t="s">
         <v>15</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D376" s="27"/>
     </row>
     <row r="377" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="B377" t="s">
+        <v>6</v>
+      </c>
+      <c r="C377" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B377" t="s">
-        <v>6</v>
-      </c>
-      <c r="C377" s="2" t="s">
+      <c r="D377" s="36" t="s">
         <v>582</v>
-      </c>
-      <c r="D377" s="36" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="35" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B378" t="s">
         <v>15</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D378" s="27"/>
     </row>
     <row r="379" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="B379" t="s">
+        <v>6</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B379" t="s">
-        <v>6</v>
-      </c>
-      <c r="C379" s="2" t="s">
+      <c r="D379" s="36" t="s">
         <v>586</v>
-      </c>
-      <c r="D379" s="36" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="35" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B380" t="s">
         <v>15</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D380" s="27"/>
     </row>
     <row r="381" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="35" t="s">
+        <v>588</v>
+      </c>
+      <c r="B381" t="s">
+        <v>6</v>
+      </c>
+      <c r="C381" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B381" t="s">
-        <v>6</v>
-      </c>
-      <c r="C381" s="2" t="s">
+      <c r="D381" s="36" t="s">
         <v>590</v>
-      </c>
-      <c r="D381" s="36" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="35" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B382" t="s">
         <v>15</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D382" s="27"/>
     </row>
     <row r="383" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="B383" t="s">
+        <v>6</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B383" t="s">
-        <v>6</v>
-      </c>
-      <c r="C383" s="2" t="s">
+      <c r="D383" s="36" t="s">
         <v>594</v>
-      </c>
-      <c r="D383" s="36" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="35" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B384" t="s">
         <v>15</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D384" s="27"/>
     </row>
     <row r="385" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="35" t="s">
+        <v>596</v>
+      </c>
+      <c r="B385" t="s">
+        <v>6</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B385" t="s">
-        <v>6</v>
-      </c>
-      <c r="C385" s="2" t="s">
+      <c r="D385" s="36" t="s">
         <v>598</v>
-      </c>
-      <c r="D385" s="36" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="36" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B386" t="s">
         <v>15</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D386" s="27"/>
     </row>
     <row r="387" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="B387" t="s">
+        <v>6</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B387" t="s">
-        <v>6</v>
-      </c>
-      <c r="C387" s="2" t="s">
+      <c r="D387" s="27" t="s">
         <v>602</v>
-      </c>
-      <c r="D387" s="27" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="388" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="37" t="s">
+        <v>603</v>
+      </c>
+      <c r="B388" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B388" t="s">
-        <v>6</v>
-      </c>
-      <c r="C388" s="2" t="s">
+      <c r="D388" s="27" t="s">
         <v>605</v>
-      </c>
-      <c r="D388" s="27" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="389" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="B389" t="s">
+        <v>6</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B389" t="s">
-        <v>6</v>
-      </c>
-      <c r="C389" s="2" t="s">
+      <c r="D389" s="27" t="s">
         <v>608</v>
-      </c>
-      <c r="D389" s="27" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="390" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B390" t="s">
+        <v>6</v>
+      </c>
+      <c r="C390" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B390" t="s">
-        <v>6</v>
-      </c>
-      <c r="C390" s="2" t="s">
+      <c r="D390" s="27" t="s">
         <v>611</v>
-      </c>
-      <c r="D390" s="27" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B391" t="s">
+        <v>6</v>
+      </c>
+      <c r="C391" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B391" t="s">
-        <v>6</v>
-      </c>
-      <c r="C391" s="2" t="s">
+      <c r="D391" s="27" t="s">
         <v>614</v>
-      </c>
-      <c r="D391" s="27" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="392" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B392" t="s">
+        <v>6</v>
+      </c>
+      <c r="C392" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B392" t="s">
-        <v>6</v>
-      </c>
-      <c r="C392" s="2" t="s">
+      <c r="D392" s="27" t="s">
         <v>617</v>
-      </c>
-      <c r="D392" s="27" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="393" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="37" t="s">
+        <v>618</v>
+      </c>
+      <c r="B393" t="s">
+        <v>6</v>
+      </c>
+      <c r="C393" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B393" t="s">
-        <v>6</v>
-      </c>
-      <c r="C393" s="2" t="s">
+      <c r="D393" s="27" t="s">
         <v>620</v>
-      </c>
-      <c r="D393" s="27" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="394" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="B394" t="s">
+        <v>6</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B394" t="s">
-        <v>6</v>
-      </c>
-      <c r="C394" s="2" t="s">
+      <c r="D394" s="27" t="s">
         <v>623</v>
-      </c>
-      <c r="D394" s="27" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="395" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="36" t="s">
+        <v>624</v>
+      </c>
+      <c r="B395" t="s">
+        <v>6</v>
+      </c>
+      <c r="C395" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B395" t="s">
-        <v>6</v>
-      </c>
-      <c r="C395" s="2" t="s">
+      <c r="D395" s="27" t="s">
         <v>626</v>
-      </c>
-      <c r="D395" s="27" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="396" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="36" t="s">
+        <v>627</v>
+      </c>
+      <c r="B396" t="s">
+        <v>6</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B396" t="s">
-        <v>6</v>
-      </c>
-      <c r="C396" s="2" t="s">
+      <c r="D396" s="27" t="s">
         <v>629</v>
-      </c>
-      <c r="D396" s="27" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="397" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B397" t="s">
+        <v>6</v>
+      </c>
+      <c r="C397" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B397" t="s">
-        <v>6</v>
-      </c>
-      <c r="C397" s="2" t="s">
+      <c r="D397" s="27" t="s">
         <v>632</v>
-      </c>
-      <c r="D397" s="27" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="398" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B398" t="s">
+        <v>6</v>
+      </c>
+      <c r="C398" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B398" t="s">
-        <v>6</v>
-      </c>
-      <c r="C398" s="2" t="s">
+      <c r="D398" s="27" t="s">
         <v>635</v>
-      </c>
-      <c r="D398" s="27" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>636</v>
+      </c>
+      <c r="B399" t="s">
         <v>637</v>
       </c>
-      <c r="B399" t="s">
+      <c r="E399" t="s">
         <v>638</v>
-      </c>
-      <c r="E399" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="400" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B400" t="s">
         <v>6</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="26" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B401" t="s">
         <v>6</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="40" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B402" t="s">
         <v>15</v>
@@ -7771,21 +7945,21 @@
     </row>
     <row r="403" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B403" t="s">
+        <v>6</v>
+      </c>
+      <c r="C403" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B403" t="s">
-        <v>6</v>
-      </c>
-      <c r="C403" s="2" t="s">
+      <c r="D403" s="27" t="s">
         <v>646</v>
-      </c>
-      <c r="D403" s="27" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B404" t="s">
         <v>15</v>
@@ -7795,638 +7969,638 @@
     </row>
     <row r="405" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B405" t="s">
         <v>225</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D405" s="27"/>
     </row>
     <row r="406" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B406" t="s">
         <v>225</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D406" s="27"/>
     </row>
     <row r="407" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B407" t="s">
         <v>225</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D407" s="27"/>
     </row>
     <row r="408" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B408" t="s">
         <v>225</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D408" s="27"/>
     </row>
     <row r="409" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B409" t="s">
         <v>225</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D409" s="27"/>
     </row>
     <row r="410" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B410" t="s">
         <v>225</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D410" s="27"/>
     </row>
     <row r="411" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B411" t="s">
         <v>225</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D411" s="27"/>
     </row>
     <row r="412" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B412" t="s">
         <v>225</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D412" s="27"/>
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B413" t="s">
         <v>6</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" s="26" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B414" t="s">
         <v>6</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" s="26" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B415" t="s">
         <v>6</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="38" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B416" t="s">
+        <v>6</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D416" s="39" t="s">
         <v>670</v>
-      </c>
-      <c r="B416" t="s">
-        <v>6</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D416" s="39" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B417" t="s">
+        <v>6</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D417" s="39" t="s">
         <v>672</v>
-      </c>
-      <c r="B417" t="s">
-        <v>6</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D417" s="39" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B418" t="s">
+        <v>6</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D418" s="39" t="s">
         <v>674</v>
-      </c>
-      <c r="B418" t="s">
-        <v>6</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D418" s="39" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B419" t="s">
+        <v>6</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D419" s="39" t="s">
         <v>676</v>
-      </c>
-      <c r="B419" t="s">
-        <v>6</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D419" s="39" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B420" t="s">
+        <v>6</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D420" s="39" t="s">
         <v>678</v>
-      </c>
-      <c r="B420" t="s">
-        <v>6</v>
-      </c>
-      <c r="C420" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D420" s="39" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B421" t="s">
+        <v>6</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D421" s="39" t="s">
         <v>680</v>
-      </c>
-      <c r="B421" t="s">
-        <v>6</v>
-      </c>
-      <c r="C421" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="D421" s="39" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B422" t="s">
+        <v>6</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D422" s="39" t="s">
         <v>682</v>
-      </c>
-      <c r="B422" t="s">
-        <v>6</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D422" s="39" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B423" t="s">
+        <v>6</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D423" s="39" t="s">
         <v>684</v>
-      </c>
-      <c r="B423" t="s">
-        <v>6</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D423" s="39" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B424" t="s">
         <v>6</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" s="38" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B425" t="s">
         <v>6</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B426" t="s">
+        <v>6</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D426" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="B426" t="s">
-        <v>6</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D426" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B427" t="s">
+        <v>6</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D427" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="B427" t="s">
-        <v>6</v>
-      </c>
-      <c r="C427" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D427" s="2" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B428" t="s">
         <v>6</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B429" t="s">
+        <v>6</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D429" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="B429" t="s">
-        <v>6</v>
-      </c>
-      <c r="C429" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D429" s="2" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B430" t="s">
         <v>6</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B431" t="s">
+        <v>6</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D431" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="B431" t="s">
-        <v>6</v>
-      </c>
-      <c r="C431" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D431" s="2" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B432" t="s">
+        <v>6</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D432" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B432" t="s">
-        <v>6</v>
-      </c>
-      <c r="C432" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D432" s="2" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="433" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B433" t="s">
+        <v>6</v>
+      </c>
+      <c r="D433" s="26" t="s">
         <v>701</v>
-      </c>
-      <c r="B433" t="s">
-        <v>6</v>
-      </c>
-      <c r="D433" s="26" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="434" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B434" t="s">
+        <v>6</v>
+      </c>
+      <c r="D434" s="27" t="s">
         <v>703</v>
-      </c>
-      <c r="B434" t="s">
-        <v>6</v>
-      </c>
-      <c r="D434" s="27" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
+        <v>704</v>
+      </c>
+      <c r="B435" t="s">
         <v>705</v>
-      </c>
-      <c r="B435" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B436" t="s">
+        <v>6</v>
+      </c>
+      <c r="D436" t="s">
         <v>707</v>
-      </c>
-      <c r="B436" t="s">
-        <v>6</v>
-      </c>
-      <c r="D436" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
+        <v>708</v>
+      </c>
+      <c r="B437" t="s">
+        <v>637</v>
+      </c>
+      <c r="E437" t="s">
         <v>709</v>
-      </c>
-      <c r="B437" t="s">
-        <v>638</v>
-      </c>
-      <c r="E437" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="438" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B438" t="s">
+        <v>6</v>
+      </c>
+      <c r="D438" s="33" t="s">
         <v>711</v>
-      </c>
-      <c r="B438" t="s">
-        <v>6</v>
-      </c>
-      <c r="D438" s="33" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B439" t="s">
         <v>6</v>
       </c>
       <c r="C439" s="2"/>
       <c r="D439" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B440" t="s">
+        <v>6</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D440" t="s">
         <v>715</v>
-      </c>
-      <c r="B440" t="s">
-        <v>6</v>
-      </c>
-      <c r="C440" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D440" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B441" t="s">
+        <v>6</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D441" t="s">
         <v>717</v>
-      </c>
-      <c r="B441" t="s">
-        <v>6</v>
-      </c>
-      <c r="C441" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="D441" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B442" t="s">
+        <v>6</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D442" t="s">
         <v>719</v>
-      </c>
-      <c r="B442" t="s">
-        <v>6</v>
-      </c>
-      <c r="C442" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D442" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B443" t="s">
+        <v>6</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D443" t="s">
         <v>721</v>
-      </c>
-      <c r="B443" t="s">
-        <v>6</v>
-      </c>
-      <c r="C443" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D443" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B444" t="s">
+        <v>6</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D444" t="s">
         <v>723</v>
-      </c>
-      <c r="B444" t="s">
-        <v>6</v>
-      </c>
-      <c r="C444" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D444" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B445" t="s">
+        <v>6</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D445" t="s">
         <v>725</v>
-      </c>
-      <c r="B445" t="s">
-        <v>6</v>
-      </c>
-      <c r="C445" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D445" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="446" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B446" t="s">
         <v>6</v>
       </c>
       <c r="C446" s="2"/>
       <c r="D446" s="26" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="447" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B447" t="s">
         <v>6</v>
       </c>
       <c r="C447" s="2"/>
       <c r="D447" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="448" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B448" t="s">
         <v>6</v>
       </c>
       <c r="C448" s="2"/>
       <c r="D448" s="10" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="449" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B449" t="s">
         <v>6</v>
       </c>
       <c r="C449" s="2"/>
       <c r="D449" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B450" t="s">
+        <v>6</v>
+      </c>
+      <c r="C450" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B450" t="s">
-        <v>6</v>
-      </c>
-      <c r="C450" s="2" t="s">
+      <c r="D450" t="s">
         <v>736</v>
-      </c>
-      <c r="D450" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B451" t="s">
+        <v>6</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="B451" t="s">
-        <v>6</v>
-      </c>
-      <c r="C451" s="2" t="s">
+      <c r="D451" t="s">
         <v>739</v>
-      </c>
-      <c r="D451" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="452" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="30" t="s">
+        <v>740</v>
+      </c>
+      <c r="B452" t="s">
+        <v>6</v>
+      </c>
+      <c r="C452" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B452" t="s">
-        <v>6</v>
-      </c>
-      <c r="C452" s="2" t="s">
+      <c r="D452" t="s">
         <v>742</v>
-      </c>
-      <c r="D452" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="453" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B453" t="s">
+        <v>6</v>
+      </c>
+      <c r="C453" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="B453" t="s">
-        <v>6</v>
-      </c>
-      <c r="C453" s="2" t="s">
+      <c r="D453" t="s">
         <v>745</v>
-      </c>
-      <c r="D453" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="28" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B454" s="28" t="s">
         <v>15</v>
@@ -8435,7 +8609,7 @@
     </row>
     <row r="455" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="31" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B455" s="28" t="s">
         <v>15</v>
@@ -8443,7 +8617,7 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="28" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B456" s="28" t="s">
         <v>15</v>
@@ -8451,7 +8625,7 @@
     </row>
     <row r="457" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="32" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B457" s="28" t="s">
         <v>15</v>
@@ -8459,7 +8633,7 @@
     </row>
     <row r="458" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="31" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B458" s="28" t="s">
         <v>15</v>
@@ -8467,7 +8641,7 @@
     </row>
     <row r="459" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="31" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B459" s="28" t="s">
         <v>15</v>
@@ -8475,7 +8649,7 @@
     </row>
     <row r="460" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B460" s="28" t="s">
         <v>15</v>
@@ -8484,7 +8658,7 @@
     </row>
     <row r="461" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="31" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B461" s="28" t="s">
         <v>15</v>
@@ -8492,7 +8666,7 @@
     </row>
     <row r="462" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="32" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B462" s="28" t="s">
         <v>15</v>
@@ -8501,7 +8675,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="28" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B463" s="28" t="s">
         <v>15</v>
@@ -8511,130 +8685,130 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="E464" t="s">
         <v>757</v>
-      </c>
-      <c r="B464" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C464" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E464" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="E465" t="s">
         <v>759</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="E465" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E466" t="s">
         <v>761</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="E466" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="467" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B467" t="s">
+        <v>6</v>
+      </c>
+      <c r="D467" s="10" t="s">
         <v>763</v>
-      </c>
-      <c r="B467" t="s">
-        <v>6</v>
-      </c>
-      <c r="D467" s="10" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="468" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B468" t="s">
+        <v>6</v>
+      </c>
+      <c r="C468" t="s">
         <v>765</v>
       </c>
-      <c r="B468" t="s">
-        <v>6</v>
-      </c>
-      <c r="C468" t="s">
+      <c r="D468" s="10" t="s">
         <v>766</v>
-      </c>
-      <c r="D468" s="10" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B469" t="s">
+        <v>6</v>
+      </c>
+      <c r="C469" t="s">
         <v>768</v>
       </c>
-      <c r="B469" t="s">
-        <v>6</v>
-      </c>
-      <c r="C469" t="s">
+      <c r="D469" t="s">
         <v>769</v>
-      </c>
-      <c r="D469" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B470" t="s">
+        <v>6</v>
+      </c>
+      <c r="C470" t="s">
         <v>771</v>
       </c>
-      <c r="B470" t="s">
-        <v>6</v>
-      </c>
-      <c r="C470" t="s">
+      <c r="D470" t="s">
         <v>772</v>
-      </c>
-      <c r="D470" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B471" t="s">
+        <v>6</v>
+      </c>
+      <c r="C471" t="s">
         <v>774</v>
       </c>
-      <c r="B471" t="s">
-        <v>6</v>
-      </c>
-      <c r="C471" t="s">
+      <c r="D471" t="s">
         <v>775</v>
-      </c>
-      <c r="D471" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B472" t="s">
+        <v>6</v>
+      </c>
+      <c r="C472" t="s">
         <v>777</v>
       </c>
-      <c r="B472" t="s">
-        <v>6</v>
-      </c>
-      <c r="C472" t="s">
+      <c r="D472" t="s">
         <v>778</v>
-      </c>
-      <c r="D472" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B473" t="s">
         <v>15</v>
@@ -8642,7 +8816,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B474" t="s">
         <v>15</v>
@@ -8650,76 +8824,76 @@
     </row>
     <row r="475" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B475" t="s">
+        <v>6</v>
+      </c>
+      <c r="C475" s="41" t="s">
         <v>782</v>
       </c>
-      <c r="B475" t="s">
-        <v>6</v>
-      </c>
-      <c r="C475" s="41" t="s">
-        <v>783</v>
-      </c>
       <c r="D475" s="42" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="476" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B476" t="s">
+        <v>6</v>
+      </c>
+      <c r="D476" s="42" t="s">
         <v>784</v>
-      </c>
-      <c r="B476" t="s">
-        <v>6</v>
-      </c>
-      <c r="D476" s="42" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B477" t="s">
+        <v>6</v>
+      </c>
+      <c r="D477" s="38" t="s">
         <v>786</v>
-      </c>
-      <c r="B477" t="s">
-        <v>6</v>
-      </c>
-      <c r="D477" s="38" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B478" t="s">
+        <v>6</v>
+      </c>
+      <c r="D478" t="s">
         <v>788</v>
-      </c>
-      <c r="B478" t="s">
-        <v>6</v>
-      </c>
-      <c r="D478" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B479" t="s">
+        <v>6</v>
+      </c>
+      <c r="D479" s="38" t="s">
         <v>790</v>
-      </c>
-      <c r="B479" t="s">
-        <v>6</v>
-      </c>
-      <c r="D479" s="38" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B480" t="s">
+        <v>6</v>
+      </c>
+      <c r="D480" t="s">
         <v>792</v>
-      </c>
-      <c r="B480" t="s">
-        <v>6</v>
-      </c>
-      <c r="D480" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B481" t="s">
         <v>6</v>
@@ -8727,7 +8901,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B482" t="s">
         <v>6</v>
@@ -8735,305 +8909,305 @@
     </row>
     <row r="483" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B483" t="s">
+        <v>6</v>
+      </c>
+      <c r="D483" s="10" t="s">
         <v>796</v>
-      </c>
-      <c r="B483" t="s">
-        <v>6</v>
-      </c>
-      <c r="D483" s="10" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B484" t="s">
+        <v>6</v>
+      </c>
+      <c r="C484" t="s">
         <v>798</v>
       </c>
-      <c r="B484" t="s">
-        <v>6</v>
-      </c>
-      <c r="C484" t="s">
+      <c r="D484" t="s">
         <v>799</v>
-      </c>
-      <c r="D484" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B485" t="s">
+        <v>6</v>
+      </c>
+      <c r="C485" t="s">
         <v>801</v>
       </c>
-      <c r="B485" t="s">
-        <v>6</v>
-      </c>
-      <c r="C485" t="s">
+      <c r="D485" t="s">
         <v>802</v>
-      </c>
-      <c r="D485" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B486" t="s">
+        <v>6</v>
+      </c>
+      <c r="C486" t="s">
         <v>804</v>
       </c>
-      <c r="B486" t="s">
-        <v>6</v>
-      </c>
-      <c r="C486" t="s">
+      <c r="D486" t="s">
         <v>805</v>
-      </c>
-      <c r="D486" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B487" t="s">
         <v>6</v>
       </c>
       <c r="C487" s="41" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D487" s="42" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B488" t="s">
         <v>6</v>
       </c>
       <c r="D488" s="42" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B489" t="s">
+        <v>6</v>
+      </c>
+      <c r="D489" s="38" t="s">
         <v>809</v>
-      </c>
-      <c r="B489" t="s">
-        <v>6</v>
-      </c>
-      <c r="D489" s="38" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B490" t="s">
+        <v>6</v>
+      </c>
+      <c r="D490" s="43" t="s">
         <v>811</v>
-      </c>
-      <c r="B490" t="s">
-        <v>6</v>
-      </c>
-      <c r="D490" s="43" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B491" t="s">
+        <v>6</v>
+      </c>
+      <c r="D491" s="38" t="s">
         <v>813</v>
-      </c>
-      <c r="B491" t="s">
-        <v>6</v>
-      </c>
-      <c r="D491" s="38" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B492" t="s">
+        <v>6</v>
+      </c>
+      <c r="D492" s="44" t="s">
         <v>815</v>
-      </c>
-      <c r="B492" t="s">
-        <v>6</v>
-      </c>
-      <c r="D492" s="44" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B493" t="s">
+        <v>6</v>
+      </c>
+      <c r="D493" s="38" t="s">
         <v>817</v>
-      </c>
-      <c r="B493" t="s">
-        <v>6</v>
-      </c>
-      <c r="D493" s="38" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B494" t="s">
+        <v>6</v>
+      </c>
+      <c r="D494" s="44" t="s">
         <v>819</v>
-      </c>
-      <c r="B494" t="s">
-        <v>6</v>
-      </c>
-      <c r="D494" s="44" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B495" t="s">
+        <v>6</v>
+      </c>
+      <c r="D495" s="38" t="s">
         <v>821</v>
-      </c>
-      <c r="B495" t="s">
-        <v>6</v>
-      </c>
-      <c r="D495" s="38" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B496" t="s">
+        <v>6</v>
+      </c>
+      <c r="D496" s="44" t="s">
         <v>823</v>
-      </c>
-      <c r="B496" t="s">
-        <v>6</v>
-      </c>
-      <c r="D496" s="44" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B497" t="s">
+        <v>6</v>
+      </c>
+      <c r="D497" s="38" t="s">
         <v>825</v>
-      </c>
-      <c r="B497" t="s">
-        <v>6</v>
-      </c>
-      <c r="D497" s="38" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B498" t="s">
+        <v>6</v>
+      </c>
+      <c r="D498" s="44" t="s">
         <v>827</v>
-      </c>
-      <c r="B498" t="s">
-        <v>6</v>
-      </c>
-      <c r="D498" s="44" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B499" t="s">
+        <v>6</v>
+      </c>
+      <c r="D499" s="39" t="s">
         <v>829</v>
-      </c>
-      <c r="B499" t="s">
-        <v>6</v>
-      </c>
-      <c r="D499" s="39" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B500" t="s">
+        <v>6</v>
+      </c>
+      <c r="D500" s="38" t="s">
         <v>831</v>
-      </c>
-      <c r="B500" t="s">
-        <v>6</v>
-      </c>
-      <c r="D500" s="38" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B501" t="s">
+        <v>6</v>
+      </c>
+      <c r="D501" s="39" t="s">
         <v>833</v>
-      </c>
-      <c r="B501" t="s">
-        <v>6</v>
-      </c>
-      <c r="D501" s="39" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B502" t="s">
+        <v>6</v>
+      </c>
+      <c r="D502" s="38" t="s">
         <v>835</v>
-      </c>
-      <c r="B502" t="s">
-        <v>6</v>
-      </c>
-      <c r="D502" s="38" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B503" t="s">
+        <v>6</v>
+      </c>
+      <c r="D503" s="39" t="s">
         <v>837</v>
-      </c>
-      <c r="B503" t="s">
-        <v>6</v>
-      </c>
-      <c r="D503" s="39" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B504" t="s">
+        <v>6</v>
+      </c>
+      <c r="D504" s="38" t="s">
         <v>839</v>
-      </c>
-      <c r="B504" t="s">
-        <v>6</v>
-      </c>
-      <c r="D504" s="38" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B505" t="s">
+        <v>6</v>
+      </c>
+      <c r="D505" s="39" t="s">
         <v>841</v>
-      </c>
-      <c r="B505" t="s">
-        <v>6</v>
-      </c>
-      <c r="D505" s="39" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B506" t="s">
+        <v>6</v>
+      </c>
+      <c r="D506" s="38" t="s">
         <v>843</v>
-      </c>
-      <c r="B506" t="s">
-        <v>6</v>
-      </c>
-      <c r="D506" s="38" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B507" t="s">
+        <v>6</v>
+      </c>
+      <c r="D507" s="39" t="s">
         <v>845</v>
-      </c>
-      <c r="B507" t="s">
-        <v>6</v>
-      </c>
-      <c r="D507" s="39" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B508" t="s">
+        <v>6</v>
+      </c>
+      <c r="D508" s="38" t="s">
         <v>847</v>
-      </c>
-      <c r="B508" t="s">
-        <v>6</v>
-      </c>
-      <c r="D508" s="38" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B509" t="s">
         <v>225</v>
@@ -9041,7 +9215,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B510" t="s">
         <v>225</v>
@@ -9049,583 +9223,583 @@
     </row>
     <row r="511" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B511" t="s">
+        <v>6</v>
+      </c>
+      <c r="D511" s="45" t="s">
         <v>850</v>
-      </c>
-      <c r="B511" t="s">
-        <v>6</v>
-      </c>
-      <c r="D511" s="45" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="512" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B512" t="s">
+        <v>6</v>
+      </c>
+      <c r="D512" s="46" t="s">
         <v>852</v>
-      </c>
-      <c r="B512" t="s">
-        <v>6</v>
-      </c>
-      <c r="D512" s="46" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="513" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B513" t="s">
+        <v>6</v>
+      </c>
+      <c r="D513" s="42" t="s">
         <v>854</v>
-      </c>
-      <c r="B513" t="s">
-        <v>6</v>
-      </c>
-      <c r="D513" s="42" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="514" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B514" t="s">
+        <v>6</v>
+      </c>
+      <c r="D514" s="42" t="s">
         <v>856</v>
-      </c>
-      <c r="B514" t="s">
-        <v>6</v>
-      </c>
-      <c r="D514" s="42" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="515" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B515" t="s">
+        <v>6</v>
+      </c>
+      <c r="D515" s="42" t="s">
         <v>858</v>
-      </c>
-      <c r="B515" t="s">
-        <v>6</v>
-      </c>
-      <c r="D515" s="42" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B516" t="s">
+        <v>6</v>
+      </c>
+      <c r="D516" s="38" t="s">
         <v>860</v>
-      </c>
-      <c r="B516" t="s">
-        <v>6</v>
-      </c>
-      <c r="D516" s="38" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B517" t="s">
+        <v>6</v>
+      </c>
+      <c r="D517" s="38" t="s">
         <v>862</v>
-      </c>
-      <c r="B517" t="s">
-        <v>6</v>
-      </c>
-      <c r="D517" s="38" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B518" t="s">
+        <v>6</v>
+      </c>
+      <c r="D518" s="38" t="s">
         <v>864</v>
-      </c>
-      <c r="B518" t="s">
-        <v>6</v>
-      </c>
-      <c r="D518" s="38" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B519" t="s">
+        <v>6</v>
+      </c>
+      <c r="D519" s="38" t="s">
         <v>866</v>
-      </c>
-      <c r="B519" t="s">
-        <v>6</v>
-      </c>
-      <c r="D519" s="38" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B520" t="s">
+        <v>6</v>
+      </c>
+      <c r="D520" s="38" t="s">
         <v>868</v>
-      </c>
-      <c r="B520" t="s">
-        <v>6</v>
-      </c>
-      <c r="D520" s="38" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B521" t="s">
+        <v>6</v>
+      </c>
+      <c r="D521" s="38" t="s">
         <v>870</v>
-      </c>
-      <c r="B521" t="s">
-        <v>6</v>
-      </c>
-      <c r="D521" s="38" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B522" t="s">
+        <v>6</v>
+      </c>
+      <c r="D522" s="38" t="s">
         <v>872</v>
-      </c>
-      <c r="B522" t="s">
-        <v>6</v>
-      </c>
-      <c r="D522" s="38" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B523" t="s">
+        <v>6</v>
+      </c>
+      <c r="D523" s="38" t="s">
         <v>874</v>
-      </c>
-      <c r="B523" t="s">
-        <v>6</v>
-      </c>
-      <c r="D523" s="38" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B524" t="s">
+        <v>6</v>
+      </c>
+      <c r="D524" s="38" t="s">
         <v>876</v>
-      </c>
-      <c r="B524" t="s">
-        <v>6</v>
-      </c>
-      <c r="D524" s="38" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B525" t="s">
+        <v>6</v>
+      </c>
+      <c r="D525" s="38" t="s">
         <v>878</v>
-      </c>
-      <c r="B525" t="s">
-        <v>6</v>
-      </c>
-      <c r="D525" s="38" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B526" t="s">
+        <v>6</v>
+      </c>
+      <c r="D526" s="38" t="s">
         <v>880</v>
-      </c>
-      <c r="B526" t="s">
-        <v>6</v>
-      </c>
-      <c r="D526" s="38" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="527" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B527" t="s">
+        <v>6</v>
+      </c>
+      <c r="D527" s="38" t="s">
         <v>882</v>
-      </c>
-      <c r="B527" t="s">
-        <v>6</v>
-      </c>
-      <c r="D527" s="38" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="528" spans="1:4" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B528" t="s">
+        <v>6</v>
+      </c>
+      <c r="D528" s="47" t="s">
         <v>884</v>
-      </c>
-      <c r="B528" t="s">
-        <v>6</v>
-      </c>
-      <c r="D528" s="47" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="529" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B529" t="s">
+        <v>6</v>
+      </c>
+      <c r="D529" s="48" t="s">
         <v>886</v>
-      </c>
-      <c r="B529" t="s">
-        <v>6</v>
-      </c>
-      <c r="D529" s="48" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="530" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B530" t="s">
+        <v>6</v>
+      </c>
+      <c r="D530" s="48" t="s">
         <v>888</v>
-      </c>
-      <c r="B530" t="s">
-        <v>6</v>
-      </c>
-      <c r="D530" s="48" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="531" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B531" t="s">
+        <v>6</v>
+      </c>
+      <c r="D531" s="48" t="s">
         <v>890</v>
-      </c>
-      <c r="B531" t="s">
-        <v>6</v>
-      </c>
-      <c r="D531" s="48" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="532" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B532" t="s">
+        <v>6</v>
+      </c>
+      <c r="D532" s="48" t="s">
         <v>892</v>
-      </c>
-      <c r="B532" t="s">
-        <v>6</v>
-      </c>
-      <c r="D532" s="48" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="533" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B533" t="s">
+        <v>6</v>
+      </c>
+      <c r="D533" s="48" t="s">
         <v>894</v>
-      </c>
-      <c r="B533" t="s">
-        <v>6</v>
-      </c>
-      <c r="D533" s="48" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="534" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B534" t="s">
+        <v>6</v>
+      </c>
+      <c r="D534" s="10" t="s">
         <v>896</v>
-      </c>
-      <c r="B534" t="s">
-        <v>6</v>
-      </c>
-      <c r="D534" s="10" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="535" spans="1:4" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B535" t="s">
+        <v>6</v>
+      </c>
+      <c r="D535" s="13" t="s">
         <v>898</v>
-      </c>
-      <c r="B535" t="s">
-        <v>6</v>
-      </c>
-      <c r="D535" s="13" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="536" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B536" t="s">
+        <v>6</v>
+      </c>
+      <c r="D536" s="45" t="s">
         <v>900</v>
-      </c>
-      <c r="B536" t="s">
-        <v>6</v>
-      </c>
-      <c r="D536" s="45" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="537" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B537" t="s">
+        <v>6</v>
+      </c>
+      <c r="D537" s="27" t="s">
         <v>902</v>
-      </c>
-      <c r="B537" t="s">
-        <v>6</v>
-      </c>
-      <c r="D537" s="27" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="538" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B538" t="s">
+        <v>6</v>
+      </c>
+      <c r="D538" s="42" t="s">
         <v>904</v>
-      </c>
-      <c r="B538" t="s">
-        <v>6</v>
-      </c>
-      <c r="D538" s="42" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="539" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B539" t="s">
         <v>6</v>
       </c>
       <c r="D539" s="42" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="540" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B540" t="s">
+        <v>6</v>
+      </c>
+      <c r="D540" t="s">
         <v>907</v>
-      </c>
-      <c r="B540" t="s">
-        <v>6</v>
-      </c>
-      <c r="D540" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="541" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B541" t="s">
         <v>6</v>
       </c>
       <c r="D541" s="49" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="542" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B542" t="s">
         <v>6</v>
       </c>
       <c r="D542" s="50" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="543" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B543" t="s">
         <v>6</v>
       </c>
       <c r="D543" s="50" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="544" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B544" t="s">
         <v>6</v>
       </c>
       <c r="D544" s="50" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="545" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B545" t="s">
+        <v>6</v>
+      </c>
+      <c r="D545" s="50" t="s">
         <v>913</v>
-      </c>
-      <c r="B545" t="s">
-        <v>6</v>
-      </c>
-      <c r="D545" s="50" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="546" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="B546" t="s">
+        <v>6</v>
+      </c>
+      <c r="D546" s="49" t="s">
         <v>915</v>
-      </c>
-      <c r="B546" t="s">
-        <v>6</v>
-      </c>
-      <c r="D546" s="49" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="547" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B547" t="s">
         <v>6</v>
       </c>
       <c r="D547" s="50" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="548" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B548" t="s">
+        <v>6</v>
+      </c>
+      <c r="D548" s="50" t="s">
         <v>918</v>
-      </c>
-      <c r="B548" t="s">
-        <v>6</v>
-      </c>
-      <c r="D548" s="50" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="549" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B549" t="s">
         <v>6</v>
       </c>
       <c r="D549" s="50" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="550" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="B550" t="s">
+        <v>6</v>
+      </c>
+      <c r="D550" s="50" t="s">
         <v>921</v>
-      </c>
-      <c r="B550" t="s">
-        <v>6</v>
-      </c>
-      <c r="D550" s="50" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="551" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B551" t="s">
+        <v>6</v>
+      </c>
+      <c r="D551" s="49" t="s">
         <v>923</v>
-      </c>
-      <c r="B551" t="s">
-        <v>6</v>
-      </c>
-      <c r="D551" s="49" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="552" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B552" t="s">
+        <v>6</v>
+      </c>
+      <c r="D552" s="50" t="s">
         <v>925</v>
-      </c>
-      <c r="B552" t="s">
-        <v>6</v>
-      </c>
-      <c r="D552" s="50" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="553" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B553" t="s">
+        <v>6</v>
+      </c>
+      <c r="D553" s="50" t="s">
         <v>927</v>
-      </c>
-      <c r="B553" t="s">
-        <v>6</v>
-      </c>
-      <c r="D553" s="50" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="554" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B554" t="s">
+        <v>6</v>
+      </c>
+      <c r="D554" s="50" t="s">
         <v>929</v>
-      </c>
-      <c r="B554" t="s">
-        <v>6</v>
-      </c>
-      <c r="D554" s="50" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="555" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B555" t="s">
+        <v>6</v>
+      </c>
+      <c r="D555" s="50" t="s">
         <v>931</v>
-      </c>
-      <c r="B555" t="s">
-        <v>6</v>
-      </c>
-      <c r="D555" s="50" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="556" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B556" t="s">
+        <v>6</v>
+      </c>
+      <c r="D556" s="10" t="s">
         <v>933</v>
-      </c>
-      <c r="B556" t="s">
-        <v>6</v>
-      </c>
-      <c r="D556" s="10" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B557" t="s">
+        <v>6</v>
+      </c>
+      <c r="D557" t="s">
         <v>935</v>
-      </c>
-      <c r="B557" t="s">
-        <v>6</v>
-      </c>
-      <c r="D557" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="558" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B558" t="s">
+        <v>6</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D558" s="27" t="s">
         <v>937</v>
-      </c>
-      <c r="B558" t="s">
-        <v>6</v>
-      </c>
-      <c r="C558" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="D558" s="27" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B559" t="s">
+        <v>6</v>
+      </c>
+      <c r="C559" t="s">
         <v>939</v>
       </c>
-      <c r="B559" t="s">
-        <v>6</v>
-      </c>
-      <c r="C559" t="s">
+      <c r="D559" t="s">
         <v>940</v>
-      </c>
-      <c r="D559" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="560" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B560" t="s">
+        <v>6</v>
+      </c>
+      <c r="D560" s="10" t="s">
         <v>942</v>
-      </c>
-      <c r="B560" t="s">
-        <v>6</v>
-      </c>
-      <c r="D560" s="10" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B561" t="s">
+        <v>6</v>
+      </c>
+      <c r="D561" t="s">
         <v>944</v>
-      </c>
-      <c r="B561" t="s">
-        <v>6</v>
-      </c>
-      <c r="D561" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" s="28" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B562" s="29" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C562" s="29"/>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B563" t="s">
         <v>15</v>
@@ -9633,7 +9807,7 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B564" t="s">
         <v>15</v>
@@ -9641,29 +9815,29 @@
     </row>
     <row r="565" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B565" t="s">
+        <v>6</v>
+      </c>
+      <c r="D565" s="26" t="s">
         <v>949</v>
-      </c>
-      <c r="B565" t="s">
-        <v>6</v>
-      </c>
-      <c r="D565" s="26" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="566" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="B566" t="s">
+        <v>6</v>
+      </c>
+      <c r="D566" s="10" t="s">
         <v>951</v>
-      </c>
-      <c r="B566" t="s">
-        <v>6</v>
-      </c>
-      <c r="D566" s="10" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B567" t="s">
         <v>6</v>
@@ -9671,7 +9845,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B568" t="s">
         <v>6</v>
@@ -9679,221 +9853,376 @@
     </row>
     <row r="569" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="30" t="s">
+        <v>954</v>
+      </c>
+      <c r="B569" t="s">
+        <v>6</v>
+      </c>
+      <c r="D569" s="51" t="s">
         <v>955</v>
-      </c>
-      <c r="B569" t="s">
-        <v>6</v>
-      </c>
-      <c r="D569" s="51" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="570" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="30" t="s">
+        <v>956</v>
+      </c>
+      <c r="B570" t="s">
+        <v>6</v>
+      </c>
+      <c r="D570" t="s">
         <v>957</v>
-      </c>
-      <c r="B570" t="s">
-        <v>6</v>
-      </c>
-      <c r="D570" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="571" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="B571" t="s">
+        <v>6</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D571" s="51" t="s">
         <v>959</v>
-      </c>
-      <c r="B571" t="s">
-        <v>6</v>
-      </c>
-      <c r="C571" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D571" s="51" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="572" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="B572" t="s">
+        <v>6</v>
+      </c>
+      <c r="D572" s="10" t="s">
         <v>961</v>
-      </c>
-      <c r="B572" t="s">
-        <v>6</v>
-      </c>
-      <c r="D572" s="10" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="573" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="B573" t="s">
+        <v>6</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D573" s="10" t="s">
         <v>963</v>
-      </c>
-      <c r="B573" t="s">
-        <v>6</v>
-      </c>
-      <c r="C573" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D573" s="10" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="574" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="B574" t="s">
+        <v>6</v>
+      </c>
+      <c r="D574" s="10" t="s">
         <v>965</v>
-      </c>
-      <c r="B574" t="s">
-        <v>6</v>
-      </c>
-      <c r="D574" s="10" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="575" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="B575" t="s">
+        <v>6</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D575" s="10" t="s">
         <v>967</v>
-      </c>
-      <c r="B575" t="s">
-        <v>6</v>
-      </c>
-      <c r="C575" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D575" s="10" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="576" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="B576" t="s">
+        <v>6</v>
+      </c>
+      <c r="D576" s="10" t="s">
         <v>969</v>
-      </c>
-      <c r="B576" t="s">
-        <v>6</v>
-      </c>
-      <c r="D576" s="10" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="577" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="B577" t="s">
+        <v>6</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D577" s="10" t="s">
         <v>971</v>
-      </c>
-      <c r="B577" t="s">
-        <v>6</v>
-      </c>
-      <c r="C577" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D577" s="10" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="578" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="B578" t="s">
+        <v>6</v>
+      </c>
+      <c r="D578" s="10" t="s">
         <v>973</v>
-      </c>
-      <c r="B578" t="s">
-        <v>6</v>
-      </c>
-      <c r="D578" s="10" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="579" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="B579" t="s">
+        <v>6</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D579" s="10" t="s">
         <v>975</v>
-      </c>
-      <c r="B579" t="s">
-        <v>6</v>
-      </c>
-      <c r="C579" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D579" s="10" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="580" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="B580" t="s">
+        <v>6</v>
+      </c>
+      <c r="D580" s="10" t="s">
         <v>977</v>
-      </c>
-      <c r="B580" t="s">
-        <v>6</v>
-      </c>
-      <c r="D580" s="10" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="581" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="B581" t="s">
+        <v>6</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D581" s="10" t="s">
         <v>979</v>
-      </c>
-      <c r="B581" t="s">
-        <v>6</v>
-      </c>
-      <c r="C581" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D581" s="10" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="582" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="B582" t="s">
+        <v>6</v>
+      </c>
+      <c r="C582" t="s">
+        <v>939</v>
+      </c>
+      <c r="D582" s="10" t="s">
         <v>981</v>
-      </c>
-      <c r="B582" t="s">
-        <v>6</v>
-      </c>
-      <c r="C582" t="s">
-        <v>940</v>
-      </c>
-      <c r="D582" s="10" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="583" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B583" t="s">
+        <v>6</v>
+      </c>
+      <c r="D583" s="10" t="s">
         <v>983</v>
-      </c>
-      <c r="B583" t="s">
-        <v>6</v>
-      </c>
-      <c r="D583" s="10" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="584" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B584" t="s">
+        <v>6</v>
+      </c>
+      <c r="D584" s="10" t="s">
         <v>985</v>
-      </c>
-      <c r="B584" t="s">
-        <v>6</v>
-      </c>
-      <c r="D584" s="10" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="585" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="B585" t="s">
+        <v>6</v>
+      </c>
+      <c r="D585" s="10" t="s">
         <v>987</v>
-      </c>
-      <c r="B585" t="s">
-        <v>6</v>
-      </c>
-      <c r="D585" s="10" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="586" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B586" t="s">
+        <v>6</v>
+      </c>
+      <c r="D586" s="10" t="s">
         <v>989</v>
       </c>
-      <c r="B586" t="s">
-        <v>6</v>
-      </c>
-      <c r="D586" s="10" t="s">
-        <v>990</v>
+    </row>
+    <row r="587" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A587" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B587" t="s">
+        <v>6</v>
+      </c>
+      <c r="D587" s="10" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A588" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B588" t="s">
+        <v>6</v>
+      </c>
+      <c r="D588" s="13" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A589" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D589" s="10" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A590" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D590" s="10" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A591" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D591" s="10" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A592" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D592" s="10" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A593" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D593" s="10" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A594" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D594" s="10" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A595" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D595" s="10" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A596" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D596" s="10" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A597" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D597" s="10" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A598" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D598" s="10" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A599" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D599" s="10" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A600" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D600" s="10" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A601" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D601" s="10" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A602" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D602" s="10" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A603" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D603" s="10" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A604" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D604" s="10" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D605" s="52" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/protocol_schema_iphra.xlsx
+++ b/inst/resources/protocol_schema_iphra.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91078F0F-6136-4D23-9BFB-A88F51445A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B822A47-05F3-44D2-A04D-736F70A44BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
